--- a/data.xlsx
+++ b/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\獎補助查詢系統\教師獎補助查詢系統_v8.2最終校務版\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\李夢涵\Desktop\教師獎補助查詢系統_v8.5.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1221,7 +1221,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="1">
-        <v>459500</v>
+        <v>59500</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\李夢涵\Desktop\教師獎補助查詢系統_v8.5.5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\115\40萬\教師獎補助查詢系統_v9.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D384DB96-6321-42C2-A4B2-E219627217C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="60" yWindow="2340" windowWidth="28740" windowHeight="7665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="資料表" sheetId="1" r:id="rId1"/>
+    <sheet name="1150309" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913" iterate="1"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="104">
   <si>
     <t>序號</t>
   </si>
@@ -219,13 +221,140 @@
   </si>
   <si>
     <t>人工智慧暨醫療應用科</t>
+  </si>
+  <si>
+    <t>王○藍</t>
+  </si>
+  <si>
+    <t>王○宏</t>
+  </si>
+  <si>
+    <t>王○豪</t>
+  </si>
+  <si>
+    <t>王○鈺</t>
+  </si>
+  <si>
+    <t>教師姓名</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>石○珍</t>
+  </si>
+  <si>
+    <t>朱○雪</t>
+  </si>
+  <si>
+    <t>吳○安</t>
+  </si>
+  <si>
+    <t>呂○陳</t>
+  </si>
+  <si>
+    <t>李○卿</t>
+  </si>
+  <si>
+    <t>李○傳</t>
+  </si>
+  <si>
+    <t>李○婷</t>
+  </si>
+  <si>
+    <t>李○緯</t>
+  </si>
+  <si>
+    <t>周○諭</t>
+  </si>
+  <si>
+    <t>林○妮</t>
+  </si>
+  <si>
+    <t>林○玉</t>
+  </si>
+  <si>
+    <t>侯○瑜</t>
+  </si>
+  <si>
+    <t>施○蘭</t>
+  </si>
+  <si>
+    <t>胡○淳</t>
+  </si>
+  <si>
+    <t>張○雯</t>
+  </si>
+  <si>
+    <t>張○昌</t>
+  </si>
+  <si>
+    <t>曹○怡</t>
+  </si>
+  <si>
+    <t>陳○靜</t>
+  </si>
+  <si>
+    <t>陳○雄</t>
+  </si>
+  <si>
+    <t>陳○森</t>
+  </si>
+  <si>
+    <t>陳○能</t>
+  </si>
+  <si>
+    <t>陳○儒</t>
+  </si>
+  <si>
+    <t>陳○彬</t>
+  </si>
+  <si>
+    <t>黃○妃</t>
+  </si>
+  <si>
+    <t>楊○偉</t>
+  </si>
+  <si>
+    <t>楊○良</t>
+  </si>
+  <si>
+    <t>楊○玲</t>
+  </si>
+  <si>
+    <t>詹○卿</t>
+  </si>
+  <si>
+    <t>詹○茹</t>
+  </si>
+  <si>
+    <t>蔡○子</t>
+  </si>
+  <si>
+    <t>鄭○菁</t>
+  </si>
+  <si>
+    <t>蕭○娟</t>
+  </si>
+  <si>
+    <t>賴○君</t>
+  </si>
+  <si>
+    <t>駱○惠</t>
+  </si>
+  <si>
+    <t>謝○威</t>
+  </si>
+  <si>
+    <t>羅○瓊</t>
+  </si>
+  <si>
+    <t>饒○先</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="21" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -381,6 +510,13 @@
       <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="33">
@@ -814,11 +950,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -842,8 +981,8 @@
     <cellStyle name="60% - 輔色5" xfId="37" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - 輔色6" xfId="41" builtinId="52" customBuiltin="1"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="一般 2" xfId="43"/>
-    <cellStyle name="一般 3" xfId="42"/>
+    <cellStyle name="一般 2" xfId="43" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="一般 3" xfId="42" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
     <cellStyle name="中等" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="合計" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
@@ -1177,9 +1316,1274 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>115</v>
+      </c>
+      <c r="C2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1">
+        <v>59500</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>115</v>
+      </c>
+      <c r="C3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1">
+        <v>52500</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>115</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="1">
+        <v>56000</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>115</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1">
+        <v>40000</v>
+      </c>
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>115</v>
+      </c>
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="1">
+        <v>51931</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>115</v>
+      </c>
+      <c r="C7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1">
+        <v>63000</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>115</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1">
+        <v>48000</v>
+      </c>
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>115</v>
+      </c>
+      <c r="C9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="1">
+        <v>56000</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>115</v>
+      </c>
+      <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="1">
+        <v>31500</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>115</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="1">
+        <v>59500</v>
+      </c>
+      <c r="G11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>115</v>
+      </c>
+      <c r="C12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="1">
+        <v>20564</v>
+      </c>
+      <c r="G12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>115</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1">
+        <v>51750</v>
+      </c>
+      <c r="G13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>115</v>
+      </c>
+      <c r="C14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="1">
+        <v>42500</v>
+      </c>
+      <c r="G14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>115</v>
+      </c>
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="1">
+        <v>63000</v>
+      </c>
+      <c r="G15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>115</v>
+      </c>
+      <c r="C16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="1">
+        <v>17000</v>
+      </c>
+      <c r="G16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>115</v>
+      </c>
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="1">
+        <v>60000</v>
+      </c>
+      <c r="G17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>115</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="1">
+        <v>59500</v>
+      </c>
+      <c r="G18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>115</v>
+      </c>
+      <c r="C19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="1">
+        <v>63000</v>
+      </c>
+      <c r="G19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>115</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="1">
+        <v>59500</v>
+      </c>
+      <c r="G20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>115</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="1">
+        <v>63000</v>
+      </c>
+      <c r="G21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>115</v>
+      </c>
+      <c r="C22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="1">
+        <v>40000</v>
+      </c>
+      <c r="G22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>115</v>
+      </c>
+      <c r="C23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1">
+        <v>70000</v>
+      </c>
+      <c r="G23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>115</v>
+      </c>
+      <c r="C24" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="1">
+        <v>56000</v>
+      </c>
+      <c r="G24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>115</v>
+      </c>
+      <c r="C25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="1">
+        <v>59500</v>
+      </c>
+      <c r="G25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>115</v>
+      </c>
+      <c r="C26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="1">
+        <v>63000</v>
+      </c>
+      <c r="G26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>115</v>
+      </c>
+      <c r="C27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="1">
+        <v>59500</v>
+      </c>
+      <c r="G27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>115</v>
+      </c>
+      <c r="C28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="1">
+        <v>59500</v>
+      </c>
+      <c r="G28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>115</v>
+      </c>
+      <c r="C29" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="1">
+        <v>51000</v>
+      </c>
+      <c r="G29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>115</v>
+      </c>
+      <c r="C30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="1">
+        <v>20368</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>115</v>
+      </c>
+      <c r="C31" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="1">
+        <v>45000</v>
+      </c>
+      <c r="G31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>115</v>
+      </c>
+      <c r="C32" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="1">
+        <v>2682</v>
+      </c>
+      <c r="G32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>115</v>
+      </c>
+      <c r="C33" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="1">
+        <v>51000</v>
+      </c>
+      <c r="G33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>115</v>
+      </c>
+      <c r="C34" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="1">
+        <v>16788</v>
+      </c>
+      <c r="G34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>115</v>
+      </c>
+      <c r="C35" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="1">
+        <v>12800</v>
+      </c>
+      <c r="G35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>115</v>
+      </c>
+      <c r="C36" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="1">
+        <v>52000</v>
+      </c>
+      <c r="G36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>115</v>
+      </c>
+      <c r="C37" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="1">
+        <v>42500</v>
+      </c>
+      <c r="G37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>115</v>
+      </c>
+      <c r="C38" t="s">
+        <v>88</v>
+      </c>
+      <c r="D38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="1">
+        <v>70000</v>
+      </c>
+      <c r="G38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>115</v>
+      </c>
+      <c r="C39" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="1">
+        <v>59500</v>
+      </c>
+      <c r="G39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>115</v>
+      </c>
+      <c r="C40" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="1">
+        <v>59500</v>
+      </c>
+      <c r="G40" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>115</v>
+      </c>
+      <c r="C41" t="s">
+        <v>90</v>
+      </c>
+      <c r="D41" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="1">
+        <v>44118</v>
+      </c>
+      <c r="G41" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>115</v>
+      </c>
+      <c r="C42" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="1">
+        <v>59500</v>
+      </c>
+      <c r="G42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>115</v>
+      </c>
+      <c r="C43" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="1">
+        <v>52500</v>
+      </c>
+      <c r="G43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>115</v>
+      </c>
+      <c r="C44" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="1">
+        <v>63000</v>
+      </c>
+      <c r="G44" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>115</v>
+      </c>
+      <c r="C45" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" t="s">
+        <v>22</v>
+      </c>
+      <c r="F45" s="1">
+        <v>31500</v>
+      </c>
+      <c r="G45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>115</v>
+      </c>
+      <c r="C46" t="s">
+        <v>95</v>
+      </c>
+      <c r="D46" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" t="s">
+        <v>22</v>
+      </c>
+      <c r="F46" s="1">
+        <v>42500</v>
+      </c>
+      <c r="G46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>115</v>
+      </c>
+      <c r="C47" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47" t="s">
+        <v>30</v>
+      </c>
+      <c r="E47" t="s">
+        <v>22</v>
+      </c>
+      <c r="F47" s="1">
+        <v>29250</v>
+      </c>
+      <c r="G47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>115</v>
+      </c>
+      <c r="C48" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" s="1">
+        <v>41384</v>
+      </c>
+      <c r="G48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>115</v>
+      </c>
+      <c r="C49" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="1">
+        <v>56000</v>
+      </c>
+      <c r="G49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>115</v>
+      </c>
+      <c r="C50" t="s">
+        <v>99</v>
+      </c>
+      <c r="D50" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" t="s">
+        <v>22</v>
+      </c>
+      <c r="F50" s="1">
+        <v>42500</v>
+      </c>
+      <c r="G50" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>115</v>
+      </c>
+      <c r="C51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D51" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" t="s">
+        <v>22</v>
+      </c>
+      <c r="F51" s="1">
+        <v>41770</v>
+      </c>
+      <c r="G51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>115</v>
+      </c>
+      <c r="C52" t="s">
+        <v>101</v>
+      </c>
+      <c r="D52" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="1">
+        <v>45000</v>
+      </c>
+      <c r="G52" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>115</v>
+      </c>
+      <c r="C53" t="s">
+        <v>102</v>
+      </c>
+      <c r="D53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="1">
+        <v>59500</v>
+      </c>
+      <c r="G53" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>115</v>
+      </c>
+      <c r="C54" t="s">
+        <v>103</v>
+      </c>
+      <c r="D54" t="s">
+        <v>61</v>
+      </c>
+      <c r="E54" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="1">
+        <v>63000</v>
+      </c>
+      <c r="G54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}">
+  <dimension ref="A1:G54"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,22 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\115\40萬\教師獎補助查詢系統_v9.2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\李夢涵\Desktop\教師獎補助查詢系統_v8.5.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D384DB96-6321-42C2-A4B2-E219627217C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="2340" windowWidth="28740" windowHeight="7665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="資料表" sheetId="1" r:id="rId1"/>
-    <sheet name="1150309" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="162913" iterate="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="62">
   <si>
     <t>序號</t>
   </si>
@@ -221,140 +219,13 @@
   </si>
   <si>
     <t>人工智慧暨醫療應用科</t>
-  </si>
-  <si>
-    <t>王○藍</t>
-  </si>
-  <si>
-    <t>王○宏</t>
-  </si>
-  <si>
-    <t>王○豪</t>
-  </si>
-  <si>
-    <t>王○鈺</t>
-  </si>
-  <si>
-    <t>教師姓名</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>石○珍</t>
-  </si>
-  <si>
-    <t>朱○雪</t>
-  </si>
-  <si>
-    <t>吳○安</t>
-  </si>
-  <si>
-    <t>呂○陳</t>
-  </si>
-  <si>
-    <t>李○卿</t>
-  </si>
-  <si>
-    <t>李○傳</t>
-  </si>
-  <si>
-    <t>李○婷</t>
-  </si>
-  <si>
-    <t>李○緯</t>
-  </si>
-  <si>
-    <t>周○諭</t>
-  </si>
-  <si>
-    <t>林○妮</t>
-  </si>
-  <si>
-    <t>林○玉</t>
-  </si>
-  <si>
-    <t>侯○瑜</t>
-  </si>
-  <si>
-    <t>施○蘭</t>
-  </si>
-  <si>
-    <t>胡○淳</t>
-  </si>
-  <si>
-    <t>張○雯</t>
-  </si>
-  <si>
-    <t>張○昌</t>
-  </si>
-  <si>
-    <t>曹○怡</t>
-  </si>
-  <si>
-    <t>陳○靜</t>
-  </si>
-  <si>
-    <t>陳○雄</t>
-  </si>
-  <si>
-    <t>陳○森</t>
-  </si>
-  <si>
-    <t>陳○能</t>
-  </si>
-  <si>
-    <t>陳○儒</t>
-  </si>
-  <si>
-    <t>陳○彬</t>
-  </si>
-  <si>
-    <t>黃○妃</t>
-  </si>
-  <si>
-    <t>楊○偉</t>
-  </si>
-  <si>
-    <t>楊○良</t>
-  </si>
-  <si>
-    <t>楊○玲</t>
-  </si>
-  <si>
-    <t>詹○卿</t>
-  </si>
-  <si>
-    <t>詹○茹</t>
-  </si>
-  <si>
-    <t>蔡○子</t>
-  </si>
-  <si>
-    <t>鄭○菁</t>
-  </si>
-  <si>
-    <t>蕭○娟</t>
-  </si>
-  <si>
-    <t>賴○君</t>
-  </si>
-  <si>
-    <t>駱○惠</t>
-  </si>
-  <si>
-    <t>謝○威</t>
-  </si>
-  <si>
-    <t>羅○瓊</t>
-  </si>
-  <si>
-    <t>饒○先</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -511,13 +382,6 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -950,14 +814,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -981,8 +842,8 @@
     <cellStyle name="60% - 輔色5" xfId="37" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - 輔色6" xfId="41" builtinId="52" customBuiltin="1"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="一般 2" xfId="43" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="一般 3" xfId="42" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="一般 2" xfId="43"/>
+    <cellStyle name="一般 3" xfId="42"/>
     <cellStyle name="中等" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="合計" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
@@ -1316,1274 +1177,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFFF0000"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="2" width="4.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>115</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>115</v>
-      </c>
-      <c r="C3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1">
-        <v>52500</v>
-      </c>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>115</v>
-      </c>
-      <c r="C4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1">
-        <v>56000</v>
-      </c>
-      <c r="G4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>115</v>
-      </c>
-      <c r="C5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="1">
-        <v>40000</v>
-      </c>
-      <c r="G5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>115</v>
-      </c>
-      <c r="C6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="1">
-        <v>51931</v>
-      </c>
-      <c r="G6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>115</v>
-      </c>
-      <c r="C7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="1">
-        <v>63000</v>
-      </c>
-      <c r="G7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>115</v>
-      </c>
-      <c r="C8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="1">
-        <v>48000</v>
-      </c>
-      <c r="G8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>115</v>
-      </c>
-      <c r="C9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="1">
-        <v>56000</v>
-      </c>
-      <c r="G9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>115</v>
-      </c>
-      <c r="C10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="1">
-        <v>31500</v>
-      </c>
-      <c r="G10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>115</v>
-      </c>
-      <c r="C11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>115</v>
-      </c>
-      <c r="C12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="1">
-        <v>20564</v>
-      </c>
-      <c r="G12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>115</v>
-      </c>
-      <c r="C13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="1">
-        <v>51750</v>
-      </c>
-      <c r="G13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>115</v>
-      </c>
-      <c r="C14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="1">
-        <v>42500</v>
-      </c>
-      <c r="G14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>115</v>
-      </c>
-      <c r="C15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="1">
-        <v>63000</v>
-      </c>
-      <c r="G15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>115</v>
-      </c>
-      <c r="C16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="1">
-        <v>17000</v>
-      </c>
-      <c r="G16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>115</v>
-      </c>
-      <c r="C17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="1">
-        <v>60000</v>
-      </c>
-      <c r="G17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>115</v>
-      </c>
-      <c r="C18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>115</v>
-      </c>
-      <c r="C19" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="1">
-        <v>63000</v>
-      </c>
-      <c r="G19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>115</v>
-      </c>
-      <c r="C20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>115</v>
-      </c>
-      <c r="C21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="1">
-        <v>63000</v>
-      </c>
-      <c r="G21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22">
-        <v>115</v>
-      </c>
-      <c r="C22" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="1">
-        <v>40000</v>
-      </c>
-      <c r="G22" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23">
-        <v>115</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="1">
-        <v>70000</v>
-      </c>
-      <c r="G23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24">
-        <v>115</v>
-      </c>
-      <c r="C24" t="s">
-        <v>78</v>
-      </c>
-      <c r="D24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="1">
-        <v>56000</v>
-      </c>
-      <c r="G24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25">
-        <v>115</v>
-      </c>
-      <c r="C25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G25" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26">
-        <v>115</v>
-      </c>
-      <c r="C26" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="1">
-        <v>63000</v>
-      </c>
-      <c r="G26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27">
-        <v>115</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28">
-        <v>115</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G28" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29">
-        <v>115</v>
-      </c>
-      <c r="C29" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="1">
-        <v>51000</v>
-      </c>
-      <c r="G29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30">
-        <v>115</v>
-      </c>
-      <c r="C30" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="1">
-        <v>20368</v>
-      </c>
-      <c r="G30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31">
-        <v>115</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="1">
-        <v>45000</v>
-      </c>
-      <c r="G31" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32">
-        <v>115</v>
-      </c>
-      <c r="C32" t="s">
-        <v>85</v>
-      </c>
-      <c r="D32" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="1">
-        <v>2682</v>
-      </c>
-      <c r="G32" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33">
-        <v>115</v>
-      </c>
-      <c r="C33" t="s">
-        <v>85</v>
-      </c>
-      <c r="D33" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="1">
-        <v>51000</v>
-      </c>
-      <c r="G33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34">
-        <v>115</v>
-      </c>
-      <c r="C34" t="s">
-        <v>86</v>
-      </c>
-      <c r="D34" t="s">
-        <v>41</v>
-      </c>
-      <c r="E34" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="1">
-        <v>16788</v>
-      </c>
-      <c r="G34" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35">
-        <v>115</v>
-      </c>
-      <c r="C35" t="s">
-        <v>86</v>
-      </c>
-      <c r="D35" t="s">
-        <v>41</v>
-      </c>
-      <c r="E35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="1">
-        <v>12800</v>
-      </c>
-      <c r="G35" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36">
-        <v>115</v>
-      </c>
-      <c r="C36" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" t="s">
-        <v>17</v>
-      </c>
-      <c r="E36" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="1">
-        <v>52000</v>
-      </c>
-      <c r="G36" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37">
-        <v>115</v>
-      </c>
-      <c r="C37" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="1">
-        <v>42500</v>
-      </c>
-      <c r="G37" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38">
-        <v>115</v>
-      </c>
-      <c r="C38" t="s">
-        <v>88</v>
-      </c>
-      <c r="D38" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="1">
-        <v>70000</v>
-      </c>
-      <c r="G38" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39">
-        <v>115</v>
-      </c>
-      <c r="C39" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G39" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40">
-        <v>115</v>
-      </c>
-      <c r="C40" t="s">
-        <v>89</v>
-      </c>
-      <c r="D40" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G40" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41">
-        <v>115</v>
-      </c>
-      <c r="C41" t="s">
-        <v>90</v>
-      </c>
-      <c r="D41" t="s">
-        <v>47</v>
-      </c>
-      <c r="E41" t="s">
-        <v>22</v>
-      </c>
-      <c r="F41" s="1">
-        <v>44118</v>
-      </c>
-      <c r="G41" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42">
-        <v>115</v>
-      </c>
-      <c r="C42" t="s">
-        <v>91</v>
-      </c>
-      <c r="D42" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43">
-        <v>115</v>
-      </c>
-      <c r="C43" t="s">
-        <v>92</v>
-      </c>
-      <c r="D43" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="1">
-        <v>52500</v>
-      </c>
-      <c r="G43" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44">
-        <v>115</v>
-      </c>
-      <c r="C44" t="s">
-        <v>93</v>
-      </c>
-      <c r="D44" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="1">
-        <v>63000</v>
-      </c>
-      <c r="G44" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45">
-        <v>115</v>
-      </c>
-      <c r="C45" t="s">
-        <v>94</v>
-      </c>
-      <c r="D45" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" t="s">
-        <v>22</v>
-      </c>
-      <c r="F45" s="1">
-        <v>31500</v>
-      </c>
-      <c r="G45" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46">
-        <v>115</v>
-      </c>
-      <c r="C46" t="s">
-        <v>95</v>
-      </c>
-      <c r="D46" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46" t="s">
-        <v>22</v>
-      </c>
-      <c r="F46" s="1">
-        <v>42500</v>
-      </c>
-      <c r="G46" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47">
-        <v>115</v>
-      </c>
-      <c r="C47" t="s">
-        <v>96</v>
-      </c>
-      <c r="D47" t="s">
-        <v>30</v>
-      </c>
-      <c r="E47" t="s">
-        <v>22</v>
-      </c>
-      <c r="F47" s="1">
-        <v>29250</v>
-      </c>
-      <c r="G47" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48">
-        <v>115</v>
-      </c>
-      <c r="C48" t="s">
-        <v>97</v>
-      </c>
-      <c r="D48" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F48" s="1">
-        <v>41384</v>
-      </c>
-      <c r="G48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49">
-        <v>115</v>
-      </c>
-      <c r="C49" t="s">
-        <v>98</v>
-      </c>
-      <c r="D49" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" s="1">
-        <v>56000</v>
-      </c>
-      <c r="G49" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50">
-        <v>115</v>
-      </c>
-      <c r="C50" t="s">
-        <v>99</v>
-      </c>
-      <c r="D50" t="s">
-        <v>21</v>
-      </c>
-      <c r="E50" t="s">
-        <v>22</v>
-      </c>
-      <c r="F50" s="1">
-        <v>42500</v>
-      </c>
-      <c r="G50" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51">
-        <v>115</v>
-      </c>
-      <c r="C51" t="s">
-        <v>100</v>
-      </c>
-      <c r="D51" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" t="s">
-        <v>22</v>
-      </c>
-      <c r="F51" s="1">
-        <v>41770</v>
-      </c>
-      <c r="G51" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52">
-        <v>115</v>
-      </c>
-      <c r="C52" t="s">
-        <v>101</v>
-      </c>
-      <c r="D52" t="s">
-        <v>21</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" s="1">
-        <v>45000</v>
-      </c>
-      <c r="G52" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53">
-        <v>115</v>
-      </c>
-      <c r="C53" t="s">
-        <v>102</v>
-      </c>
-      <c r="D53" t="s">
-        <v>61</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G53" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54">
-        <v>115</v>
-      </c>
-      <c r="C54" t="s">
-        <v>103</v>
-      </c>
-      <c r="D54" t="s">
-        <v>61</v>
-      </c>
-      <c r="E54" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" s="1">
-        <v>63000</v>
-      </c>
-      <c r="G54" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}">
-  <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\李夢涵\Desktop\教師獎補助查詢系統_v8.5.5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE0A574-B569-4623-B375-4B05FEA945E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="資料表" sheetId="1" r:id="rId1"/>
+    <sheet name="資料表" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="69">
   <si>
     <t>序號</t>
   </si>
@@ -219,13 +220,41 @@
   </si>
   <si>
     <t>人工智慧暨醫療應用科</t>
+  </si>
+  <si>
+    <t>楊東偉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>智慧科技長期照顧科</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>進修</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>(請款額度依學雜費繳費單,上限60000元/學期)113年6月24日校教評會議通過</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>李瑾婷</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>護理科</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>(請款額度依學雜費繳費單,上限60000元/學期)114年3月25日校教評會議通過</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="21" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -382,6 +411,13 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -814,11 +850,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -842,8 +881,8 @@
     <cellStyle name="60% - 輔色5" xfId="37" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - 輔色6" xfId="41" builtinId="52" customBuiltin="1"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="一般 2" xfId="43"/>
-    <cellStyle name="一般 3" xfId="42"/>
+    <cellStyle name="一般 2" xfId="43" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="一般 3" xfId="42" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
     <cellStyle name="中等" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="合計" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
@@ -1177,9 +1216,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}">
+  <dimension ref="A1:G56"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -2421,6 +2460,46 @@
       </c>
       <c r="G54" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>115</v>
+      </c>
+      <c r="C55" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" t="s">
+        <v>63</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>115</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE0A574-B569-4623-B375-4B05FEA945E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CECD1BD-3BA1-4388-84A3-3714023F5400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="資料表" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$G$73</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="83">
   <si>
     <t>序號</t>
   </si>
@@ -226,27 +229,86 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>李瑾婷</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>智慧科技長期照顧科</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>護理科</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>進修</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>(請款額度依學雜費繳費單,上限60000元/學期)114年3月25日校教評會議通過</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>(請款額度依學雜費繳費單,上限60000元/學期)113年6月24日校教評會議通過</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>李瑾婷</t>
+    <t>陳家蓁</t>
+  </si>
+  <si>
+    <t>115年3月17日教學發展委員會會議通過</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>護理科</t>
+    <t>張義宏</t>
+  </si>
+  <si>
+    <t>廖淑雯</t>
+  </si>
+  <si>
+    <t>陳偉玲</t>
+  </si>
+  <si>
+    <t>柯榮貴</t>
+  </si>
+  <si>
+    <t>劉錦源</t>
+  </si>
+  <si>
+    <t>幼兒保育科</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>(請款額度依學雜費繳費單,上限60000元/學期)114年3月25日校教評會議通過</t>
+    <t>餐飲管理科</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>化妝品應用與管理科</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命關懷事業科</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智慧暨醫療應用科</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>研究</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>115年3月17日學術審查委員會會議通過</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -254,7 +316,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -418,6 +480,33 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -850,7 +939,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -858,6 +947,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1217,8 +1315,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.125" customWidth="1"/>
+    <col min="4" max="4" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -2473,13 +2579,13 @@
         <v>62</v>
       </c>
       <c r="D55" t="s">
-        <v>63</v>
-      </c>
-      <c r="E55" s="2" t="s">
         <v>64</v>
       </c>
+      <c r="E55" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="G55" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -2490,16 +2596,407 @@
         <v>115</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="G56" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E56" s="2" t="s">
+    </row>
+    <row r="57" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>115</v>
+      </c>
+      <c r="C57" t="s">
+        <v>71</v>
+      </c>
+      <c r="D57" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F57">
+        <v>300000</v>
+      </c>
+      <c r="G57" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>115</v>
+      </c>
+      <c r="C58" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F58">
+        <v>140000</v>
+      </c>
+      <c r="G58" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>115</v>
+      </c>
+      <c r="C59" t="s">
+        <v>37</v>
+      </c>
+      <c r="D59" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F59">
+        <v>250000</v>
+      </c>
+      <c r="G59" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>115</v>
+      </c>
+      <c r="C60" t="s">
+        <v>72</v>
+      </c>
+      <c r="D60" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F60">
+        <v>95912</v>
+      </c>
+      <c r="G60" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>115</v>
+      </c>
+      <c r="C61" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F61">
+        <v>128075</v>
+      </c>
+      <c r="G61" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>115</v>
+      </c>
+      <c r="C62" t="s">
+        <v>73</v>
+      </c>
+      <c r="D62" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F62">
+        <v>300000</v>
+      </c>
+      <c r="G62" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>115</v>
+      </c>
+      <c r="C63" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" t="s">
+        <v>76</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F63">
+        <v>150000</v>
+      </c>
+      <c r="G63" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>115</v>
+      </c>
+      <c r="C64" t="s">
+        <v>74</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F64">
+        <v>117750</v>
+      </c>
+      <c r="G64" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A65">
         <v>64</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="B65">
+        <v>115</v>
+      </c>
+      <c r="C65" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F65">
+        <v>143300</v>
+      </c>
+      <c r="G65" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>115</v>
+      </c>
+      <c r="C66" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F66">
+        <v>165000</v>
+      </c>
+      <c r="G66" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>115</v>
+      </c>
+      <c r="C67" t="s">
+        <v>36</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F67">
+        <v>255000</v>
+      </c>
+      <c r="G67" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>115</v>
+      </c>
+      <c r="C68" t="s">
+        <v>43</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F68">
+        <v>210000</v>
+      </c>
+      <c r="G68" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A69">
         <v>68</v>
+      </c>
+      <c r="B69">
+        <v>115</v>
+      </c>
+      <c r="C69" t="s">
+        <v>45</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F69">
+        <v>200000</v>
+      </c>
+      <c r="G69" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>115</v>
+      </c>
+      <c r="C70" t="s">
+        <v>34</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F70">
+        <v>106530</v>
+      </c>
+      <c r="G70" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>115</v>
+      </c>
+      <c r="C71" t="s">
+        <v>46</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F71">
+        <v>217500</v>
+      </c>
+      <c r="G71" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>115</v>
+      </c>
+      <c r="C72" t="s">
+        <v>75</v>
+      </c>
+      <c r="D72" t="s">
+        <v>41</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F72">
+        <v>28500</v>
+      </c>
+      <c r="G72" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>115</v>
+      </c>
+      <c r="C73" t="s">
+        <v>59</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F73">
+        <v>221000</v>
+      </c>
+      <c r="G73" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CECD1BD-3BA1-4388-84A3-3714023F5400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42E7BCF-967E-45D7-8826-B33331F917B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -245,14 +245,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>(請款額度依學雜費繳費單,上限60000元/學期)114年3月25日校教評會議通過</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>(請款額度依學雜費繳費單,上限60000元/學期)113年6月24日校教評會議通過</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>陳家蓁</t>
   </si>
   <si>
@@ -309,6 +301,14 @@
   </si>
   <si>
     <t>115年3月17日學術審查委員會會議通過</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>(暫顯示0,請款經費依學雜費繳費單實支,上限60000元/學期)113年6月24日校教評會議通過</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>(暫顯示0,請款額度依學雜費繳費單實支,上限60000元/學期)114年3月25日校教評會議通過</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2585,7 +2585,7 @@
         <v>66</v>
       </c>
       <c r="G55" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -2605,7 +2605,7 @@
         <v>66</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2616,19 +2616,19 @@
         <v>115</v>
       </c>
       <c r="C57" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D57" t="s">
         <v>24</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F57">
         <v>300000</v>
       </c>
       <c r="G57" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2645,13 +2645,13 @@
         <v>24</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F58">
         <v>140000</v>
       </c>
       <c r="G58" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2668,13 +2668,13 @@
         <v>24</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F59">
         <v>250000</v>
       </c>
       <c r="G59" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2685,19 +2685,19 @@
         <v>115</v>
       </c>
       <c r="C60" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D60" t="s">
         <v>24</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F60">
         <v>95912</v>
       </c>
       <c r="G60" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2714,13 +2714,13 @@
         <v>24</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F61">
         <v>128075</v>
       </c>
       <c r="G61" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2731,19 +2731,19 @@
         <v>115</v>
       </c>
       <c r="C62" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D62" t="s">
         <v>24</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F62">
         <v>300000</v>
       </c>
       <c r="G62" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2757,16 +2757,16 @@
         <v>29</v>
       </c>
       <c r="D63" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F63">
         <v>150000</v>
       </c>
       <c r="G63" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2777,19 +2777,19 @@
         <v>115</v>
       </c>
       <c r="C64" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F64">
         <v>117750</v>
       </c>
       <c r="G64" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2800,19 +2800,19 @@
         <v>115</v>
       </c>
       <c r="C65" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F65">
         <v>143300</v>
       </c>
       <c r="G65" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2826,16 +2826,16 @@
         <v>16</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F66">
         <v>165000</v>
       </c>
       <c r="G66" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2849,16 +2849,16 @@
         <v>36</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F67">
         <v>255000</v>
       </c>
       <c r="G67" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2872,16 +2872,16 @@
         <v>43</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F68">
         <v>210000</v>
       </c>
       <c r="G68" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2895,16 +2895,16 @@
         <v>45</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F69">
         <v>200000</v>
       </c>
       <c r="G69" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2918,16 +2918,16 @@
         <v>34</v>
       </c>
       <c r="D70" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E70" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="F70">
         <v>106530</v>
       </c>
       <c r="G70" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2944,13 +2944,13 @@
         <v>64</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F71">
         <v>217500</v>
       </c>
       <c r="G71" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2961,19 +2961,19 @@
         <v>115</v>
       </c>
       <c r="C72" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D72" t="s">
         <v>41</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F72">
         <v>28500</v>
       </c>
       <c r="G72" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2987,16 +2987,16 @@
         <v>59</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F73">
         <v>221000</v>
       </c>
       <c r="G73" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42E7BCF-967E-45D7-8826-B33331F917B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26480584-7061-4B40-81BD-2079B29C5DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="資料表" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$G$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$G$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2568,7 +2568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2576,36 +2576,42 @@
         <v>115</v>
       </c>
       <c r="C55" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D55" t="s">
-        <v>64</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>66</v>
+        <v>24</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F55">
+        <v>300000</v>
       </c>
       <c r="G55" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56">
         <v>115</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>82</v>
+      <c r="C56" t="s">
+        <v>28</v>
+      </c>
+      <c r="D56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F56">
+        <v>140000</v>
+      </c>
+      <c r="G56" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2616,7 +2622,7 @@
         <v>115</v>
       </c>
       <c r="C57" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="D57" t="s">
         <v>24</v>
@@ -2625,10 +2631,10 @@
         <v>79</v>
       </c>
       <c r="F57">
-        <v>300000</v>
+        <v>250000</v>
       </c>
       <c r="G57" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2639,7 +2645,7 @@
         <v>115</v>
       </c>
       <c r="C58" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="D58" t="s">
         <v>24</v>
@@ -2648,7 +2654,7 @@
         <v>79</v>
       </c>
       <c r="F58">
-        <v>140000</v>
+        <v>95912</v>
       </c>
       <c r="G58" t="s">
         <v>80</v>
@@ -2662,7 +2668,7 @@
         <v>115</v>
       </c>
       <c r="C59" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D59" t="s">
         <v>24</v>
@@ -2671,7 +2677,7 @@
         <v>79</v>
       </c>
       <c r="F59">
-        <v>250000</v>
+        <v>128075</v>
       </c>
       <c r="G59" t="s">
         <v>80</v>
@@ -2685,7 +2691,7 @@
         <v>115</v>
       </c>
       <c r="C60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D60" t="s">
         <v>24</v>
@@ -2694,7 +2700,7 @@
         <v>79</v>
       </c>
       <c r="F60">
-        <v>95912</v>
+        <v>300000</v>
       </c>
       <c r="G60" t="s">
         <v>80</v>
@@ -2708,16 +2714,16 @@
         <v>115</v>
       </c>
       <c r="C61" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D61" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>79</v>
       </c>
       <c r="F61">
-        <v>128075</v>
+        <v>150000</v>
       </c>
       <c r="G61" t="s">
         <v>80</v>
@@ -2731,16 +2737,16 @@
         <v>115</v>
       </c>
       <c r="C62" t="s">
-        <v>71</v>
-      </c>
-      <c r="D62" t="s">
-        <v>24</v>
+        <v>72</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="E62" s="5" t="s">
         <v>79</v>
       </c>
       <c r="F62">
-        <v>300000</v>
+        <v>117750</v>
       </c>
       <c r="G62" t="s">
         <v>80</v>
@@ -2754,16 +2760,16 @@
         <v>115</v>
       </c>
       <c r="C63" t="s">
-        <v>29</v>
-      </c>
-      <c r="D63" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>79</v>
       </c>
       <c r="F63">
-        <v>150000</v>
+        <v>143300</v>
       </c>
       <c r="G63" t="s">
         <v>80</v>
@@ -2777,16 +2783,16 @@
         <v>115</v>
       </c>
       <c r="C64" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>79</v>
       </c>
       <c r="F64">
-        <v>117750</v>
+        <v>165000</v>
       </c>
       <c r="G64" t="s">
         <v>80</v>
@@ -2800,16 +2806,16 @@
         <v>115</v>
       </c>
       <c r="C65" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>79</v>
       </c>
       <c r="F65">
-        <v>143300</v>
+        <v>255000</v>
       </c>
       <c r="G65" t="s">
         <v>80</v>
@@ -2823,7 +2829,7 @@
         <v>115</v>
       </c>
       <c r="C66" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>76</v>
@@ -2832,7 +2838,7 @@
         <v>79</v>
       </c>
       <c r="F66">
-        <v>165000</v>
+        <v>210000</v>
       </c>
       <c r="G66" t="s">
         <v>80</v>
@@ -2846,7 +2852,7 @@
         <v>115</v>
       </c>
       <c r="C67" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>76</v>
@@ -2855,7 +2861,7 @@
         <v>79</v>
       </c>
       <c r="F67">
-        <v>255000</v>
+        <v>200000</v>
       </c>
       <c r="G67" t="s">
         <v>80</v>
@@ -2869,16 +2875,16 @@
         <v>115</v>
       </c>
       <c r="C68" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>79</v>
       </c>
       <c r="F68">
-        <v>210000</v>
+        <v>106530</v>
       </c>
       <c r="G68" t="s">
         <v>80</v>
@@ -2892,16 +2898,16 @@
         <v>115</v>
       </c>
       <c r="C69" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>79</v>
       </c>
       <c r="F69">
-        <v>200000</v>
+        <v>217500</v>
       </c>
       <c r="G69" t="s">
         <v>80</v>
@@ -2915,16 +2921,16 @@
         <v>115</v>
       </c>
       <c r="C70" t="s">
-        <v>34</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
+      </c>
+      <c r="D70" t="s">
+        <v>41</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>79</v>
       </c>
       <c r="F70">
-        <v>106530</v>
+        <v>28500</v>
       </c>
       <c r="G70" t="s">
         <v>80</v>
@@ -2938,22 +2944,22 @@
         <v>115</v>
       </c>
       <c r="C71" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>79</v>
       </c>
       <c r="F71">
-        <v>217500</v>
+        <v>221000</v>
       </c>
       <c r="G71" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2961,42 +2967,36 @@
         <v>115</v>
       </c>
       <c r="C72" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D72" t="s">
-        <v>41</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F72">
-        <v>28500</v>
+        <v>64</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="G72" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73">
         <v>115</v>
       </c>
-      <c r="C73" t="s">
-        <v>59</v>
+      <c r="C73" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F73">
-        <v>221000</v>
-      </c>
-      <c r="G73" t="s">
-        <v>80</v>
+        <v>65</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26480584-7061-4B40-81BD-2079B29C5DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A85E2848-66F0-4D2A-A126-EBBB4E221C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="資料表" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$G$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$G$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="89">
   <si>
     <t>序號</t>
   </si>
@@ -245,7 +245,27 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>(請款額度依學雜費繳費單,上限60000元/學期)114年3月25日校教評會議通過</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>(請款額度依學雜費繳費單,上限60000元/學期)113年6月24日校教評會議通過</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡芷茵</t>
+  </si>
+  <si>
     <t>陳家蓁</t>
+  </si>
+  <si>
+    <t>林敬順</t>
+  </si>
+  <si>
+    <t>吳緯文</t>
+  </si>
+  <si>
+    <t>孫惠玲</t>
   </si>
   <si>
     <t>115年3月17日教學發展委員會會議通過</t>
@@ -304,19 +324,21 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>(暫顯示0,請款經費依學雜費繳費單實支,上限60000元/學期)113年6月24日校教評會議通過</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>(暫顯示0,請款額度依學雜費繳費單實支,上限60000元/學期)114年3月25日校教評會議通過</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>補助教師指導學生參與校外競賽</t>
+    <phoneticPr fontId="26" type="noConversion"/>
+  </si>
+  <si>
+    <t>115年3月17日教學發展委員會會議通過</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="#,##0_ "/>
+  </numFmts>
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -506,6 +528,13 @@
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -939,7 +968,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -957,6 +986,12 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1315,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="4.75" bestFit="1" customWidth="1"/>
@@ -2568,7 +2603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2576,42 +2611,36 @@
         <v>115</v>
       </c>
       <c r="C55" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D55" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F55">
-        <v>300000</v>
+        <v>64</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="G55" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56">
         <v>115</v>
       </c>
-      <c r="C56" t="s">
-        <v>28</v>
-      </c>
-      <c r="D56" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F56">
-        <v>140000</v>
-      </c>
-      <c r="G56" t="s">
-        <v>80</v>
+      <c r="C56" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2622,19 +2651,19 @@
         <v>115</v>
       </c>
       <c r="C57" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D57" t="s">
         <v>24</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F57">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="G57" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2645,19 +2674,19 @@
         <v>115</v>
       </c>
       <c r="C58" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="D58" t="s">
         <v>24</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F58">
-        <v>95912</v>
+        <v>140000</v>
       </c>
       <c r="G58" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2668,19 +2697,19 @@
         <v>115</v>
       </c>
       <c r="C59" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D59" t="s">
         <v>24</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F59">
-        <v>128075</v>
+        <v>250000</v>
       </c>
       <c r="G59" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2691,19 +2720,19 @@
         <v>115</v>
       </c>
       <c r="C60" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D60" t="s">
         <v>24</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F60">
-        <v>300000</v>
+        <v>95912</v>
       </c>
       <c r="G60" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2714,19 +2743,19 @@
         <v>115</v>
       </c>
       <c r="C61" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F61">
-        <v>150000</v>
+        <v>128075</v>
       </c>
       <c r="G61" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2737,19 +2766,19 @@
         <v>115</v>
       </c>
       <c r="C62" t="s">
-        <v>72</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="D62" t="s">
+        <v>24</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F62">
-        <v>117750</v>
+        <v>300000</v>
       </c>
       <c r="G62" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2760,19 +2789,19 @@
         <v>115</v>
       </c>
       <c r="C63" t="s">
-        <v>67</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>75</v>
+        <v>29</v>
+      </c>
+      <c r="D63" t="s">
+        <v>80</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F63">
-        <v>143300</v>
+        <v>150000</v>
       </c>
       <c r="G63" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2783,19 +2812,19 @@
         <v>115</v>
       </c>
       <c r="C64" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F64">
-        <v>165000</v>
+        <v>117750</v>
       </c>
       <c r="G64" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2806,19 +2835,19 @@
         <v>115</v>
       </c>
       <c r="C65" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F65">
-        <v>255000</v>
+        <v>143300</v>
       </c>
       <c r="G65" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2829,19 +2858,19 @@
         <v>115</v>
       </c>
       <c r="C66" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F66">
-        <v>210000</v>
+        <v>165000</v>
       </c>
       <c r="G66" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2852,19 +2881,19 @@
         <v>115</v>
       </c>
       <c r="C67" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F67">
-        <v>200000</v>
+        <v>255000</v>
       </c>
       <c r="G67" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2875,19 +2904,19 @@
         <v>115</v>
       </c>
       <c r="C68" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F68">
-        <v>106530</v>
+        <v>210000</v>
       </c>
       <c r="G68" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2898,19 +2927,19 @@
         <v>115</v>
       </c>
       <c r="C69" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F69">
-        <v>217500</v>
+        <v>200000</v>
       </c>
       <c r="G69" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2921,19 +2950,19 @@
         <v>115</v>
       </c>
       <c r="C70" t="s">
-        <v>73</v>
-      </c>
-      <c r="D70" t="s">
-        <v>41</v>
+        <v>34</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F70">
-        <v>28500</v>
+        <v>106530</v>
       </c>
       <c r="G70" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2944,22 +2973,22 @@
         <v>115</v>
       </c>
       <c r="C71" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F71">
-        <v>221000</v>
+        <v>217500</v>
       </c>
       <c r="G71" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2967,36 +2996,410 @@
         <v>115</v>
       </c>
       <c r="C72" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="D72" t="s">
-        <v>64</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F72">
+        <v>28500</v>
       </c>
       <c r="G72" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73">
         <v>115</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>63</v>
+      <c r="C73" t="s">
+        <v>59</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F73">
+        <v>221000</v>
+      </c>
+      <c r="G73" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74" s="6">
+        <v>115</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F74" s="7">
+        <v>28884</v>
+      </c>
+      <c r="G74" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>72</v>
+      </c>
+      <c r="B75" s="6">
+        <v>115</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F75" s="7">
+        <v>23014</v>
+      </c>
+      <c r="G75" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>72</v>
+      </c>
+      <c r="B76" s="6">
+        <v>115</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F76" s="7">
+        <v>39125</v>
+      </c>
+      <c r="G76" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>72</v>
+      </c>
+      <c r="B77" s="6">
+        <v>115</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F77" s="7">
+        <v>43084</v>
+      </c>
+      <c r="G77" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>72</v>
+      </c>
+      <c r="B78" s="6">
+        <v>115</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F78" s="7">
+        <v>62600</v>
+      </c>
+      <c r="G78" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>72</v>
+      </c>
+      <c r="B79" s="6">
+        <v>115</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F79" s="7">
+        <v>47687</v>
+      </c>
+      <c r="G79" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>72</v>
+      </c>
+      <c r="B80" s="6">
+        <v>115</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F80" s="7">
+        <v>39355</v>
+      </c>
+      <c r="G80" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>72</v>
+      </c>
+      <c r="B81" s="6">
+        <v>115</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F81" s="7">
+        <v>34568</v>
+      </c>
+      <c r="G81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>72</v>
+      </c>
+      <c r="B82" s="6">
+        <v>115</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F82" s="7">
+        <v>52776</v>
+      </c>
+      <c r="G82" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>72</v>
+      </c>
+      <c r="B83" s="6">
+        <v>115</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F83" s="7">
+        <v>48284</v>
+      </c>
+      <c r="G83" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>72</v>
+      </c>
+      <c r="B84" s="6">
+        <v>115</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F84" s="7">
+        <v>8285</v>
+      </c>
+      <c r="G84" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>72</v>
+      </c>
+      <c r="B85" s="6">
+        <v>115</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F85" s="7">
+        <v>18412</v>
+      </c>
+      <c r="G85" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>72</v>
+      </c>
+      <c r="B86" s="6">
+        <v>115</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F86" s="7">
+        <v>16571</v>
+      </c>
+      <c r="G86" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>72</v>
+      </c>
+      <c r="B87" s="6">
+        <v>115</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F87" s="7">
+        <v>8285</v>
+      </c>
+      <c r="G87" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>72</v>
+      </c>
+      <c r="B88" s="6">
+        <v>115</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F88" s="7">
+        <v>11185</v>
+      </c>
+      <c r="G88" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>72</v>
+      </c>
+      <c r="B89" s="6">
+        <v>115</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F89" s="7">
+        <v>26283</v>
+      </c>
+      <c r="G89" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A85E2848-66F0-4D2A-A126-EBBB4E221C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B4382A-D6E8-45F9-A82D-077D623B8625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -972,26 +972,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1350,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}">
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="4.75" bestFit="1" customWidth="1"/>
@@ -1365,22 +1365,22 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1388,22 +1388,22 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>115</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="1">
+        <v>115</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>59500</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1411,22 +1411,22 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>115</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="1">
+        <v>115</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>52500</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1434,22 +1434,22 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>115</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="1">
+        <v>115</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <v>56000</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1457,22 +1457,22 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>115</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" s="1">
+        <v>115</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <v>40000</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1480,160 +1480,160 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>115</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="1">
-        <v>51931</v>
-      </c>
-      <c r="G6" t="s">
-        <v>9</v>
+      <c r="B6" s="1">
+        <v>115</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="3">
+        <v>43084</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>115</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="1">
-        <v>63000</v>
-      </c>
-      <c r="G7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B7" s="1">
+        <v>115</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2">
+        <v>51931</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>115</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
+      <c r="B8" s="1">
+        <v>115</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="F8" s="1">
-        <v>48000</v>
-      </c>
-      <c r="G8" t="s">
-        <v>9</v>
+        <v>128075</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>115</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="B9" s="1">
+        <v>115</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="1">
-        <v>56000</v>
-      </c>
-      <c r="G9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F9" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
-        <v>115</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
+      <c r="B10" s="1">
+        <v>115</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="F10" s="1">
-        <v>31500</v>
-      </c>
-      <c r="G10" t="s">
-        <v>9</v>
+        <v>165000</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11">
-        <v>115</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G11" t="s">
-        <v>9</v>
+      <c r="B11" s="1">
+        <v>115</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" s="3">
+        <v>8285</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12">
-        <v>115</v>
-      </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="1">
-        <v>20564</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="B12" s="1">
+        <v>115</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="2">
+        <v>48000</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1641,45 +1641,45 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13">
-        <v>115</v>
-      </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="B13" s="1">
+        <v>115</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="1">
-        <v>51750</v>
-      </c>
-      <c r="G13" t="s">
-        <v>9</v>
+      <c r="E13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="3">
+        <v>62600</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14">
-        <v>115</v>
-      </c>
-      <c r="C14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="B14" s="1">
+        <v>115</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="1">
-        <v>42500</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="E14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2">
+        <v>56000</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1687,68 +1687,68 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15">
-        <v>115</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="B15" s="1">
+        <v>115</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="1">
-        <v>63000</v>
-      </c>
-      <c r="G15" t="s">
-        <v>9</v>
+      <c r="E15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="3">
+        <v>18412</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16">
-        <v>115</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="1">
-        <v>17000</v>
-      </c>
-      <c r="G16" t="s">
-        <v>9</v>
+      <c r="B16" s="1">
+        <v>115</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="3">
+        <v>16571</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17">
-        <v>115</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="B17" s="1">
+        <v>115</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="1">
-        <v>60000</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="E17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="2">
+        <v>31500</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1756,22 +1756,22 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18">
-        <v>115</v>
-      </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="B18" s="1">
+        <v>115</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="2">
         <v>59500</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1779,22 +1779,22 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19">
-        <v>115</v>
-      </c>
-      <c r="C19" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="1">
-        <v>63000</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="B19" s="1">
+        <v>115</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="2">
+        <v>20564</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1802,22 +1802,22 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20">
-        <v>115</v>
-      </c>
-      <c r="C20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="B20" s="1">
+        <v>115</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="F20" s="2">
+        <v>51750</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1825,45 +1825,45 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21">
-        <v>115</v>
-      </c>
-      <c r="C21" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="1">
-        <v>63000</v>
-      </c>
-      <c r="G21" t="s">
-        <v>9</v>
+      <c r="B21" s="1">
+        <v>115</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" s="3">
+        <v>47687</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22">
-        <v>115</v>
-      </c>
-      <c r="C22" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="B22" s="1">
+        <v>115</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F22" s="1">
-        <v>40000</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="F22" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1871,22 +1871,22 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23">
-        <v>115</v>
-      </c>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="1">
-        <v>70000</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="B23" s="1">
+        <v>115</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1894,22 +1894,22 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24">
-        <v>115</v>
-      </c>
-      <c r="C24" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="1">
-        <v>56000</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="B24" s="1">
+        <v>115</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="2">
+        <v>17000</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25">
-        <v>115</v>
-      </c>
-      <c r="C25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="B25" s="1">
+        <v>115</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="F25" s="2">
+        <v>60000</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1940,22 +1940,22 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26">
-        <v>115</v>
-      </c>
-      <c r="C26" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="B26" s="1">
+        <v>115</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="1">
-        <v>63000</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="F26" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1963,160 +1963,158 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27">
-        <v>115</v>
-      </c>
-      <c r="C27" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B27" s="1">
+        <v>115</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28">
-        <v>115</v>
-      </c>
-      <c r="C28" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" t="s">
-        <v>12</v>
+      <c r="B28" s="1">
+        <v>115</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="F28" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G28" t="s">
-        <v>9</v>
+        <v>140000</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29">
-        <v>115</v>
-      </c>
-      <c r="C29" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="B29" s="1">
+        <v>115</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="1">
-        <v>51000</v>
-      </c>
-      <c r="G29" t="s">
-        <v>9</v>
+      <c r="E29" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="3">
+        <v>28884</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30">
-        <v>115</v>
-      </c>
-      <c r="C30" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="1">
-        <v>20368</v>
-      </c>
-      <c r="G30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B30" s="1">
+        <v>115</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31">
-        <v>115</v>
-      </c>
-      <c r="C31" t="s">
-        <v>39</v>
-      </c>
-      <c r="D31" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" t="s">
-        <v>22</v>
+      <c r="B31" s="1">
+        <v>115</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="F31" s="1">
-        <v>45000</v>
-      </c>
-      <c r="G31" t="s">
-        <v>9</v>
+        <v>150000</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32">
-        <v>115</v>
-      </c>
-      <c r="C32" t="s">
-        <v>40</v>
-      </c>
-      <c r="D32" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="1">
-        <v>2682</v>
-      </c>
-      <c r="G32" t="s">
-        <v>9</v>
+      <c r="B32" s="1">
+        <v>115</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="3">
+        <v>11185</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33">
-        <v>115</v>
-      </c>
-      <c r="C33" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="B33" s="1">
+        <v>115</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="1">
-        <v>51000</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="F33" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2124,22 +2122,22 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34">
-        <v>115</v>
-      </c>
-      <c r="C34" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" t="s">
-        <v>41</v>
-      </c>
-      <c r="E34" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="1">
-        <v>16788</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="B34" s="1">
+        <v>115</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2147,22 +2145,22 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35">
-        <v>115</v>
-      </c>
-      <c r="C35" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" t="s">
-        <v>41</v>
-      </c>
-      <c r="E35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="1">
-        <v>12800</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="B35" s="1">
+        <v>115</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2170,22 +2168,22 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36">
-        <v>115</v>
-      </c>
-      <c r="C36" t="s">
-        <v>43</v>
-      </c>
-      <c r="D36" t="s">
-        <v>17</v>
-      </c>
-      <c r="E36" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="1">
-        <v>52000</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="B36" s="1">
+        <v>115</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="2">
+        <v>70000</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2193,22 +2191,22 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37">
-        <v>115</v>
-      </c>
-      <c r="C37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="1">
-        <v>42500</v>
-      </c>
-      <c r="G37" t="s">
+      <c r="B37" s="1">
+        <v>115</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="2">
+        <v>56000</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2216,45 +2214,45 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38">
-        <v>115</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="1">
-        <v>70000</v>
-      </c>
-      <c r="G38" t="s">
-        <v>9</v>
+      <c r="B38" s="1">
+        <v>115</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F38" s="3">
+        <v>39355</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39">
-        <v>115</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="B39" s="1">
+        <v>115</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="2">
         <v>59500</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2262,91 +2260,91 @@
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40">
-        <v>115</v>
-      </c>
-      <c r="C40" t="s">
-        <v>45</v>
-      </c>
-      <c r="D40" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="B40" s="1">
+        <v>115</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F40" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G40" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F40" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41">
-        <v>115</v>
-      </c>
-      <c r="C41" t="s">
-        <v>46</v>
-      </c>
-      <c r="D41" t="s">
-        <v>47</v>
-      </c>
-      <c r="E41" t="s">
-        <v>22</v>
+      <c r="B41" s="1">
+        <v>115</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="F41" s="1">
-        <v>44118</v>
-      </c>
-      <c r="G41" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+        <v>106530</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42">
-        <v>115</v>
-      </c>
-      <c r="C42" t="s">
-        <v>48</v>
-      </c>
-      <c r="D42" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
+      <c r="B42" s="1">
+        <v>115</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="F42" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G42" t="s">
-        <v>9</v>
+        <v>117750</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43">
-        <v>115</v>
-      </c>
-      <c r="C43" t="s">
-        <v>49</v>
-      </c>
-      <c r="D43" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="B43" s="1">
+        <v>115</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="1">
-        <v>52500</v>
-      </c>
-      <c r="G43" t="s">
+      <c r="F43" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2354,183 +2352,183 @@
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44">
-        <v>115</v>
-      </c>
-      <c r="C44" t="s">
-        <v>50</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="B44" s="1">
+        <v>115</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="1">
-        <v>63000</v>
-      </c>
-      <c r="G44" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E44" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F44" s="3">
+        <v>23014</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45">
-        <v>115</v>
-      </c>
-      <c r="C45" t="s">
-        <v>51</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="B45" s="1">
+        <v>115</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E45" t="s">
-        <v>22</v>
+      <c r="E45" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="F45" s="1">
-        <v>31500</v>
-      </c>
-      <c r="G45" t="s">
-        <v>9</v>
+        <v>300000</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46">
-        <v>115</v>
-      </c>
-      <c r="C46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46" t="s">
-        <v>22</v>
-      </c>
-      <c r="F46" s="1">
-        <v>42500</v>
-      </c>
-      <c r="G46" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B46" s="1">
+        <v>115</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47">
-        <v>115</v>
-      </c>
-      <c r="C47" t="s">
-        <v>53</v>
-      </c>
-      <c r="D47" t="s">
-        <v>30</v>
-      </c>
-      <c r="E47" t="s">
-        <v>22</v>
+      <c r="B47" s="1">
+        <v>115</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="F47" s="1">
-        <v>29250</v>
-      </c>
-      <c r="G47" t="s">
-        <v>9</v>
+        <v>255000</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48">
-        <v>115</v>
-      </c>
-      <c r="C48" t="s">
-        <v>54</v>
-      </c>
-      <c r="D48" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F48" s="1">
-        <v>41384</v>
-      </c>
-      <c r="G48" t="s">
-        <v>9</v>
+      <c r="B48" s="1">
+        <v>115</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F48" s="3">
+        <v>8285</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49">
-        <v>115</v>
-      </c>
-      <c r="C49" t="s">
-        <v>55</v>
-      </c>
-      <c r="D49" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="B49" s="1">
+        <v>115</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="1">
-        <v>56000</v>
-      </c>
-      <c r="G49" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F49" s="2">
+        <v>51000</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50">
-        <v>115</v>
-      </c>
-      <c r="C50" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" t="s">
-        <v>21</v>
-      </c>
-      <c r="E50" t="s">
-        <v>22</v>
+      <c r="B50" s="1">
+        <v>115</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="F50" s="1">
-        <v>42500</v>
-      </c>
-      <c r="G50" t="s">
-        <v>9</v>
+        <v>250000</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51">
-        <v>115</v>
-      </c>
-      <c r="C51" t="s">
-        <v>57</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="B51" s="1">
+        <v>115</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F51" s="1">
-        <v>41770</v>
-      </c>
-      <c r="G51" t="s">
+      <c r="F51" s="2">
+        <v>20368</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2538,22 +2536,22 @@
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52">
-        <v>115</v>
-      </c>
-      <c r="C52" t="s">
-        <v>58</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="B52" s="1">
+        <v>115</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" s="1">
+      <c r="E52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F52" s="2">
         <v>45000</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G52" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2561,22 +2559,22 @@
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53">
-        <v>115</v>
-      </c>
-      <c r="C53" t="s">
-        <v>59</v>
-      </c>
-      <c r="D53" t="s">
-        <v>61</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" s="1">
-        <v>59500</v>
-      </c>
-      <c r="G53" t="s">
+      <c r="B53" s="1">
+        <v>115</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F53" s="2">
+        <v>2682</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2584,22 +2582,22 @@
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54">
-        <v>115</v>
-      </c>
-      <c r="C54" t="s">
-        <v>60</v>
-      </c>
-      <c r="D54" t="s">
-        <v>61</v>
-      </c>
-      <c r="E54" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" s="1">
-        <v>63000</v>
-      </c>
-      <c r="G54" t="s">
+      <c r="B54" s="1">
+        <v>115</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" s="2">
+        <v>51000</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2607,802 +2605,817 @@
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55">
-        <v>115</v>
-      </c>
-      <c r="C55" t="s">
-        <v>62</v>
-      </c>
-      <c r="D55" t="s">
-        <v>64</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G55" t="s">
-        <v>68</v>
+      <c r="B55" s="1">
+        <v>115</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F55" s="2">
+        <v>16788</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56">
-        <v>115</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>67</v>
+      <c r="B56" s="1">
+        <v>115</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="2">
+        <v>12800</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57">
-        <v>115</v>
-      </c>
-      <c r="C57" t="s">
-        <v>75</v>
-      </c>
-      <c r="D57" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" s="5" t="s">
+      <c r="B57" s="1">
+        <v>115</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E57" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F57">
-        <v>300000</v>
-      </c>
-      <c r="G57" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="F57" s="1">
+        <v>143300</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58">
-        <v>115</v>
-      </c>
-      <c r="C58" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F58">
-        <v>140000</v>
-      </c>
-      <c r="G58" t="s">
-        <v>86</v>
+      <c r="B58" s="1">
+        <v>115</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F58" s="3">
+        <v>34568</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59">
-        <v>115</v>
-      </c>
-      <c r="C59" t="s">
-        <v>37</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="B59" s="1">
+        <v>115</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="E59" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F59">
-        <v>250000</v>
-      </c>
-      <c r="G59" t="s">
+      <c r="F59" s="1">
+        <v>300000</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60">
-        <v>115</v>
-      </c>
-      <c r="C60" t="s">
-        <v>76</v>
-      </c>
-      <c r="D60" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F60">
-        <v>95912</v>
-      </c>
-      <c r="G60" t="s">
-        <v>86</v>
+      <c r="B60" s="1">
+        <v>115</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="2">
+        <v>52000</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61">
-        <v>115</v>
-      </c>
-      <c r="C61" t="s">
-        <v>15</v>
-      </c>
-      <c r="D61" t="s">
-        <v>24</v>
-      </c>
-      <c r="E61" s="5" t="s">
+      <c r="B61" s="1">
+        <v>115</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F61">
-        <v>128075</v>
-      </c>
-      <c r="G61" t="s">
+      <c r="F61" s="1">
+        <v>210000</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62">
-        <v>115</v>
-      </c>
-      <c r="C62" t="s">
-        <v>77</v>
-      </c>
-      <c r="D62" t="s">
-        <v>24</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F62">
-        <v>300000</v>
-      </c>
-      <c r="G62" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="B62" s="1">
+        <v>115</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F62" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63">
-        <v>115</v>
-      </c>
-      <c r="C63" t="s">
-        <v>29</v>
-      </c>
-      <c r="D63" t="s">
-        <v>80</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F63">
-        <v>150000</v>
-      </c>
-      <c r="G63" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="B63" s="1">
+        <v>115</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="2">
+        <v>70000</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64">
-        <v>115</v>
-      </c>
-      <c r="C64" t="s">
-        <v>78</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F64">
-        <v>117750</v>
-      </c>
-      <c r="G64" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="B64" s="1">
+        <v>115</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65">
-        <v>115</v>
-      </c>
-      <c r="C65" t="s">
-        <v>70</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F65">
-        <v>143300</v>
-      </c>
-      <c r="G65" t="s">
-        <v>86</v>
+      <c r="B65" s="1">
+        <v>115</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66">
-        <v>115</v>
-      </c>
-      <c r="C66" t="s">
-        <v>16</v>
-      </c>
-      <c r="D66" s="2" t="s">
+      <c r="B66" s="1">
+        <v>115</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D66" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="E66" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F66">
-        <v>165000</v>
-      </c>
-      <c r="G66" t="s">
+      <c r="F66" s="1">
+        <v>200000</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67">
-        <v>115</v>
-      </c>
-      <c r="C67" t="s">
-        <v>36</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F67">
-        <v>255000</v>
-      </c>
-      <c r="G67" t="s">
-        <v>86</v>
+      <c r="B67" s="1">
+        <v>115</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F67" s="2">
+        <v>44118</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68">
-        <v>115</v>
-      </c>
-      <c r="C68" t="s">
-        <v>43</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E68" s="5" t="s">
+      <c r="B68" s="1">
+        <v>115</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E68" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F68">
-        <v>210000</v>
-      </c>
-      <c r="G68" t="s">
+      <c r="F68" s="1">
+        <v>217500</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69">
-        <v>115</v>
-      </c>
-      <c r="C69" t="s">
-        <v>45</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F69">
-        <v>200000</v>
-      </c>
-      <c r="G69" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="B69" s="1">
+        <v>115</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70">
-        <v>115</v>
-      </c>
-      <c r="C70" t="s">
-        <v>34</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F70">
-        <v>106530</v>
-      </c>
-      <c r="G70" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="B70" s="1">
+        <v>115</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71">
-        <v>115</v>
-      </c>
-      <c r="C71" t="s">
-        <v>46</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F71">
-        <v>217500</v>
-      </c>
-      <c r="G71" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="B71" s="1">
+        <v>115</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F71" s="2">
+        <v>52500</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72">
-        <v>115</v>
-      </c>
-      <c r="C72" t="s">
-        <v>79</v>
-      </c>
-      <c r="D72" t="s">
-        <v>41</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F72">
-        <v>28500</v>
-      </c>
-      <c r="G72" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="B72" s="1">
+        <v>115</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F72" s="3">
+        <v>52776</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73">
-        <v>115</v>
-      </c>
-      <c r="C73" t="s">
-        <v>59</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F73">
-        <v>221000</v>
-      </c>
-      <c r="G73" t="s">
-        <v>86</v>
+      <c r="B73" s="1">
+        <v>115</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F73" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>72</v>
-      </c>
-      <c r="B74" s="6">
-        <v>115</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D74" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B74" s="1">
+        <v>115</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E74" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F74" s="7">
-        <v>28884</v>
-      </c>
-      <c r="G74" t="s">
-        <v>88</v>
+      <c r="E74" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F74" s="2">
+        <v>31500</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>72</v>
-      </c>
-      <c r="B75" s="6">
-        <v>115</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D75" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B75" s="1">
+        <v>115</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F75" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" s="1">
+        <v>115</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F75" s="7">
-        <v>23014</v>
-      </c>
-      <c r="G75" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A76">
-        <v>72</v>
-      </c>
-      <c r="B76" s="6">
-        <v>115</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F76" s="7">
-        <v>39125</v>
-      </c>
-      <c r="G76" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E76" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F76" s="1">
+        <v>95912</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>72</v>
-      </c>
-      <c r="B77" s="6">
-        <v>115</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F77" s="7">
-        <v>43084</v>
-      </c>
-      <c r="G77" t="s">
-        <v>88</v>
+        <v>76</v>
+      </c>
+      <c r="B77" s="1">
+        <v>115</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F77" s="1">
+        <v>28500</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>72</v>
-      </c>
-      <c r="B78" s="6">
-        <v>115</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F78" s="7">
-        <v>62600</v>
-      </c>
-      <c r="G78" t="s">
-        <v>88</v>
+        <v>77</v>
+      </c>
+      <c r="B78" s="1">
+        <v>115</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F78" s="2">
+        <v>29250</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>72</v>
-      </c>
-      <c r="B79" s="6">
-        <v>115</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F79" s="7">
-        <v>47687</v>
-      </c>
-      <c r="G79" t="s">
-        <v>88</v>
+        <v>78</v>
+      </c>
+      <c r="B79" s="1">
+        <v>115</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F79" s="2">
+        <v>41384</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>72</v>
-      </c>
-      <c r="B80" s="6">
-        <v>115</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D80" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80" s="1">
+        <v>115</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E80" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F80" s="7">
-        <v>39355</v>
-      </c>
-      <c r="G80" t="s">
-        <v>88</v>
+      <c r="E80" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" s="2">
+        <v>56000</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>72</v>
-      </c>
-      <c r="B81" s="6">
-        <v>115</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D81" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1">
+        <v>115</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E81" s="6" t="s">
+      <c r="E81" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F81" s="7">
-        <v>34568</v>
-      </c>
-      <c r="G81" t="s">
+      <c r="F81" s="3">
+        <v>48284</v>
+      </c>
+      <c r="G81" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>72</v>
-      </c>
-      <c r="B82" s="6">
-        <v>115</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F82" s="7">
-        <v>52776</v>
-      </c>
-      <c r="G82" t="s">
-        <v>88</v>
+        <v>81</v>
+      </c>
+      <c r="B82" s="1">
+        <v>115</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F82" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>72</v>
-      </c>
-      <c r="B83" s="6">
-        <v>115</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F83" s="7">
-        <v>48284</v>
-      </c>
-      <c r="G83" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="B83" s="1">
+        <v>115</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F83" s="2">
+        <v>41770</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>72</v>
-      </c>
-      <c r="B84" s="6">
-        <v>115</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F84" s="7">
-        <v>8285</v>
-      </c>
-      <c r="G84" t="s">
-        <v>88</v>
+        <v>83</v>
+      </c>
+      <c r="B84" s="1">
+        <v>115</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F84" s="2">
+        <v>45000</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>72</v>
-      </c>
-      <c r="B85" s="6">
-        <v>115</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E85" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1">
+        <v>115</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F85" s="7">
-        <v>18412</v>
-      </c>
-      <c r="G85" t="s">
+      <c r="F85" s="3">
+        <v>39125</v>
+      </c>
+      <c r="G85" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>72</v>
-      </c>
-      <c r="B86" s="6">
-        <v>115</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F86" s="7">
-        <v>16571</v>
-      </c>
-      <c r="G86" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1">
+        <v>115</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>72</v>
-      </c>
-      <c r="B87" s="6">
-        <v>115</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F87" s="7">
-        <v>8285</v>
-      </c>
-      <c r="G87" t="s">
-        <v>88</v>
+        <v>86</v>
+      </c>
+      <c r="B87" s="1">
+        <v>115</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F87" s="1">
+        <v>221000</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>72</v>
-      </c>
-      <c r="B88" s="6">
-        <v>115</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D88" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1">
+        <v>115</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E88" s="6" t="s">
+      <c r="E88" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F88" s="7">
-        <v>11185</v>
-      </c>
-      <c r="G88" t="s">
+      <c r="F88" s="3">
+        <v>26283</v>
+      </c>
+      <c r="G88" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>72</v>
-      </c>
-      <c r="B89" s="6">
-        <v>115</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D89" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1">
+        <v>115</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E89" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F89" s="7">
-        <v>26283</v>
-      </c>
-      <c r="G89" t="s">
-        <v>88</v>
-      </c>
+      <c r="E89" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F89" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G89">
+    <sortCondition ref="C2:C89"/>
+  </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B4382A-D6E8-45F9-A82D-077D623B8625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33758DB-F1BB-4F75-B775-3C829A4482D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="93">
   <si>
     <t>序號</t>
   </si>
@@ -330,6 +330,70 @@
   <si>
     <t>115年3月17日教學發展委員會會議通過</t>
   </si>
+  <si>
+    <t>李碧霞</t>
+  </si>
+  <si>
+    <t>視光學科</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>校務研究</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>114</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>日校務研究推動委員會會議通過</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -338,7 +402,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -535,6 +599,32 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="33">
@@ -968,7 +1058,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -992,6 +1082,21 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1350,7 +1455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}">
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="4.75" bestFit="1" customWidth="1"/>
@@ -1805,20 +1910,20 @@
       <c r="B20" s="1">
         <v>115</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="2">
-        <v>51750</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>9</v>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" s="10">
+        <v>45000</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -1835,13 +1940,13 @@
         <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F21" s="3">
-        <v>47687</v>
+        <v>8</v>
+      </c>
+      <c r="F21" s="2">
+        <v>51750</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -1852,19 +1957,19 @@
         <v>115</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="2">
-        <v>42500</v>
+        <v>87</v>
+      </c>
+      <c r="F22" s="3">
+        <v>47687</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -1881,10 +1986,10 @@
         <v>17</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F23" s="2">
-        <v>63000</v>
+        <v>42500</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>9</v>
@@ -1898,16 +2003,16 @@
         <v>115</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F24" s="2">
-        <v>17000</v>
+        <v>63000</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>9</v>
@@ -1927,10 +2032,10 @@
         <v>21</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F25" s="2">
-        <v>60000</v>
+        <v>17000</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>9</v>
@@ -1944,16 +2049,16 @@
         <v>115</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F26" s="2">
-        <v>59500</v>
+        <v>60000</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>9</v>
@@ -1966,21 +2071,23 @@
       <c r="B27" s="1">
         <v>115</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="C27" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27" s="10">
+        <v>47500</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1988,19 +2095,19 @@
         <v>115</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F28" s="1">
-        <v>140000</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>86</v>
+      <c r="E28" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" s="11">
+        <v>50000</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -2017,13 +2124,13 @@
         <v>24</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F29" s="3">
-        <v>28884</v>
+        <v>8</v>
+      </c>
+      <c r="F29" s="2">
+        <v>59500</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -2033,20 +2140,18 @@
       <c r="B30" s="1">
         <v>115</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>9</v>
+      <c r="C30" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2057,16 +2162,16 @@
         <v>115</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>85</v>
       </c>
       <c r="F31" s="1">
-        <v>150000</v>
+        <v>140000</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>86</v>
@@ -2080,16 +2185,16 @@
         <v>115</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>87</v>
       </c>
       <c r="F32" s="3">
-        <v>11185</v>
+        <v>28884</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>88</v>
@@ -2103,22 +2208,22 @@
         <v>115</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="2">
-        <v>59500</v>
+        <v>63000</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2126,19 +2231,19 @@
         <v>115</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="2">
-        <v>63000</v>
+        <v>80</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" s="1">
+        <v>150000</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -2149,19 +2254,19 @@
         <v>115</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="2">
-        <v>40000</v>
+        <v>87</v>
+      </c>
+      <c r="F35" s="3">
+        <v>11185</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -2172,7 +2277,7 @@
         <v>115</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>24</v>
@@ -2181,7 +2286,7 @@
         <v>8</v>
       </c>
       <c r="F36" s="2">
-        <v>70000</v>
+        <v>59500</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>9</v>
@@ -2195,16 +2300,16 @@
         <v>115</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F37" s="2">
-        <v>56000</v>
+        <v>63000</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>9</v>
@@ -2218,19 +2323,19 @@
         <v>115</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F38" s="3">
-        <v>39355</v>
+        <v>22</v>
+      </c>
+      <c r="F38" s="2">
+        <v>40000</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
@@ -2241,16 +2346,16 @@
         <v>115</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F39" s="2">
-        <v>59500</v>
+        <v>70000</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>9</v>
@@ -2263,23 +2368,23 @@
       <c r="B40" s="1">
         <v>115</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="C40" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F40" s="10">
+        <v>40000</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2287,22 +2392,22 @@
         <v>115</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F41" s="1">
-        <v>106530</v>
+        <v>33</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="2">
+        <v>56000</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2310,19 +2415,19 @@
         <v>115</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F42" s="1">
-        <v>117750</v>
+        <v>33</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F42" s="3">
+        <v>39355</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
@@ -2333,13 +2438,13 @@
         <v>115</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F43" s="2">
         <v>59500</v>
@@ -2356,19 +2461,19 @@
         <v>115</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F44" s="3">
-        <v>23014</v>
+        <v>8</v>
+      </c>
+      <c r="F44" s="2">
+        <v>63000</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2379,22 +2484,22 @@
         <v>115</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>85</v>
       </c>
       <c r="F45" s="1">
-        <v>300000</v>
+        <v>106530</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2402,22 +2507,22 @@
         <v>115</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="2">
-        <v>59500</v>
+        <v>78</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F46" s="1">
+        <v>117750</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2425,19 +2530,19 @@
         <v>115</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F47" s="1">
-        <v>255000</v>
+        <v>35</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="2">
+        <v>59500</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
@@ -2448,22 +2553,22 @@
         <v>115</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>87</v>
       </c>
       <c r="F48" s="3">
-        <v>8285</v>
+        <v>23014</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2471,22 +2576,22 @@
         <v>115</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" s="2">
-        <v>51000</v>
+      <c r="E49" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49" s="1">
+        <v>300000</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2494,22 +2599,22 @@
         <v>115</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F50" s="1">
-        <v>250000</v>
+        <v>17</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="2">
+        <v>59500</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2517,19 +2622,19 @@
         <v>115</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F51" s="2">
-        <v>20368</v>
+        <v>36</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F51" s="1">
+        <v>255000</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -2540,19 +2645,19 @@
         <v>115</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F52" s="2">
-        <v>45000</v>
+        <v>87</v>
+      </c>
+      <c r="F52" s="3">
+        <v>8285</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -2563,22 +2668,22 @@
         <v>115</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F53" s="2">
-        <v>2682</v>
+        <v>51000</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2586,19 +2691,19 @@
         <v>115</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" s="2">
-        <v>51000</v>
+        <v>24</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F54" s="1">
+        <v>250000</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -2609,16 +2714,16 @@
         <v>115</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F55" s="2">
-        <v>16788</v>
+        <v>20368</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>9</v>
@@ -2632,22 +2737,22 @@
         <v>115</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F56" s="2">
-        <v>12800</v>
+        <v>45000</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2655,19 +2760,19 @@
         <v>115</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F57" s="1">
-        <v>143300</v>
+        <v>40</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F57" s="2">
+        <v>2682</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -2678,22 +2783,22 @@
         <v>115</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F58" s="3">
-        <v>34568</v>
+        <v>8</v>
+      </c>
+      <c r="F58" s="2">
+        <v>51000</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2701,19 +2806,19 @@
         <v>115</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F59" s="1">
-        <v>300000</v>
+        <v>41</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F59" s="2">
+        <v>16788</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -2724,16 +2829,16 @@
         <v>115</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F60" s="2">
-        <v>52000</v>
+        <v>12800</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>9</v>
@@ -2747,16 +2852,16 @@
         <v>115</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>85</v>
       </c>
       <c r="F61" s="1">
-        <v>210000</v>
+        <v>143300</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>86</v>
@@ -2770,22 +2875,22 @@
         <v>115</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F62" s="2">
-        <v>42500</v>
+        <v>87</v>
+      </c>
+      <c r="F62" s="3">
+        <v>34568</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2793,19 +2898,19 @@
         <v>115</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" s="2">
-        <v>70000</v>
+        <v>24</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F63" s="1">
+        <v>300000</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -2815,20 +2920,20 @@
       <c r="B64" s="1">
         <v>115</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F64" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>9</v>
+      <c r="C64" t="s">
+        <v>77</v>
+      </c>
+      <c r="D64" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F64" s="10">
+        <v>47500</v>
+      </c>
+      <c r="G64" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
@@ -2839,16 +2944,16 @@
         <v>115</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F65" s="2">
-        <v>59500</v>
+        <v>52000</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>9</v>
@@ -2862,7 +2967,7 @@
         <v>115</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>82</v>
@@ -2871,7 +2976,7 @@
         <v>85</v>
       </c>
       <c r="F66" s="1">
-        <v>200000</v>
+        <v>210000</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>86</v>
@@ -2885,22 +2990,22 @@
         <v>115</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F67" s="2">
-        <v>44118</v>
+        <v>42500</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2908,19 +3013,19 @@
         <v>115</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F68" s="1">
-        <v>217500</v>
+        <v>44</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="2">
+        <v>70000</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
@@ -2931,13 +3036,13 @@
         <v>115</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F69" s="2">
         <v>59500</v>
@@ -2954,20 +3059,22 @@
         <v>115</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F70" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F70" s="2">
+        <v>59500</v>
+      </c>
       <c r="G70" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2975,19 +3082,19 @@
         <v>115</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F71" s="2">
-        <v>52500</v>
+        <v>45</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F71" s="1">
+        <v>200000</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
@@ -2998,22 +3105,22 @@
         <v>115</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F72" s="3">
-        <v>52776</v>
+        <v>22</v>
+      </c>
+      <c r="F72" s="2">
+        <v>44118</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3021,19 +3128,19 @@
         <v>115</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" s="2">
-        <v>63000</v>
+        <v>46</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F73" s="1">
+        <v>217500</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
@@ -3044,16 +3151,16 @@
         <v>115</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F74" s="2">
-        <v>31500</v>
+        <v>59500</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>9</v>
@@ -3067,22 +3174,20 @@
         <v>115</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F75" s="2">
-        <v>42500</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F75" s="1"/>
       <c r="G75" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3090,22 +3195,22 @@
         <v>115</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F76" s="1">
-        <v>95912</v>
+        <v>14</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="2">
+        <v>52500</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3113,19 +3218,19 @@
         <v>115</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F77" s="1">
-        <v>28500</v>
+        <v>14</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F77" s="3">
+        <v>52776</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
@@ -3136,16 +3241,16 @@
         <v>115</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F78" s="2">
-        <v>29250</v>
+        <v>63000</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>9</v>
@@ -3158,20 +3263,20 @@
       <c r="B79" s="1">
         <v>115</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D79" s="1" t="s">
+      <c r="C79" t="s">
+        <v>50</v>
+      </c>
+      <c r="D79" t="s">
         <v>24</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F79" s="2">
-        <v>41384</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>9</v>
+      <c r="E79" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F79" s="10">
+        <v>41616</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
@@ -3182,16 +3287,16 @@
         <v>115</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F80" s="2">
-        <v>56000</v>
+        <v>31500</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>9</v>
@@ -3205,22 +3310,22 @@
         <v>115</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F81" s="3">
-        <v>48284</v>
+        <v>22</v>
+      </c>
+      <c r="F81" s="2">
+        <v>42500</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3228,22 +3333,22 @@
         <v>115</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F82" s="2">
-        <v>42500</v>
+        <v>24</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F82" s="1">
+        <v>95912</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3251,19 +3356,19 @@
         <v>115</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F83" s="2">
-        <v>41770</v>
+        <v>41</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F83" s="1">
+        <v>28500</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
@@ -3274,16 +3379,16 @@
         <v>115</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F84" s="2">
-        <v>45000</v>
+        <v>29250</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>9</v>
@@ -3297,19 +3402,19 @@
         <v>115</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F85" s="3">
-        <v>39125</v>
+        <v>22</v>
+      </c>
+      <c r="F85" s="2">
+        <v>41384</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
@@ -3320,22 +3425,22 @@
         <v>115</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F86" s="2">
-        <v>59500</v>
+        <v>56000</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3343,19 +3448,19 @@
         <v>115</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F87" s="1">
-        <v>221000</v>
+        <v>55</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F87" s="3">
+        <v>48284</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
@@ -3366,19 +3471,19 @@
         <v>115</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F88" s="3">
-        <v>26283</v>
+        <v>22</v>
+      </c>
+      <c r="F88" s="2">
+        <v>42500</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
@@ -3389,32 +3494,185 @@
         <v>115</v>
       </c>
       <c r="C89" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F89" s="2">
+        <v>41770</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" s="1">
+        <v>115</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F90" s="2">
+        <v>45000</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1">
+        <v>115</v>
+      </c>
+      <c r="C91" t="s">
+        <v>58</v>
+      </c>
+      <c r="D91" t="s">
+        <v>90</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F91" s="10">
+        <v>40000</v>
+      </c>
+      <c r="G91" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" s="1">
+        <v>115</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F92" s="3">
+        <v>39125</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1">
+        <v>115</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" s="1">
+        <v>115</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F94" s="1">
+        <v>221000</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" s="1">
+        <v>115</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F95" s="3">
+        <v>26283</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" s="1">
+        <v>115</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F96" s="2">
         <v>63000</v>
       </c>
-      <c r="G89" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
+      <c r="G96" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G89">
-    <sortCondition ref="C2:C89"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:G96">
+    <sortCondition ref="C2:C96"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33758DB-F1BB-4F75-B775-3C829A4482D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A570BD-D77F-4AB3-BBFE-A61ECD197E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="94">
   <si>
     <t>序號</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>核定經費</t>
-  </si>
-  <si>
-    <t>備註</t>
   </si>
   <si>
     <t>王珮藍</t>
@@ -393,6 +390,14 @@
       </rPr>
       <t>日校務研究推動委員會會議通過</t>
     </r>
+  </si>
+  <si>
+    <t>會議通過(核定)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1455,7 +1460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}">
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="4.75" bestFit="1" customWidth="1"/>
@@ -1466,7 +1471,7 @@
     <col min="7" max="7" width="33.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1485,11 +1490,14 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1497,22 +1505,22 @@
         <v>115</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F2" s="2">
         <v>59500</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1520,22 +1528,22 @@
         <v>115</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F3" s="2">
         <v>52500</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1543,22 +1551,22 @@
         <v>115</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
         <v>56000</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1566,22 +1574,22 @@
         <v>115</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
         <v>40000</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1589,22 +1597,22 @@
         <v>115</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F6" s="3">
         <v>43084</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1612,22 +1620,22 @@
         <v>115</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2">
         <v>51931</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1635,22 +1643,22 @@
         <v>115</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F8" s="1">
         <v>128075</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1658,22 +1666,22 @@
         <v>115</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="2">
         <v>63000</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1681,22 +1689,22 @@
         <v>115</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F10" s="1">
         <v>165000</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1704,22 +1712,22 @@
         <v>115</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F11" s="3">
         <v>8285</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1727,22 +1735,22 @@
         <v>115</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" s="2">
         <v>48000</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1750,22 +1758,22 @@
         <v>115</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F13" s="3">
         <v>62600</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1773,22 +1781,22 @@
         <v>115</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F14" s="2">
         <v>56000</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1796,22 +1804,22 @@
         <v>115</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F15" s="3">
         <v>18412</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1819,19 +1827,19 @@
         <v>115</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F16" s="3">
         <v>16571</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -1842,19 +1850,19 @@
         <v>115</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="F17" s="2">
         <v>31500</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -1865,19 +1873,19 @@
         <v>115</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" s="2">
         <v>59500</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -1888,19 +1896,19 @@
         <v>115</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="E19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F19" s="2">
         <v>20564</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1911,19 +1919,19 @@
         <v>115</v>
       </c>
       <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" t="s">
         <v>23</v>
       </c>
-      <c r="D20" t="s">
-        <v>24</v>
-      </c>
       <c r="E20" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F20" s="10">
         <v>45000</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -1934,19 +1942,19 @@
         <v>115</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F21" s="2">
         <v>51750</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -1957,19 +1965,19 @@
         <v>115</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F22" s="3">
         <v>47687</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -1980,19 +1988,19 @@
         <v>115</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23" s="2">
         <v>42500</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -2003,19 +2011,19 @@
         <v>115</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F24" s="2">
         <v>63000</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -2026,19 +2034,19 @@
         <v>115</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="F25" s="2">
         <v>17000</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -2049,19 +2057,19 @@
         <v>115</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F26" s="2">
         <v>60000</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -2072,19 +2080,19 @@
         <v>115</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="F27" s="10">
         <v>47500</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -2095,19 +2103,19 @@
         <v>115</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F28" s="11">
         <v>50000</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -2118,19 +2126,19 @@
         <v>115</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" s="2">
         <v>59500</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -2141,17 +2149,17 @@
         <v>115</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D30" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2162,19 +2170,19 @@
         <v>115</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F31" s="1">
         <v>140000</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
@@ -2185,19 +2193,19 @@
         <v>115</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F32" s="3">
         <v>28884</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -2208,19 +2216,19 @@
         <v>115</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F33" s="2">
         <v>63000</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2231,19 +2239,19 @@
         <v>115</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F34" s="1">
         <v>150000</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -2254,19 +2262,19 @@
         <v>115</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F35" s="3">
         <v>11185</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -2277,19 +2285,19 @@
         <v>115</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F36" s="2">
         <v>59500</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -2300,19 +2308,19 @@
         <v>115</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F37" s="2">
         <v>63000</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
@@ -2323,19 +2331,19 @@
         <v>115</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F38" s="2">
         <v>40000</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
@@ -2346,19 +2354,19 @@
         <v>115</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F39" s="2">
         <v>70000</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
@@ -2369,19 +2377,19 @@
         <v>115</v>
       </c>
       <c r="C40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F40" s="10">
         <v>40000</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
@@ -2392,19 +2400,19 @@
         <v>115</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F41" s="2">
         <v>56000</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
@@ -2415,19 +2423,19 @@
         <v>115</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F42" s="3">
         <v>39355</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
@@ -2438,19 +2446,19 @@
         <v>115</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F43" s="2">
         <v>59500</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
@@ -2461,19 +2469,19 @@
         <v>115</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F44" s="2">
         <v>63000</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2484,19 +2492,19 @@
         <v>115</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F45" s="1">
         <v>106530</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2507,19 +2515,19 @@
         <v>115</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F46" s="1">
         <v>117750</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
@@ -2530,19 +2538,19 @@
         <v>115</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F47" s="2">
         <v>59500</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
@@ -2553,19 +2561,19 @@
         <v>115</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F48" s="3">
         <v>23014</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2576,19 +2584,19 @@
         <v>115</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F49" s="1">
         <v>300000</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -2599,19 +2607,19 @@
         <v>115</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F50" s="2">
         <v>59500</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2622,19 +2630,19 @@
         <v>115</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F51" s="1">
         <v>255000</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -2645,19 +2653,19 @@
         <v>115</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F52" s="3">
         <v>8285</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -2668,19 +2676,19 @@
         <v>115</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F53" s="2">
         <v>51000</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2691,19 +2699,19 @@
         <v>115</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F54" s="1">
         <v>250000</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -2714,19 +2722,19 @@
         <v>115</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F55" s="2">
         <v>20368</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -2737,19 +2745,19 @@
         <v>115</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="F56" s="2">
         <v>45000</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -2760,19 +2768,19 @@
         <v>115</v>
       </c>
       <c r="C57" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="E57" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F57" s="2">
         <v>2682</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -2783,19 +2791,19 @@
         <v>115</v>
       </c>
       <c r="C58" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F58" s="2">
         <v>51000</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
@@ -2806,19 +2814,19 @@
         <v>115</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F59" s="2">
         <v>16788</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -2829,19 +2837,19 @@
         <v>115</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F60" s="2">
         <v>12800</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2852,19 +2860,19 @@
         <v>115</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F61" s="1">
         <v>143300</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -2875,19 +2883,19 @@
         <v>115</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F62" s="3">
         <v>34568</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2898,19 +2906,19 @@
         <v>115</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F63" s="1">
         <v>300000</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -2921,19 +2929,19 @@
         <v>115</v>
       </c>
       <c r="C64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F64" s="10">
         <v>47500</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
@@ -2944,19 +2952,19 @@
         <v>115</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F65" s="2">
         <v>52000</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2967,19 +2975,19 @@
         <v>115</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F66" s="1">
         <v>210000</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
@@ -2990,19 +2998,19 @@
         <v>115</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="F67" s="2">
         <v>42500</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
@@ -3013,19 +3021,19 @@
         <v>115</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F68" s="2">
         <v>70000</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
@@ -3036,19 +3044,19 @@
         <v>115</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F69" s="2">
         <v>59500</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
@@ -3059,19 +3067,19 @@
         <v>115</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F70" s="2">
         <v>59500</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -3082,19 +3090,19 @@
         <v>115</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F71" s="1">
         <v>200000</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
@@ -3105,19 +3113,19 @@
         <v>115</v>
       </c>
       <c r="C72" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E72" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F72" s="2">
         <v>44118</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -3128,19 +3136,19 @@
         <v>115</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F73" s="1">
         <v>217500</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
@@ -3151,19 +3159,19 @@
         <v>115</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F74" s="2">
         <v>59500</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
@@ -3174,17 +3182,17 @@
         <v>115</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
@@ -3195,19 +3203,19 @@
         <v>115</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F76" s="2">
         <v>52500</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
@@ -3218,19 +3226,19 @@
         <v>115</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F77" s="3">
         <v>52776</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
@@ -3241,19 +3249,19 @@
         <v>115</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F78" s="2">
         <v>63000</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
@@ -3264,19 +3272,19 @@
         <v>115</v>
       </c>
       <c r="C79" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F79" s="10">
         <v>41616</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
@@ -3287,19 +3295,19 @@
         <v>115</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F80" s="2">
         <v>31500</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
@@ -3310,19 +3318,19 @@
         <v>115</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="F81" s="2">
         <v>42500</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -3333,19 +3341,19 @@
         <v>115</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F82" s="1">
         <v>95912</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -3356,19 +3364,19 @@
         <v>115</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F83" s="1">
         <v>28500</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
@@ -3379,19 +3387,19 @@
         <v>115</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F84" s="2">
         <v>29250</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
@@ -3402,19 +3410,19 @@
         <v>115</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F85" s="2">
         <v>41384</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
@@ -3425,19 +3433,19 @@
         <v>115</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F86" s="2">
         <v>56000</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
@@ -3448,19 +3456,19 @@
         <v>115</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F87" s="3">
         <v>48284</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
@@ -3471,19 +3479,19 @@
         <v>115</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="F88" s="2">
         <v>42500</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
@@ -3494,19 +3502,19 @@
         <v>115</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F89" s="2">
         <v>41770</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
@@ -3517,19 +3525,19 @@
         <v>115</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F90" s="2">
         <v>45000</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
@@ -3540,19 +3548,19 @@
         <v>115</v>
       </c>
       <c r="C91" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D91" t="s">
+        <v>89</v>
+      </c>
+      <c r="E91" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="E91" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="F91" s="10">
         <v>40000</v>
       </c>
       <c r="G91" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
@@ -3563,19 +3571,19 @@
         <v>115</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F92" s="3">
         <v>39125</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
@@ -3586,19 +3594,19 @@
         <v>115</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F93" s="2">
         <v>59500</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -3609,19 +3617,19 @@
         <v>115</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D94" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E94" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>85</v>
       </c>
       <c r="F94" s="1">
         <v>221000</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
@@ -3632,19 +3640,19 @@
         <v>115</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F95" s="3">
         <v>26283</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
@@ -3655,19 +3663,19 @@
         <v>115</v>
       </c>
       <c r="C96" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="E96" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F96" s="2">
         <v>63000</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A570BD-D77F-4AB3-BBFE-A61ECD197E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE4765C3-3151-4D96-AB01-984244A647DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="95">
   <si>
     <t>序號</t>
   </si>
@@ -239,14 +239,6 @@
   </si>
   <si>
     <t>進修</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>(請款額度依學雜費繳費單,上限60000元/學期)114年3月25日校教評會議通過</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>(請款額度依學雜費繳費單,上限60000元/學期)113年6月24日校教評會議通過</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -397,6 +389,18 @@
   </si>
   <si>
     <t>備註</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>(暫顯示為0,請款額度依學雜費繳費單申請,上限60000元/學期)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>113年6月24日校教師評審委員會議通過</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>114年3月25日校教師評審委員會議通過</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1491,10 +1495,10 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -1603,13 +1607,13 @@
         <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F6" s="3">
         <v>43084</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1649,13 +1653,13 @@
         <v>23</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F8" s="1">
         <v>128075</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -1692,16 +1696,16 @@
         <v>15</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F10" s="1">
         <v>165000</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1718,13 +1722,13 @@
         <v>16</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F11" s="3">
         <v>8285</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1764,13 +1768,13 @@
         <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F13" s="3">
         <v>62600</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -1810,13 +1814,13 @@
         <v>16</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F15" s="3">
         <v>18412</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -1827,22 +1831,22 @@
         <v>115</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F16" s="3">
         <v>16571</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1865,7 +1869,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1888,7 +1892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1911,7 +1915,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1925,16 +1929,16 @@
         <v>23</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F20" s="10">
         <v>45000</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1957,7 +1961,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1971,16 +1975,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F22" s="3">
         <v>47687</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2003,7 +2007,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2026,7 +2030,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2049,7 +2053,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2072,7 +2076,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2083,19 +2087,19 @@
         <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F27" s="10">
         <v>47500</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2103,22 +2107,22 @@
         <v>115</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F28" s="11">
         <v>50000</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2141,7 +2145,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2159,10 +2163,13 @@
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+      <c r="H30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2176,16 +2183,16 @@
         <v>23</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F31" s="1">
         <v>140000</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2199,13 +2206,13 @@
         <v>23</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F32" s="3">
         <v>28884</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -2242,16 +2249,16 @@
         <v>28</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F34" s="1">
         <v>150000</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -2262,19 +2269,19 @@
         <v>115</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F35" s="3">
         <v>11185</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -2383,13 +2390,13 @@
         <v>23</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F40" s="10">
         <v>40000</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
@@ -2429,13 +2436,13 @@
         <v>13</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F42" s="3">
         <v>39355</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
@@ -2495,16 +2502,16 @@
         <v>33</v>
       </c>
       <c r="D45" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="F45" s="1">
         <v>106530</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2515,19 +2522,19 @@
         <v>115</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F46" s="1">
         <v>117750</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
@@ -2561,19 +2568,19 @@
         <v>115</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F48" s="3">
         <v>23014</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2584,19 +2591,19 @@
         <v>115</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F49" s="1">
         <v>300000</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -2633,16 +2640,16 @@
         <v>35</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F51" s="1">
         <v>255000</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -2659,13 +2666,13 @@
         <v>16</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F52" s="3">
         <v>8285</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -2705,13 +2712,13 @@
         <v>23</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F54" s="1">
         <v>250000</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -2860,19 +2867,19 @@
         <v>115</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F61" s="1">
         <v>143300</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -2883,19 +2890,19 @@
         <v>115</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F62" s="3">
         <v>34568</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -2906,19 +2913,19 @@
         <v>115</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F63" s="1">
         <v>300000</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -2929,22 +2936,22 @@
         <v>115</v>
       </c>
       <c r="C64" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D64" t="s">
         <v>23</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F64" s="10">
         <v>47500</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2967,7 +2974,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2978,19 +2985,19 @@
         <v>42</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F66" s="1">
         <v>210000</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3013,7 +3020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3036,7 +3043,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3059,7 +3066,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3082,7 +3089,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3093,19 +3100,19 @@
         <v>44</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F71" s="1">
         <v>200000</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3128,7 +3135,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3142,16 +3149,16 @@
         <v>63</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F73" s="1">
         <v>217500</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3174,7 +3181,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3192,10 +3199,13 @@
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+      <c r="H75" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3218,7 +3228,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3232,16 +3242,16 @@
         <v>13</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F77" s="3">
         <v>52776</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3264,7 +3274,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3278,16 +3288,16 @@
         <v>23</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F79" s="10">
         <v>41616</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3341,19 +3351,19 @@
         <v>115</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F82" s="1">
         <v>95912</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
@@ -3364,19 +3374,19 @@
         <v>115</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>40</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F83" s="1">
         <v>28500</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
@@ -3462,13 +3472,13 @@
         <v>13</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F87" s="3">
         <v>48284</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
@@ -3551,16 +3561,16 @@
         <v>57</v>
       </c>
       <c r="D91" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F91" s="10">
         <v>40000</v>
       </c>
       <c r="G91" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
@@ -3571,19 +3581,19 @@
         <v>115</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F92" s="3">
         <v>39125</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
@@ -3620,16 +3630,16 @@
         <v>58</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F94" s="1">
         <v>221000</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
@@ -3646,13 +3656,13 @@
         <v>60</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F95" s="3">
         <v>26283</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE4765C3-3151-4D96-AB01-984244A647DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D880AC-6D20-4434-B41F-63EED2DAE3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="153">
   <si>
     <t>序號</t>
   </si>
@@ -235,10 +235,6 @@
   </si>
   <si>
     <t>護理科</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>進修</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -402,6 +398,188 @@
   <si>
     <t>114年3月25日校教師評審委員會議通過</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>(請款額度依學雜費繳費單申請,上限60000元/學期)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>進修114-2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>傅雅麟</t>
+  </si>
+  <si>
+    <t>王燕慧</t>
+  </si>
+  <si>
+    <t>侯本昕</t>
+  </si>
+  <si>
+    <t>王金淑</t>
+  </si>
+  <si>
+    <t>鄧慧茹</t>
+  </si>
+  <si>
+    <t>陳秀玲</t>
+  </si>
+  <si>
+    <t>研習_參加國際研討會並發表_差旅費</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>新加坡/Effects of Generative AI Virtual Humans on Nursing Students Communication Skills, Self-Directed Learning, and Self-Efficacy: A Quasi-Experimental Study</t>
+  </si>
+  <si>
+    <t>加拿大/Effectiveness of a nursing simulation course in promoting preoperative care skills</t>
+  </si>
+  <si>
+    <t>新加坡/Stroke Symptom Recognition and Anticipated Coping Behaviors Among Senior Five-Year Nursing Students</t>
+  </si>
+  <si>
+    <t>新加坡/Adolescent Sexual Risk Control and Sexual Health Self-Care: A Mediation Model</t>
+  </si>
+  <si>
+    <t>韓國/Home and school contexts as mechanisms and buffers of socioeconomic gaps in executive function</t>
+  </si>
+  <si>
+    <t>Canada/Mastery Learning Using Past Exam Questions to Enhance Achievement and Self-Directed Learning</t>
+  </si>
+  <si>
+    <t>日本/Developing a Multicultural Story Corner to Foster Cultural Awareness in Early Childhood Education</t>
+  </si>
+  <si>
+    <t>新加坡/Exploring the Learning Effectiveness of Applying NotebookLM in a Nursing Professional Issues Seminar</t>
+  </si>
+  <si>
+    <t>日本/An Analysis of Criminal Disputes in Funeral and Burial Administration through Case Law: A Study of High Court Judgments</t>
+  </si>
+  <si>
+    <t>Austria/Integrating Gamification and Micro-Flipped Teaching into End-of-Life Care Nursing Education</t>
+  </si>
+  <si>
+    <t>奧地利/Embracing the Inner Child: Generative AI–Enabled Visualization and Scenario Simulation for Enhancing Affective Learning in Nursing Human Development</t>
+  </si>
+  <si>
+    <t>Singapore/The mediating role of teacher-child interaction in the association between parent-teacher relationship and preschoolers&amp;#039; executive function</t>
+  </si>
+  <si>
+    <t>日本/Self-Perceived Health Status and Health Behaviors Among Junior Nursing College Students</t>
+  </si>
+  <si>
+    <t>印尼/A Study of Nurses’ Experiences Caring for End-of-Life Residents in Nursing Homes</t>
+  </si>
+  <si>
+    <t>印尼/Enhancing Medical Terminology Instruction through the Use of H5P  Digital Learning Tools</t>
+  </si>
+  <si>
+    <t>中華民國/AI-Supported Wound Care Decision Support for HomeBased and Long-Term Care Services</t>
+  </si>
+  <si>
+    <t>研習_參加國際研討會並發表_報名(註冊)費</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>115年6月22日校教師評審委員會通過</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>115年6月23日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月24日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月25日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月26日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月27日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月28日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月29日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月30日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月31日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月32日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月33日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月34日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月35日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月36日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月37日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月38日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月39日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月40日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月41日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月42日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月43日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月44日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月45日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月46日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月47日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月48日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月49日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月50日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月51日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月52日校教師評審委員會通過</t>
+  </si>
+  <si>
+    <t>115年6月53日校教師評審委員會通過</t>
   </si>
 </sst>
 </file>
@@ -1067,7 +1245,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1105,6 +1283,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1464,7 +1645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}">
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="4.75" bestFit="1" customWidth="1"/>
@@ -1495,10 +1676,10 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -1508,20 +1689,23 @@
       <c r="B2" s="1">
         <v>115</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
+      <c r="C2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2">
+        <v>29000</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="H2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1531,20 +1715,23 @@
       <c r="B3" s="1">
         <v>115</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2">
-        <v>52500</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
+      <c r="C3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3">
+        <v>2000</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="H3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -1555,16 +1742,16 @@
         <v>115</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>56000</v>
+        <v>59500</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>8</v>
@@ -1578,16 +1765,16 @@
         <v>115</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2">
-        <v>40000</v>
+        <v>52500</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>8</v>
@@ -1601,19 +1788,19 @@
         <v>115</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F6" s="3">
-        <v>43084</v>
+        <v>7</v>
+      </c>
+      <c r="F6" s="2">
+        <v>56000</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1624,22 +1811,22 @@
         <v>115</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="2">
-        <v>51931</v>
+        <v>40000</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1647,19 +1834,19 @@
         <v>115</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" s="1">
-        <v>128075</v>
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="3">
+        <v>43084</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -1669,43 +1856,49 @@
       <c r="B9" s="1">
         <v>115</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9">
+        <v>29636</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="1">
         <v>115</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10" s="1">
-        <v>165000</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>83</v>
+      <c r="C10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10">
+        <v>11068</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="H10" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1716,22 +1909,22 @@
         <v>115</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" s="3">
-        <v>8285</v>
+        <v>7</v>
+      </c>
+      <c r="F11" s="2">
+        <v>51931</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1739,19 +1932,19 @@
         <v>115</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="2">
-        <v>48000</v>
+        <v>23</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="1">
+        <v>128075</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -1761,20 +1954,23 @@
       <c r="B13" s="1">
         <v>115</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F13" s="3">
-        <v>62600</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>85</v>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F13">
+        <v>30850</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="H13" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -1784,20 +1980,23 @@
       <c r="B14" s="1">
         <v>115</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="2">
-        <v>56000</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>8</v>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14">
+        <v>12726</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H14" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -1808,22 +2007,22 @@
         <v>115</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F15" s="3">
-        <v>18412</v>
+        <v>11</v>
+      </c>
+      <c r="F15" s="2">
+        <v>63000</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1831,22 +2030,22 @@
         <v>115</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F16" s="3">
-        <v>16571</v>
+        <v>15</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="1">
+        <v>165000</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1854,22 +2053,22 @@
         <v>115</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="2">
-        <v>31500</v>
+        <v>83</v>
+      </c>
+      <c r="F17" s="3">
+        <v>8285</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1877,22 +2076,22 @@
         <v>115</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F18" s="2">
-        <v>59500</v>
+        <v>48000</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1900,45 +2099,45 @@
         <v>115</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" s="2">
-        <v>20564</v>
+        <v>83</v>
+      </c>
+      <c r="F19" s="3">
+        <v>62600</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="1">
         <v>115</v>
       </c>
-      <c r="C20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F20" s="10">
-        <v>45000</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="2">
+        <v>56000</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1946,22 +2145,22 @@
         <v>115</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" s="2">
-        <v>51750</v>
+        <v>83</v>
+      </c>
+      <c r="F21" s="3">
+        <v>18412</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1969,22 +2168,22 @@
         <v>115</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="3">
+        <v>16571</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F22" s="3">
-        <v>47687</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1992,22 +2191,22 @@
         <v>115</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F23" s="2">
-        <v>42500</v>
+        <v>31500</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2015,22 +2214,22 @@
         <v>115</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F24" s="2">
-        <v>63000</v>
+        <v>59500</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2038,68 +2237,68 @@
         <v>115</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F25" s="2">
-        <v>17000</v>
+        <v>20564</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" s="1">
         <v>115</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" s="10">
+        <v>45000</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="1">
         <v>115</v>
       </c>
-      <c r="C27" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" t="s">
-        <v>87</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="10">
-        <v>47500</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="2">
+        <v>51750</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2107,22 +2306,22 @@
         <v>115</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F28" s="11">
-        <v>50000</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" s="3">
+        <v>47687</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2130,46 +2329,45 @@
         <v>115</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F29" s="2">
-        <v>59500</v>
+        <v>42500</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="1">
         <v>115</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="H30" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="C30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2177,22 +2375,22 @@
         <v>115</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F31" s="1">
-        <v>140000</v>
+        <v>20</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="2">
+        <v>17000</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2200,45 +2398,45 @@
         <v>115</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F32" s="3">
-        <v>28884</v>
+        <v>11</v>
+      </c>
+      <c r="F32" s="2">
+        <v>60000</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="1">
         <v>115</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="C33" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" t="s">
+        <v>86</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F33" s="10">
+        <v>47500</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2246,68 +2444,74 @@
         <v>115</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F34" s="1">
-        <v>150000</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F34" s="11">
+        <v>50000</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" s="1">
         <v>115</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F35" s="3">
-        <v>11185</v>
-      </c>
-      <c r="G35" s="1" t="s">
+      <c r="C35" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D35" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F35">
+        <v>30850</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" s="1">
         <v>115</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C36" t="s">
+        <v>85</v>
+      </c>
+      <c r="D36" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F36">
+        <v>9696</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="H36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2315,45 +2519,48 @@
         <v>115</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F37" s="2">
-        <v>63000</v>
+        <v>59500</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" s="1">
         <v>115</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C38" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F38" s="1">
+        <v>32320</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H38" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2361,137 +2568,149 @@
         <v>115</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" s="2">
-        <v>70000</v>
+      <c r="E39" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F39" s="1">
+        <v>140000</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" s="1">
         <v>115</v>
       </c>
-      <c r="C40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F40" s="10">
-        <v>40000</v>
-      </c>
-      <c r="G40" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C40" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F40" s="3">
+        <v>28884</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" s="1">
         <v>115</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" s="2">
-        <v>56000</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C41" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F41">
+        <v>30850</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H41" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" s="1">
         <v>115</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F42" s="3">
-        <v>39355</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C42" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F42">
+        <v>19150</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="H42" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" s="1">
         <v>115</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F43">
+        <v>12936</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="H43" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" s="1">
         <v>115</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="C44" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F44">
+        <v>31462</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="H44" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2499,22 +2718,22 @@
         <v>115</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F45" s="1">
-        <v>106530</v>
+        <v>28</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" s="2">
+        <v>63000</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2522,68 +2741,74 @@
         <v>115</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>78</v>
+        <v>28</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="E46" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F46" s="1">
+        <v>150000</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F46" s="1">
-        <v>117750</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" s="1">
         <v>115</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D47" s="1" t="s">
+      <c r="C47" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" t="s">
         <v>29</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E47" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F47">
+        <v>17789</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="H47" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" s="1">
         <v>115</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F48" s="3">
-        <v>23014</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="C48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F48">
+        <v>8085</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="H48" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2591,22 +2816,22 @@
         <v>115</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F49" s="1">
-        <v>300000</v>
+        <v>60</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F49" s="3">
+        <v>11185</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2614,13 +2839,13 @@
         <v>115</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F50" s="2">
         <v>59500</v>
@@ -2629,7 +2854,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2637,22 +2862,22 @@
         <v>115</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F51" s="1">
-        <v>255000</v>
+        <v>30</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="2">
+        <v>63000</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2660,22 +2885,22 @@
         <v>115</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F52" s="3">
-        <v>8285</v>
+        <v>21</v>
+      </c>
+      <c r="F52" s="2">
+        <v>40000</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2683,7 +2908,7 @@
         <v>115</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>23</v>
@@ -2692,82 +2917,88 @@
         <v>7</v>
       </c>
       <c r="F53" s="2">
-        <v>51000</v>
+        <v>70000</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" s="1">
         <v>115</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F54" s="1">
-        <v>250000</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C54" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F54" s="10">
+        <v>40000</v>
+      </c>
+      <c r="G54" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" s="1">
         <v>115</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F55" s="2">
-        <v>20368</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C55" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F55">
+        <v>50000</v>
+      </c>
+      <c r="G55" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H55" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" s="1">
         <v>115</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F56" s="2">
-        <v>45000</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C56" t="s">
+        <v>98</v>
+      </c>
+      <c r="D56" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F56">
+        <v>38015</v>
+      </c>
+      <c r="G56" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="H56" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2775,22 +3006,22 @@
         <v>115</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F57" s="2">
-        <v>2682</v>
+        <v>56000</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2798,22 +3029,22 @@
         <v>115</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" s="2">
-        <v>51000</v>
+        <v>83</v>
+      </c>
+      <c r="F58" s="3">
+        <v>39355</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2821,22 +3052,22 @@
         <v>115</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F59" s="2">
-        <v>16788</v>
+        <v>59500</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2844,22 +3075,22 @@
         <v>115</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F60" s="2">
-        <v>12800</v>
+        <v>63000</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2867,88 +3098,94 @@
         <v>115</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E61" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F61" s="1">
+        <v>106530</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F61" s="1">
-        <v>143300</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" s="1">
         <v>115</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F62" s="3">
-        <v>34568</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="C62" t="s">
+        <v>33</v>
+      </c>
+      <c r="D62" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F62">
+        <v>19942</v>
+      </c>
+      <c r="G62" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="H62" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" s="1">
         <v>115</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F63" s="1">
-        <v>300000</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C63" t="s">
+        <v>33</v>
+      </c>
+      <c r="D63" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F63">
+        <v>16447</v>
+      </c>
+      <c r="G63" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="H63" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" s="1">
         <v>115</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D64" t="s">
-        <v>23</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F64" s="10">
-        <v>47500</v>
-      </c>
-      <c r="G64" s="12" t="s">
-        <v>89</v>
+      <c r="D64" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F64" s="1">
+        <v>117750</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
@@ -2959,22 +3196,22 @@
         <v>115</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F65" s="2">
-        <v>52000</v>
+        <v>59500</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2982,22 +3219,22 @@
         <v>115</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F66" s="1">
-        <v>210000</v>
+        <v>69</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F66" s="3">
+        <v>23014</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3005,19 +3242,19 @@
         <v>115</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F67" s="2">
-        <v>42500</v>
+        <v>23</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F67" s="1">
+        <v>300000</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
@@ -3028,22 +3265,22 @@
         <v>115</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F68" s="2">
-        <v>70000</v>
+        <v>59500</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3051,19 +3288,19 @@
         <v>115</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F69" s="2">
-        <v>59500</v>
+        <v>35</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F69" s="1">
+        <v>255000</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
@@ -3074,22 +3311,22 @@
         <v>115</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F70" s="2">
-        <v>59500</v>
+        <v>83</v>
+      </c>
+      <c r="F70" s="3">
+        <v>8285</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3097,22 +3334,22 @@
         <v>115</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F71" s="1">
-        <v>200000</v>
+        <v>36</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F71" s="2">
+        <v>51000</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3120,22 +3357,22 @@
         <v>115</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F72" s="2">
-        <v>44118</v>
+        <v>23</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F72" s="1">
+        <v>250000</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3143,19 +3380,19 @@
         <v>115</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F73" s="1">
-        <v>217500</v>
+        <v>37</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F73" s="2">
+        <v>20368</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -3166,16 +3403,16 @@
         <v>115</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F74" s="2">
-        <v>59500</v>
+        <v>45000</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>8</v>
@@ -3188,21 +3425,23 @@
       <c r="B75" s="1">
         <v>115</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1" t="s">
-        <v>93</v>
+      <c r="C75" t="s">
+        <v>101</v>
+      </c>
+      <c r="D75" t="s">
+        <v>60</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F75">
+        <v>3400</v>
+      </c>
+      <c r="G75" s="13" t="s">
+        <v>136</v>
       </c>
       <c r="H75" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
@@ -3212,20 +3451,23 @@
       <c r="B76" s="1">
         <v>115</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F76" s="2">
-        <v>52500</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>8</v>
+      <c r="C76" t="s">
+        <v>101</v>
+      </c>
+      <c r="D76" t="s">
+        <v>60</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F76">
+        <v>13120</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="H76" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
@@ -3236,19 +3478,19 @@
         <v>115</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F77" s="3">
-        <v>52776</v>
+        <v>21</v>
+      </c>
+      <c r="F77" s="2">
+        <v>2682</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
@@ -3259,16 +3501,16 @@
         <v>115</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F78" s="2">
-        <v>63000</v>
+        <v>51000</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>8</v>
@@ -3281,20 +3523,20 @@
       <c r="B79" s="1">
         <v>115</v>
       </c>
-      <c r="C79" t="s">
-        <v>49</v>
-      </c>
-      <c r="D79" t="s">
-        <v>23</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F79" s="10">
-        <v>41616</v>
-      </c>
-      <c r="G79" s="12" t="s">
-        <v>89</v>
+      <c r="C79" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F79" s="2">
+        <v>16788</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
@@ -3305,22 +3547,22 @@
         <v>115</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F80" s="2">
-        <v>31500</v>
+        <v>12800</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3328,22 +3570,22 @@
         <v>115</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F81" s="2">
-        <v>42500</v>
+        <v>66</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F81" s="1">
+        <v>143300</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3351,22 +3593,22 @@
         <v>115</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F82" s="1">
-        <v>95912</v>
+        <v>13</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F82" s="3">
+        <v>34568</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3374,45 +3616,45 @@
         <v>115</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E83" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F83" s="1">
+        <v>300000</v>
+      </c>
+      <c r="G83" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F83" s="1">
-        <v>28500</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" s="1">
         <v>115</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F84" s="2">
-        <v>29250</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C84" t="s">
+        <v>73</v>
+      </c>
+      <c r="D84" t="s">
+        <v>23</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F84" s="10">
+        <v>47500</v>
+      </c>
+      <c r="G84" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -3420,22 +3662,22 @@
         <v>115</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F85" s="2">
-        <v>41384</v>
+        <v>52000</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3443,22 +3685,22 @@
         <v>115</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F86" s="2">
-        <v>56000</v>
+        <v>42</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F86" s="1">
+        <v>210000</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3466,22 +3708,22 @@
         <v>115</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F87" s="3">
-        <v>48284</v>
+        <v>21</v>
+      </c>
+      <c r="F87" s="2">
+        <v>42500</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3489,22 +3731,22 @@
         <v>115</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F88" s="2">
-        <v>42500</v>
+        <v>70000</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3512,22 +3754,22 @@
         <v>115</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F89" s="2">
-        <v>41770</v>
+        <v>59500</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3535,91 +3777,97 @@
         <v>115</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F90" s="2">
-        <v>45000</v>
+        <v>59500</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" s="1">
         <v>115</v>
       </c>
-      <c r="C91" t="s">
-        <v>57</v>
-      </c>
-      <c r="D91" t="s">
-        <v>87</v>
-      </c>
-      <c r="E91" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F91" s="10">
-        <v>40000</v>
-      </c>
-      <c r="G91" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C91" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F91" s="1">
+        <v>200000</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" s="1">
         <v>115</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F92" s="3">
-        <v>39125</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C92" t="s">
+        <v>96</v>
+      </c>
+      <c r="D92" t="s">
+        <v>23</v>
+      </c>
+      <c r="E92" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F92">
+        <v>50000</v>
+      </c>
+      <c r="G92" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H92" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" s="1">
         <v>115</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F93" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="C93" t="s">
+        <v>96</v>
+      </c>
+      <c r="D93" t="s">
+        <v>23</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F93">
+        <v>42393</v>
+      </c>
+      <c r="G93" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H93" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3627,22 +3875,22 @@
         <v>115</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F94" s="1">
-        <v>221000</v>
+        <v>45</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F94" s="2">
+        <v>44118</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3650,22 +3898,22 @@
         <v>115</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F95" s="3">
-        <v>26283</v>
+        <v>45</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F95" s="1">
+        <v>217500</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3673,24 +3921,791 @@
         <v>115</v>
       </c>
       <c r="C96" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F96" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" s="1">
+        <v>115</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H97" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" s="1">
+        <v>115</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F98" s="2">
+        <v>52500</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" s="1">
+        <v>115</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F99" s="3">
+        <v>52776</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" s="1">
+        <v>115</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F100" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" s="1">
+        <v>115</v>
+      </c>
+      <c r="C101" t="s">
+        <v>49</v>
+      </c>
+      <c r="D101" t="s">
+        <v>23</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F101" s="10">
+        <v>41616</v>
+      </c>
+      <c r="G101" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" s="1">
+        <v>115</v>
+      </c>
+      <c r="C102" t="s">
+        <v>49</v>
+      </c>
+      <c r="D102" t="s">
+        <v>23</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F102">
+        <v>50000</v>
+      </c>
+      <c r="G102" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H102" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" s="1">
+        <v>115</v>
+      </c>
+      <c r="C103" t="s">
+        <v>49</v>
+      </c>
+      <c r="D103" t="s">
+        <v>23</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F103">
+        <v>38569</v>
+      </c>
+      <c r="G103" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="H103" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" s="1">
+        <v>115</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F104" s="2">
+        <v>31500</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" s="1">
+        <v>115</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F105" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" s="1">
+        <v>115</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F106" s="1">
+        <v>95912</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" s="1">
+        <v>115</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F107" s="1">
+        <v>28500</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" s="1">
+        <v>115</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F108" s="2">
+        <v>29250</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" s="1">
+        <v>115</v>
+      </c>
+      <c r="C109" t="s">
+        <v>52</v>
+      </c>
+      <c r="D109" t="s">
+        <v>29</v>
+      </c>
+      <c r="E109" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F109">
+        <v>8900</v>
+      </c>
+      <c r="G109" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="H109" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" s="1">
+        <v>115</v>
+      </c>
+      <c r="C110" t="s">
+        <v>52</v>
+      </c>
+      <c r="D110" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F110" t="s">
+        <v>103</v>
+      </c>
+      <c r="G110" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H110" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" s="1">
+        <v>115</v>
+      </c>
+      <c r="C111" t="s">
+        <v>52</v>
+      </c>
+      <c r="D111" t="s">
+        <v>29</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F111">
+        <v>19190</v>
+      </c>
+      <c r="G111" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="H111" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" s="1">
+        <v>115</v>
+      </c>
+      <c r="C112" t="s">
+        <v>52</v>
+      </c>
+      <c r="D112" t="s">
+        <v>29</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F112">
+        <v>17728</v>
+      </c>
+      <c r="G112" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="H112" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" s="1">
+        <v>115</v>
+      </c>
+      <c r="C113" t="s">
+        <v>100</v>
+      </c>
+      <c r="D113" t="s">
+        <v>23</v>
+      </c>
+      <c r="E113" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F113">
+        <v>40000</v>
+      </c>
+      <c r="G113" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="H113" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" s="1">
+        <v>115</v>
+      </c>
+      <c r="C114" t="s">
+        <v>100</v>
+      </c>
+      <c r="D114" t="s">
+        <v>23</v>
+      </c>
+      <c r="E114" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F114">
+        <v>17600</v>
+      </c>
+      <c r="G114" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="H114" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" s="1">
+        <v>115</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F115" s="2">
+        <v>41384</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" s="1">
+        <v>115</v>
+      </c>
+      <c r="C116" t="s">
+        <v>53</v>
+      </c>
+      <c r="D116" t="s">
+        <v>23</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F116">
+        <v>40000</v>
+      </c>
+      <c r="G116" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="H116" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" s="1">
+        <v>115</v>
+      </c>
+      <c r="C117" t="s">
+        <v>53</v>
+      </c>
+      <c r="D117" t="s">
+        <v>23</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F117">
+        <v>19200</v>
+      </c>
+      <c r="G117" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="H117" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" s="1">
+        <v>115</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F118" s="2">
+        <v>56000</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" s="1">
+        <v>115</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F119" s="3">
+        <v>48284</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" s="1">
+        <v>115</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F120" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" s="1">
+        <v>115</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F121" s="2">
+        <v>41770</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" s="1">
+        <v>115</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F122" s="2">
+        <v>45000</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" s="1">
+        <v>115</v>
+      </c>
+      <c r="C123" t="s">
+        <v>57</v>
+      </c>
+      <c r="D123" t="s">
+        <v>86</v>
+      </c>
+      <c r="E123" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F123" s="10">
+        <v>40000</v>
+      </c>
+      <c r="G123" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" s="1">
+        <v>115</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F124" s="3">
+        <v>39125</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" s="1">
+        <v>115</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F125" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" s="1">
+        <v>115</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F126" s="1">
+        <v>221000</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" s="1">
+        <v>115</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F127" s="3">
+        <v>26283</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" s="1">
+        <v>115</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="D128" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E128" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F128" s="2">
         <v>63000</v>
       </c>
-      <c r="G96" s="1" t="s">
+      <c r="G128" s="1" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:G96">
-    <sortCondition ref="C2:C96"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:H128">
+    <sortCondition ref="C2:C128"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D880AC-6D20-4434-B41F-63EED2DAE3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53ED4489-91DC-41AE-A62B-1DADB0A1DB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="資料表" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$G$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$H$128</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="121">
   <si>
     <t>序號</t>
   </si>
@@ -388,10 +388,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>(暫顯示為0,請款額度依學雜費繳費單申請,上限60000元/學期)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>113年6月24日校教師評審委員會議通過</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -487,99 +483,6 @@
   <si>
     <t>115年6月22日校教師評審委員會通過</t>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>115年6月23日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月24日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月25日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月26日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月27日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月28日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月29日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月30日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月31日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月32日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月33日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月34日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月35日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月36日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月37日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月38日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月39日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月40日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月41日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月42日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月43日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月44日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月45日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月46日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月47日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月48日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月49日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月50日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月51日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月52日校教師評審委員會通過</t>
-  </si>
-  <si>
-    <t>115年6月53日校教師評審委員會通過</t>
   </si>
 </sst>
 </file>
@@ -1690,22 +1593,22 @@
         <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F2">
         <v>29000</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="H2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1716,22 +1619,22 @@
         <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F3">
         <v>2000</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="H3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -1857,22 +1760,22 @@
         <v>115</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F9">
         <v>29636</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1883,22 +1786,22 @@
         <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
         <v>23</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F10">
         <v>11068</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1961,16 +1864,16 @@
         <v>23</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F13">
         <v>30850</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -1987,16 +1890,16 @@
         <v>23</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F14">
         <v>12726</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="H14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -2473,16 +2376,16 @@
         <v>23</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F35">
         <v>30850</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="H35" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
@@ -2499,16 +2402,16 @@
         <v>23</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F36">
         <v>9696</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="H36" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
@@ -2548,16 +2451,16 @@
         <v>64</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F38" s="1">
         <v>32320</v>
       </c>
       <c r="G38" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H38" t="s">
         <v>93</v>
-      </c>
-      <c r="H38" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
@@ -2620,16 +2523,16 @@
         <v>23</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F41">
         <v>30850</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -2646,16 +2549,16 @@
         <v>23</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F42">
         <v>19150</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -2672,16 +2575,16 @@
         <v>23</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F43">
         <v>12936</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="H43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -2698,16 +2601,16 @@
         <v>23</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F44">
         <v>31462</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="H44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -2770,16 +2673,16 @@
         <v>29</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F47">
         <v>17789</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
@@ -2796,16 +2699,16 @@
         <v>29</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F48">
         <v>8085</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="H48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
@@ -2954,22 +2857,22 @@
         <v>115</v>
       </c>
       <c r="C55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D55" t="s">
         <v>23</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F55">
         <v>50000</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="H55" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
@@ -2980,22 +2883,22 @@
         <v>115</v>
       </c>
       <c r="C56" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D56" t="s">
         <v>23</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F56">
         <v>38015</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="H56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
@@ -3127,16 +3030,16 @@
         <v>10</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F62">
         <v>19942</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="H62" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
@@ -3153,16 +3056,16 @@
         <v>10</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F63">
         <v>16447</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="H63" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
@@ -3426,22 +3329,22 @@
         <v>115</v>
       </c>
       <c r="C75" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D75" t="s">
         <v>60</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F75">
         <v>3400</v>
       </c>
       <c r="G75" s="13" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="H75" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
@@ -3452,22 +3355,22 @@
         <v>115</v>
       </c>
       <c r="C76" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D76" t="s">
         <v>60</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F76">
         <v>13120</v>
       </c>
       <c r="G76" s="13" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="H76" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
@@ -3823,22 +3726,22 @@
         <v>115</v>
       </c>
       <c r="C92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D92" t="s">
         <v>23</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F92">
         <v>50000</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H92" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
@@ -3849,22 +3752,22 @@
         <v>115</v>
       </c>
       <c r="C93" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D93" t="s">
         <v>23</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F93">
         <v>42393</v>
       </c>
       <c r="G93" s="13" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="H93" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.35">
@@ -3950,14 +3853,16 @@
         <v>63</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="F97" s="1"/>
+        <v>94</v>
+      </c>
+      <c r="F97" s="1">
+        <v>60000</v>
+      </c>
       <c r="G97" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H97" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.35">
@@ -4066,16 +3971,16 @@
         <v>23</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F102">
         <v>50000</v>
       </c>
       <c r="G102" s="13" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H102" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
@@ -4092,16 +3997,16 @@
         <v>23</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F103">
         <v>38569</v>
       </c>
       <c r="G103" s="13" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="H103" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
@@ -4233,16 +4138,16 @@
         <v>29</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F109">
         <v>8900</v>
       </c>
       <c r="G109" s="13" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H109" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.35">
@@ -4259,16 +4164,16 @@
         <v>29</v>
       </c>
       <c r="E110" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F110" t="s">
         <v>102</v>
       </c>
-      <c r="F110" t="s">
-        <v>103</v>
-      </c>
       <c r="G110" s="13" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="H110" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
@@ -4285,16 +4190,16 @@
         <v>29</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F111">
         <v>19190</v>
       </c>
       <c r="G111" s="13" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="H111" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
@@ -4311,16 +4216,16 @@
         <v>29</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F112">
         <v>17728</v>
       </c>
       <c r="G112" s="13" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="H112" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.35">
@@ -4331,22 +4236,22 @@
         <v>115</v>
       </c>
       <c r="C113" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D113" t="s">
         <v>23</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F113">
         <v>40000</v>
       </c>
       <c r="G113" s="13" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="H113" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.35">
@@ -4357,22 +4262,22 @@
         <v>115</v>
       </c>
       <c r="C114" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D114" t="s">
         <v>23</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F114">
         <v>17600</v>
       </c>
       <c r="G114" s="13" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H114" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.35">
@@ -4412,16 +4317,16 @@
         <v>23</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F116">
         <v>40000</v>
       </c>
       <c r="G116" s="13" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="H116" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.35">
@@ -4438,16 +4343,16 @@
         <v>23</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F117">
         <v>19200</v>
       </c>
       <c r="G117" s="13" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="H117" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.35">
@@ -4704,6 +4609,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H128" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:H128">
     <sortCondition ref="C2:C128"/>
   </sortState>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53ED4489-91DC-41AE-A62B-1DADB0A1DB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9298242D-5EA0-40E2-8587-2A7C77623AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1148,16 +1148,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1177,12 +1174,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1598,13 +1589,13 @@
       <c r="D2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>29000</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H2" t="s">
@@ -1624,13 +1615,13 @@
       <c r="D3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>2000</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H3" t="s">
@@ -1745,7 +1736,7 @@
       <c r="E8" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>43084</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1765,13 +1756,13 @@
       <c r="D9" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>29636</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H9" t="s">
@@ -1791,13 +1782,13 @@
       <c r="D10" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>11068</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H10" t="s">
@@ -1840,10 +1831,10 @@
       <c r="D12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="2">
         <v>128075</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -1863,13 +1854,13 @@
       <c r="D13" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>30850</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H13" t="s">
@@ -1889,13 +1880,13 @@
       <c r="D14" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>12726</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H14" t="s">
@@ -1935,13 +1926,13 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="2">
         <v>165000</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -1964,7 +1955,7 @@
       <c r="E17" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <v>8285</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -2010,7 +2001,7 @@
       <c r="E19" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <v>62600</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -2056,7 +2047,7 @@
       <c r="E21" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
         <v>18412</v>
       </c>
       <c r="G21" s="1" t="s">
@@ -2079,7 +2070,7 @@
       <c r="E22" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="2">
         <v>16571</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -2168,13 +2159,13 @@
       <c r="D26" t="s">
         <v>23</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="2">
         <v>45000</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="9" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2217,7 +2208,7 @@
       <c r="E28" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="2">
         <v>47687</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -2329,13 +2320,13 @@
       <c r="D33" t="s">
         <v>86</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="2">
         <v>47500</v>
       </c>
-      <c r="G33" s="12" t="s">
+      <c r="G33" s="9" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2352,13 +2343,13 @@
       <c r="D34" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="2">
         <v>50000</v>
       </c>
-      <c r="G34" s="12" t="s">
+      <c r="G34" s="9" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2375,13 +2366,13 @@
       <c r="D35" t="s">
         <v>23</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="2">
         <v>30850</v>
       </c>
-      <c r="G35" s="13" t="s">
+      <c r="G35" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H35" t="s">
@@ -2401,13 +2392,13 @@
       <c r="D36" t="s">
         <v>23</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="2">
         <v>9696</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H36" t="s">
@@ -2444,19 +2435,19 @@
       <c r="B38" s="1">
         <v>115</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="2">
         <v>32320</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="4" t="s">
         <v>92</v>
       </c>
       <c r="H38" t="s">
@@ -2476,10 +2467,10 @@
       <c r="D39" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="2">
         <v>140000</v>
       </c>
       <c r="G39" s="1" t="s">
@@ -2502,7 +2493,7 @@
       <c r="E40" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="2">
         <v>28884</v>
       </c>
       <c r="G40" s="1" t="s">
@@ -2522,13 +2513,13 @@
       <c r="D41" t="s">
         <v>23</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E41" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="2">
         <v>30850</v>
       </c>
-      <c r="G41" s="13" t="s">
+      <c r="G41" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H41" t="s">
@@ -2548,13 +2539,13 @@
       <c r="D42" t="s">
         <v>23</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E42" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="2">
         <v>19150</v>
       </c>
-      <c r="G42" s="13" t="s">
+      <c r="G42" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H42" t="s">
@@ -2574,13 +2565,13 @@
       <c r="D43" t="s">
         <v>23</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="E43" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="2">
         <v>12936</v>
       </c>
-      <c r="G43" s="13" t="s">
+      <c r="G43" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H43" t="s">
@@ -2600,13 +2591,13 @@
       <c r="D44" t="s">
         <v>23</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E44" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="2">
         <v>31462</v>
       </c>
-      <c r="G44" s="13" t="s">
+      <c r="G44" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H44" t="s">
@@ -2649,10 +2640,10 @@
       <c r="D46" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="2">
         <v>150000</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -2672,13 +2663,13 @@
       <c r="D47" t="s">
         <v>29</v>
       </c>
-      <c r="E47" s="13" t="s">
+      <c r="E47" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="2">
         <v>17789</v>
       </c>
-      <c r="G47" s="13" t="s">
+      <c r="G47" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H47" t="s">
@@ -2698,13 +2689,13 @@
       <c r="D48" t="s">
         <v>29</v>
       </c>
-      <c r="E48" s="13" t="s">
+      <c r="E48" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="2">
         <v>8085</v>
       </c>
-      <c r="G48" s="13" t="s">
+      <c r="G48" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H48" t="s">
@@ -2727,7 +2718,7 @@
       <c r="E49" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="2">
         <v>11185</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -2839,13 +2830,13 @@
       <c r="D54" t="s">
         <v>23</v>
       </c>
-      <c r="E54" s="9" t="s">
+      <c r="E54" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F54" s="10">
+      <c r="F54" s="2">
         <v>40000</v>
       </c>
-      <c r="G54" s="12" t="s">
+      <c r="G54" s="9" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2862,13 +2853,13 @@
       <c r="D55" t="s">
         <v>23</v>
       </c>
-      <c r="E55" s="13" t="s">
+      <c r="E55" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="2">
         <v>50000</v>
       </c>
-      <c r="G55" s="13" t="s">
+      <c r="G55" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H55" t="s">
@@ -2888,13 +2879,13 @@
       <c r="D56" t="s">
         <v>23</v>
       </c>
-      <c r="E56" s="13" t="s">
+      <c r="E56" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="2">
         <v>38015</v>
       </c>
-      <c r="G56" s="13" t="s">
+      <c r="G56" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H56" t="s">
@@ -2940,7 +2931,7 @@
       <c r="E58" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="2">
         <v>39355</v>
       </c>
       <c r="G58" s="1" t="s">
@@ -3003,13 +2994,13 @@
       <c r="C61" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="D61" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="E61" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="2">
         <v>106530</v>
       </c>
       <c r="G61" s="1" t="s">
@@ -3029,13 +3020,13 @@
       <c r="D62" t="s">
         <v>10</v>
       </c>
-      <c r="E62" s="13" t="s">
+      <c r="E62" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="2">
         <v>19942</v>
       </c>
-      <c r="G62" s="13" t="s">
+      <c r="G62" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H62" t="s">
@@ -3055,13 +3046,13 @@
       <c r="D63" t="s">
         <v>10</v>
       </c>
-      <c r="E63" s="13" t="s">
+      <c r="E63" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="2">
         <v>16447</v>
       </c>
-      <c r="G63" s="13" t="s">
+      <c r="G63" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H63" t="s">
@@ -3078,13 +3069,13 @@
       <c r="C64" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="E64" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="2">
         <v>117750</v>
       </c>
       <c r="G64" s="1" t="s">
@@ -3130,7 +3121,7 @@
       <c r="E66" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F66" s="3">
+      <c r="F66" s="2">
         <v>23014</v>
       </c>
       <c r="G66" s="1" t="s">
@@ -3150,10 +3141,10 @@
       <c r="D67" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="E67" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67" s="2">
         <v>300000</v>
       </c>
       <c r="G67" s="1" t="s">
@@ -3193,13 +3184,13 @@
       <c r="C69" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="D69" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="E69" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="2">
         <v>255000</v>
       </c>
       <c r="G69" s="1" t="s">
@@ -3222,7 +3213,7 @@
       <c r="E70" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F70" s="3">
+      <c r="F70" s="2">
         <v>8285</v>
       </c>
       <c r="G70" s="1" t="s">
@@ -3265,10 +3256,10 @@
       <c r="D72" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="E72" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72" s="2">
         <v>250000</v>
       </c>
       <c r="G72" s="1" t="s">
@@ -3334,13 +3325,13 @@
       <c r="D75" t="s">
         <v>60</v>
       </c>
-      <c r="E75" s="13" t="s">
+      <c r="E75" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="2">
         <v>3400</v>
       </c>
-      <c r="G75" s="13" t="s">
+      <c r="G75" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H75" t="s">
@@ -3360,13 +3351,13 @@
       <c r="D76" t="s">
         <v>60</v>
       </c>
-      <c r="E76" s="13" t="s">
+      <c r="E76" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="2">
         <v>13120</v>
       </c>
-      <c r="G76" s="13" t="s">
+      <c r="G76" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H76" t="s">
@@ -3475,13 +3466,13 @@
       <c r="C81" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D81" s="5" t="s">
+      <c r="D81" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="E81" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81" s="2">
         <v>143300</v>
       </c>
       <c r="G81" s="1" t="s">
@@ -3504,7 +3495,7 @@
       <c r="E82" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F82" s="3">
+      <c r="F82" s="2">
         <v>34568</v>
       </c>
       <c r="G82" s="1" t="s">
@@ -3524,10 +3515,10 @@
       <c r="D83" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E83" s="4" t="s">
+      <c r="E83" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83" s="2">
         <v>300000</v>
       </c>
       <c r="G83" s="1" t="s">
@@ -3547,13 +3538,13 @@
       <c r="D84" t="s">
         <v>23</v>
       </c>
-      <c r="E84" s="8" t="s">
+      <c r="E84" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F84" s="10">
+      <c r="F84" s="2">
         <v>47500</v>
       </c>
-      <c r="G84" s="12" t="s">
+      <c r="G84" s="9" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3590,13 +3581,13 @@
       <c r="C86" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D86" s="5" t="s">
+      <c r="D86" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E86" s="4" t="s">
+      <c r="E86" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86" s="2">
         <v>210000</v>
       </c>
       <c r="G86" s="1" t="s">
@@ -3705,13 +3696,13 @@
       <c r="C91" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D91" s="5" t="s">
+      <c r="D91" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E91" s="4" t="s">
+      <c r="E91" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91" s="2">
         <v>200000</v>
       </c>
       <c r="G91" s="1" t="s">
@@ -3731,13 +3722,13 @@
       <c r="D92" t="s">
         <v>23</v>
       </c>
-      <c r="E92" s="13" t="s">
+      <c r="E92" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="2">
         <v>50000</v>
       </c>
-      <c r="G92" s="13" t="s">
+      <c r="G92" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H92" t="s">
@@ -3757,13 +3748,13 @@
       <c r="D93" t="s">
         <v>23</v>
       </c>
-      <c r="E93" s="13" t="s">
+      <c r="E93" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="2">
         <v>42393</v>
       </c>
-      <c r="G93" s="13" t="s">
+      <c r="G93" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H93" t="s">
@@ -3803,13 +3794,13 @@
       <c r="C95" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D95" s="5" t="s">
+      <c r="D95" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E95" s="4" t="s">
+      <c r="E95" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F95" s="2">
         <v>217500</v>
       </c>
       <c r="G95" s="1" t="s">
@@ -3852,10 +3843,10 @@
       <c r="D97" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E97" s="7" t="s">
+      <c r="E97" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97" s="2">
         <v>60000</v>
       </c>
       <c r="G97" s="1" t="s">
@@ -3904,7 +3895,7 @@
       <c r="E99" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F99" s="3">
+      <c r="F99" s="2">
         <v>52776</v>
       </c>
       <c r="G99" s="1" t="s">
@@ -3947,13 +3938,13 @@
       <c r="D101" t="s">
         <v>23</v>
       </c>
-      <c r="E101" s="9" t="s">
+      <c r="E101" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F101" s="10">
+      <c r="F101" s="2">
         <v>41616</v>
       </c>
-      <c r="G101" s="12" t="s">
+      <c r="G101" s="9" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3970,13 +3961,13 @@
       <c r="D102" t="s">
         <v>23</v>
       </c>
-      <c r="E102" s="13" t="s">
+      <c r="E102" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F102">
+      <c r="F102" s="2">
         <v>50000</v>
       </c>
-      <c r="G102" s="13" t="s">
+      <c r="G102" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H102" t="s">
@@ -3996,13 +3987,13 @@
       <c r="D103" t="s">
         <v>23</v>
       </c>
-      <c r="E103" s="13" t="s">
+      <c r="E103" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="2">
         <v>38569</v>
       </c>
-      <c r="G103" s="13" t="s">
+      <c r="G103" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H103" t="s">
@@ -4068,10 +4059,10 @@
       <c r="D106" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E106" s="4" t="s">
+      <c r="E106" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F106" s="2">
         <v>95912</v>
       </c>
       <c r="G106" s="1" t="s">
@@ -4091,10 +4082,10 @@
       <c r="D107" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E107" s="4" t="s">
+      <c r="E107" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F107" s="2">
         <v>28500</v>
       </c>
       <c r="G107" s="1" t="s">
@@ -4137,13 +4128,13 @@
       <c r="D109" t="s">
         <v>29</v>
       </c>
-      <c r="E109" s="13" t="s">
+      <c r="E109" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F109">
+      <c r="F109" s="2">
         <v>8900</v>
       </c>
-      <c r="G109" s="13" t="s">
+      <c r="G109" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H109" t="s">
@@ -4163,13 +4154,13 @@
       <c r="D110" t="s">
         <v>29</v>
       </c>
-      <c r="E110" s="13" t="s">
+      <c r="E110" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F110" t="s">
+      <c r="F110" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G110" s="13" t="s">
+      <c r="G110" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H110" t="s">
@@ -4189,13 +4180,13 @@
       <c r="D111" t="s">
         <v>29</v>
       </c>
-      <c r="E111" s="13" t="s">
+      <c r="E111" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F111">
+      <c r="F111" s="2">
         <v>19190</v>
       </c>
-      <c r="G111" s="13" t="s">
+      <c r="G111" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H111" t="s">
@@ -4215,13 +4206,13 @@
       <c r="D112" t="s">
         <v>29</v>
       </c>
-      <c r="E112" s="13" t="s">
+      <c r="E112" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F112">
+      <c r="F112" s="2">
         <v>17728</v>
       </c>
-      <c r="G112" s="13" t="s">
+      <c r="G112" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H112" t="s">
@@ -4241,13 +4232,13 @@
       <c r="D113" t="s">
         <v>23</v>
       </c>
-      <c r="E113" s="13" t="s">
+      <c r="E113" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F113">
+      <c r="F113" s="2">
         <v>40000</v>
       </c>
-      <c r="G113" s="13" t="s">
+      <c r="G113" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H113" t="s">
@@ -4267,13 +4258,13 @@
       <c r="D114" t="s">
         <v>23</v>
       </c>
-      <c r="E114" s="13" t="s">
+      <c r="E114" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F114">
+      <c r="F114" s="2">
         <v>17600</v>
       </c>
-      <c r="G114" s="13" t="s">
+      <c r="G114" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H114" t="s">
@@ -4316,13 +4307,13 @@
       <c r="D116" t="s">
         <v>23</v>
       </c>
-      <c r="E116" s="13" t="s">
+      <c r="E116" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F116">
+      <c r="F116" s="2">
         <v>40000</v>
       </c>
-      <c r="G116" s="13" t="s">
+      <c r="G116" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H116" t="s">
@@ -4342,13 +4333,13 @@
       <c r="D117" t="s">
         <v>23</v>
       </c>
-      <c r="E117" s="13" t="s">
+      <c r="E117" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F117">
+      <c r="F117" s="2">
         <v>19200</v>
       </c>
-      <c r="G117" s="13" t="s">
+      <c r="G117" s="10" t="s">
         <v>120</v>
       </c>
       <c r="H117" t="s">
@@ -4394,7 +4385,7 @@
       <c r="E119" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F119" s="3">
+      <c r="F119" s="2">
         <v>48284</v>
       </c>
       <c r="G119" s="1" t="s">
@@ -4483,13 +4474,13 @@
       <c r="D123" t="s">
         <v>86</v>
       </c>
-      <c r="E123" s="9" t="s">
+      <c r="E123" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F123" s="10">
+      <c r="F123" s="2">
         <v>40000</v>
       </c>
-      <c r="G123" s="12" t="s">
+      <c r="G123" s="9" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4509,7 +4500,7 @@
       <c r="E124" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F124" s="3">
+      <c r="F124" s="2">
         <v>39125</v>
       </c>
       <c r="G124" s="1" t="s">
@@ -4549,13 +4540,13 @@
       <c r="C126" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D126" s="5" t="s">
+      <c r="D126" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E126" s="4" t="s">
+      <c r="E126" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F126" s="1">
+      <c r="F126" s="2">
         <v>221000</v>
       </c>
       <c r="G126" s="1" t="s">
@@ -4578,7 +4569,7 @@
       <c r="E127" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F127" s="3">
+      <c r="F127" s="2">
         <v>26283</v>
       </c>
       <c r="G127" s="1" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9298242D-5EA0-40E2-8587-2A7C77623AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC445617-3FAD-47A5-A3F2-06424FA49E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC445617-3FAD-47A5-A3F2-06424FA49E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8783F57E-2B58-495F-80E6-9E830C855279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="120">
   <si>
     <t>序號</t>
   </si>
@@ -424,9 +424,6 @@
   <si>
     <t>研習_參加國際研討會並發表_差旅費</t>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>新加坡/Effects of Generative AI Virtual Humans on Nursing Students Communication Skills, Self-Directed Learning, and Self-Efficacy: A Quasi-Experimental Study</t>
@@ -1596,10 +1593,10 @@
         <v>29000</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1616,16 +1613,16 @@
         <v>23</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F3" s="2">
         <v>2000</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -1763,10 +1760,10 @@
         <v>29636</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1783,16 +1780,16 @@
         <v>23</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F10" s="2">
         <v>11068</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1861,10 +1858,10 @@
         <v>30850</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -1881,16 +1878,16 @@
         <v>23</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F14" s="2">
         <v>12726</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -2373,10 +2370,10 @@
         <v>30850</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
@@ -2393,16 +2390,16 @@
         <v>23</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F36" s="2">
         <v>9696</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H36" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
@@ -2520,10 +2517,10 @@
         <v>30850</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -2546,10 +2543,10 @@
         <v>19150</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -2566,16 +2563,16 @@
         <v>23</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F43" s="2">
         <v>12936</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -2592,16 +2589,16 @@
         <v>23</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F44" s="2">
         <v>31462</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -2670,10 +2667,10 @@
         <v>17789</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
@@ -2690,16 +2687,16 @@
         <v>29</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F48" s="2">
         <v>8085</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
@@ -2860,10 +2857,10 @@
         <v>50000</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H55" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
@@ -2880,16 +2877,16 @@
         <v>23</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F56" s="2">
         <v>38015</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H56" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
@@ -3027,10 +3024,10 @@
         <v>19942</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H62" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
@@ -3047,16 +3044,16 @@
         <v>10</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F63" s="2">
         <v>16447</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H63" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
@@ -3332,10 +3329,10 @@
         <v>3400</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H75" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
@@ -3352,16 +3349,16 @@
         <v>60</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F76" s="2">
         <v>13120</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H76" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
@@ -3729,10 +3726,10 @@
         <v>50000</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H92" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
@@ -3749,16 +3746,16 @@
         <v>23</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F93" s="2">
         <v>42393</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H93" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.35">
@@ -3968,10 +3965,10 @@
         <v>50000</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H102" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
@@ -3988,16 +3985,16 @@
         <v>23</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F103" s="2">
         <v>38569</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H103" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
@@ -4135,10 +4132,10 @@
         <v>8900</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H109" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.35">
@@ -4157,14 +4154,14 @@
       <c r="E110" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F110" s="2" t="s">
-        <v>102</v>
+      <c r="F110" s="2">
+        <v>0</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H110" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
@@ -4181,16 +4178,16 @@
         <v>29</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F111" s="2">
         <v>19190</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H111" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
@@ -4207,16 +4204,16 @@
         <v>29</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F112" s="2">
         <v>17728</v>
       </c>
       <c r="G112" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H112" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.35">
@@ -4239,10 +4236,10 @@
         <v>40000</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H113" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.35">
@@ -4259,16 +4256,16 @@
         <v>23</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F114" s="2">
         <v>17600</v>
       </c>
       <c r="G114" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H114" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.35">
@@ -4314,10 +4311,10 @@
         <v>40000</v>
       </c>
       <c r="G116" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H116" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.35">
@@ -4334,16 +4331,16 @@
         <v>23</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F117" s="2">
         <v>19200</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H117" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.35">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D722FB-BBEB-45D0-8FCE-4EC2F40A265B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F5D769-1152-44A6-ADEE-3E43A3AA58BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9938,22 +9938,19 @@
         <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F2" s="2">
-        <v>29000</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H2" t="s">
-        <v>113</v>
+      <c r="E2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G2" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -9964,22 +9961,19 @@
         <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F3" s="2">
-        <v>2000</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" t="s">
-        <v>113</v>
+      <c r="E3" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G3" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -9989,20 +9983,20 @@
       <c r="B4" s="1">
         <v>115</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>23</v>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" t="s">
+        <v>173</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F4" s="11">
+        <v>5100</v>
+      </c>
+      <c r="G4" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -10012,20 +10006,20 @@
       <c r="B5" s="1">
         <v>115</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
+      <c r="C5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2">
-        <v>52500</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F5" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G5" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -10035,20 +10029,23 @@
       <c r="B6" s="1">
         <v>115</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>7</v>
+      <c r="C6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="F6" s="2">
-        <v>56000</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>8</v>
+        <v>29000</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -10058,20 +10055,23 @@
       <c r="B7" s="1">
         <v>115</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>7</v>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="F7" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>8</v>
+        <v>2000</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H7" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -10081,20 +10081,20 @@
       <c r="B8" s="1">
         <v>115</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>13</v>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="2">
-        <v>43084</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>84</v>
+        <v>170</v>
+      </c>
+      <c r="F8" s="11">
+        <v>5000</v>
+      </c>
+      <c r="G8" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -10104,23 +10104,20 @@
       <c r="B9" s="1">
         <v>115</v>
       </c>
-      <c r="C9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>178</v>
+      <c r="E9" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F9" s="2">
-        <v>29636</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H9" t="s">
-        <v>104</v>
+        <v>59500</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -10131,22 +10128,19 @@
         <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="D10" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F10" s="2">
-        <v>11068</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H10" t="s">
-        <v>104</v>
+      <c r="E10" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F10" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G10" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -10157,22 +10151,22 @@
         <v>115</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F11" s="2">
-        <v>51931</v>
+        <v>52500</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -10180,19 +10174,19 @@
         <v>115</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>81</v>
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F12" s="2">
-        <v>128075</v>
+        <v>56000</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -10203,22 +10197,19 @@
         <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F13" s="2">
-        <v>30850</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H13" t="s">
-        <v>103</v>
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F13" s="11">
+        <v>3700</v>
+      </c>
+      <c r="G13" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -10228,23 +10219,20 @@
       <c r="B14" s="1">
         <v>115</v>
       </c>
-      <c r="C14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>179</v>
+      <c r="C14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F14" s="2">
-        <v>12726</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H14" t="s">
-        <v>103</v>
+        <v>40000</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -10255,114 +10243,120 @@
         <v>115</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="F15" s="2">
-        <v>63000</v>
+        <v>43084</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="1">
         <v>115</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F16" s="2">
-        <v>165000</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F16" s="11">
+        <v>500</v>
+      </c>
+      <c r="G16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="1">
         <v>115</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>83</v>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="F17" s="2">
-        <v>8285</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+        <v>29636</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="1">
         <v>115</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>7</v>
+      <c r="C18" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="F18" s="2">
-        <v>48000</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+        <v>11068</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="1">
         <v>115</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>13</v>
+      <c r="C19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" s="2">
-        <v>62600</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F19" s="11">
+        <v>3900</v>
+      </c>
+      <c r="G19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -10370,22 +10364,22 @@
         <v>115</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F20" s="2">
-        <v>56000</v>
+        <v>51931</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -10393,114 +10387,120 @@
         <v>115</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F21" s="2">
-        <v>18412</v>
+        <v>128075</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="1">
         <v>115</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>83</v>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="F22" s="2">
-        <v>16571</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+        <v>30850</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H22" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="1">
         <v>115</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>21</v>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="F23" s="2">
-        <v>31500</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+        <v>12726</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H23" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="1">
         <v>115</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
         <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F24" s="11">
+        <v>7600</v>
+      </c>
+      <c r="G24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" s="1">
         <v>115</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="C25" t="s">
+        <v>145</v>
+      </c>
+      <c r="D25" t="s">
         <v>23</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" s="2">
-        <v>20564</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F25" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G25" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -10508,22 +10508,22 @@
         <v>115</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="D26" t="s">
         <v>23</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F26" s="2">
-        <v>45000</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E26" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F26" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G26" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -10531,22 +10531,22 @@
         <v>115</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F27" s="2">
-        <v>51750</v>
+        <v>63000</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -10554,22 +10554,22 @@
         <v>115</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F28" s="2">
-        <v>47687</v>
+        <v>165000</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -10577,45 +10577,45 @@
         <v>115</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="F29" s="2">
-        <v>42500</v>
+        <v>8285</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="1">
         <v>115</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30" s="1" t="s">
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F30" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -10623,22 +10623,22 @@
         <v>115</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F31" s="2">
-        <v>17000</v>
+        <v>48000</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -10646,22 +10646,22 @@
         <v>115</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="F32" s="2">
-        <v>60000</v>
+        <v>62600</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -10669,22 +10669,22 @@
         <v>115</v>
       </c>
       <c r="C33" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F33" s="2">
-        <v>47500</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F33" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G33" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -10692,48 +10692,45 @@
         <v>115</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>87</v>
+        <v>16</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F34" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+        <v>56000</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" s="1">
         <v>115</v>
       </c>
-      <c r="C35" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>178</v>
+      <c r="C35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F35" s="2">
-        <v>30850</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H35" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+        <v>18412</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -10741,74 +10738,68 @@
         <v>115</v>
       </c>
       <c r="C36" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F36" s="2">
-        <v>9696</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H36" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F36" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G36" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" s="1">
         <v>115</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>23</v>
+      <c r="C37" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" t="s">
+        <v>20</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F37" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G37" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" s="1">
         <v>115</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F38" s="2">
-        <v>32320</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="C38" t="s">
+        <v>131</v>
+      </c>
+      <c r="D38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F38" s="11">
+        <v>3900</v>
+      </c>
+      <c r="G38" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -10816,71 +10807,68 @@
         <v>115</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>81</v>
+        <v>16</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F39" s="2">
-        <v>140000</v>
+        <v>16571</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" s="1">
         <v>115</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>23</v>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>16</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F40" s="2">
-        <v>28884</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F40" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G40" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" s="1">
         <v>115</v>
       </c>
-      <c r="C41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D41" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>178</v>
+      <c r="C41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="F41" s="2">
-        <v>30850</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H41" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+        <v>31500</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -10888,172 +10876,157 @@
         <v>115</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F42" s="2">
-        <v>19150</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H42" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F42" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G42" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" s="1">
         <v>115</v>
       </c>
-      <c r="C43" t="s">
-        <v>27</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E43" s="10" t="s">
-        <v>179</v>
+      <c r="E43" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F43" s="2">
-        <v>12936</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H43" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+        <v>59500</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" s="1">
         <v>115</v>
       </c>
-      <c r="C44" t="s">
-        <v>27</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="C44" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E44" s="10" t="s">
-        <v>179</v>
+      <c r="E44" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="F44" s="2">
-        <v>31462</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H44" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+        <v>20564</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" s="1">
         <v>115</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>7</v>
+      <c r="C45" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="F45" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>45000</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" s="1">
         <v>115</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F46" s="2">
-        <v>150000</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G46" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" s="1">
         <v>115</v>
       </c>
-      <c r="C47" t="s">
-        <v>28</v>
-      </c>
-      <c r="D47" t="s">
-        <v>29</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>178</v>
+      <c r="C47" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F47" s="2">
-        <v>17789</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H47" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+        <v>51750</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" s="1">
         <v>115</v>
       </c>
-      <c r="C48" t="s">
-        <v>28</v>
-      </c>
-      <c r="D48" t="s">
-        <v>29</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>179</v>
+      <c r="C48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F48" s="2">
-        <v>8085</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H48" t="s">
-        <v>107</v>
+        <v>47687</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
@@ -11063,20 +11036,20 @@
       <c r="B49" s="1">
         <v>115</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>60</v>
+      <c r="C49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" t="s">
+        <v>13</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F49" s="2">
-        <v>11185</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>84</v>
+        <v>170</v>
+      </c>
+      <c r="F49" s="11">
+        <v>7200</v>
+      </c>
+      <c r="G49" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
@@ -11086,20 +11059,20 @@
       <c r="B50" s="1">
         <v>115</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D50" s="1" t="s">
+      <c r="C50" t="s">
+        <v>134</v>
+      </c>
+      <c r="D50" t="s">
         <v>23</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F50" s="11">
+        <v>1500</v>
+      </c>
+      <c r="G50" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
@@ -11110,16 +11083,16 @@
         <v>115</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F51" s="2">
-        <v>63000</v>
+        <v>42500</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>8</v>
@@ -11133,16 +11106,16 @@
         <v>115</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F52" s="2">
-        <v>40000</v>
+        <v>63000</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>8</v>
@@ -11155,20 +11128,20 @@
       <c r="B53" s="1">
         <v>115</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>23</v>
+      <c r="C53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" t="s">
+        <v>16</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" s="2">
-        <v>70000</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F53" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G53" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
@@ -11179,19 +11152,19 @@
         <v>115</v>
       </c>
       <c r="C54" t="s">
-        <v>31</v>
+        <v>135</v>
       </c>
       <c r="D54" t="s">
         <v>23</v>
       </c>
-      <c r="E54" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F54" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>88</v>
+      <c r="E54" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F54" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G54" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
@@ -11201,23 +11174,20 @@
       <c r="B55" s="1">
         <v>115</v>
       </c>
-      <c r="C55" t="s">
-        <v>97</v>
-      </c>
-      <c r="D55" t="s">
-        <v>23</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>178</v>
+      <c r="C55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="F55" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H55" t="s">
-        <v>111</v>
+        <v>17000</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
@@ -11227,23 +11197,20 @@
       <c r="B56" s="1">
         <v>115</v>
       </c>
-      <c r="C56" t="s">
-        <v>97</v>
-      </c>
-      <c r="D56" t="s">
-        <v>23</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>179</v>
+      <c r="C56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F56" s="2">
-        <v>38015</v>
-      </c>
-      <c r="G56" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H56" t="s">
-        <v>111</v>
+        <v>60000</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
@@ -11253,20 +11220,20 @@
       <c r="B57" s="1">
         <v>115</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>7</v>
+      <c r="C57" t="s">
+        <v>26</v>
+      </c>
+      <c r="D57" t="s">
+        <v>86</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="F57" s="2">
-        <v>56000</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>8</v>
+        <v>47500</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
@@ -11276,20 +11243,20 @@
       <c r="B58" s="1">
         <v>115</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>13</v>
+      <c r="C58" t="s">
+        <v>26</v>
+      </c>
+      <c r="D58" t="s">
+        <v>20</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F58" s="2">
-        <v>39355</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>84</v>
+        <v>170</v>
+      </c>
+      <c r="F58" s="11">
+        <v>8400</v>
+      </c>
+      <c r="G58" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
@@ -11300,19 +11267,19 @@
         <v>115</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="F59" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>8</v>
+        <v>50000</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
@@ -11322,43 +11289,49 @@
       <c r="B60" s="1">
         <v>115</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>7</v>
+      <c r="C60" t="s">
+        <v>85</v>
+      </c>
+      <c r="D60" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="F60" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>30850</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H60" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" s="1">
         <v>115</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>81</v>
+      <c r="C61" t="s">
+        <v>85</v>
+      </c>
+      <c r="D61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="F61" s="2">
-        <v>106530</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>82</v>
+        <v>9696</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H61" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
@@ -11369,22 +11342,19 @@
         <v>115</v>
       </c>
       <c r="C62" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D62" t="s">
-        <v>10</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F62" s="2">
-        <v>19942</v>
-      </c>
-      <c r="G62" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H62" t="s">
-        <v>109</v>
+        <v>23</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F62" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G62" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
@@ -11394,49 +11364,49 @@
       <c r="B63" s="1">
         <v>115</v>
       </c>
-      <c r="C63" t="s">
-        <v>33</v>
-      </c>
-      <c r="D63" t="s">
-        <v>10</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>179</v>
+      <c r="C63" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F63" s="2">
-        <v>16447</v>
-      </c>
-      <c r="G63" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H63" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>59500</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" s="1">
         <v>115</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>74</v>
+      <c r="C64" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>81</v>
+        <v>64</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="F64" s="2">
-        <v>117750</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+        <v>32320</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H64" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -11444,19 +11414,19 @@
         <v>115</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F65" s="2">
-        <v>59500</v>
+        <v>140000</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
@@ -11467,7 +11437,7 @@
         <v>115</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>23</v>
@@ -11476,33 +11446,36 @@
         <v>83</v>
       </c>
       <c r="F66" s="2">
-        <v>23014</v>
+        <v>28884</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" s="1">
         <v>115</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D67" s="1" t="s">
+      <c r="C67" t="s">
+        <v>27</v>
+      </c>
+      <c r="D67" t="s">
         <v>23</v>
       </c>
-      <c r="E67" s="3" t="s">
-        <v>81</v>
+      <c r="E67" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="F67" s="2">
-        <v>300000</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>70</v>
+        <v>30850</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H67" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
@@ -11512,43 +11485,49 @@
       <c r="B68" s="1">
         <v>115</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>11</v>
+      <c r="C68" t="s">
+        <v>27</v>
+      </c>
+      <c r="D68" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="F68" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>19150</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H68" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" s="1">
         <v>115</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>81</v>
+      <c r="C69" t="s">
+        <v>27</v>
+      </c>
+      <c r="D69" t="s">
+        <v>23</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="F69" s="2">
-        <v>255000</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>82</v>
+        <v>12936</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H69" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
@@ -11558,20 +11537,23 @@
       <c r="B70" s="1">
         <v>115</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>83</v>
+      <c r="C70" t="s">
+        <v>27</v>
+      </c>
+      <c r="D70" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="F70" s="2">
-        <v>8285</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>84</v>
+        <v>31462</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H70" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
@@ -11581,43 +11563,43 @@
       <c r="B71" s="1">
         <v>115</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D71" s="1" t="s">
+      <c r="C71" t="s">
+        <v>27</v>
+      </c>
+      <c r="D71" t="s">
         <v>23</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" s="2">
-        <v>51000</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F71" s="11">
+        <v>3700</v>
+      </c>
+      <c r="G71" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" s="1">
         <v>115</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D72" s="1" t="s">
+      <c r="C72" t="s">
+        <v>136</v>
+      </c>
+      <c r="D72" t="s">
         <v>23</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F72" s="2">
-        <v>250000</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>82</v>
+      <c r="E72" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F72" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G72" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
@@ -11628,22 +11610,22 @@
         <v>115</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F73" s="2">
-        <v>20368</v>
+        <v>63000</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -11651,19 +11633,19 @@
         <v>115</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>21</v>
+        <v>76</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F74" s="2">
-        <v>45000</v>
+        <v>150000</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
@@ -11674,22 +11656,22 @@
         <v>115</v>
       </c>
       <c r="C75" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="D75" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>178</v>
       </c>
       <c r="F75" s="2">
-        <v>3400</v>
+        <v>17789</v>
       </c>
       <c r="G75" s="10" t="s">
         <v>117</v>
       </c>
       <c r="H75" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
@@ -11700,22 +11682,22 @@
         <v>115</v>
       </c>
       <c r="C76" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="D76" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>179</v>
       </c>
       <c r="F76" s="2">
-        <v>13120</v>
+        <v>8085</v>
       </c>
       <c r="G76" s="10" t="s">
         <v>117</v>
       </c>
       <c r="H76" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
@@ -11725,20 +11707,20 @@
       <c r="B77" s="1">
         <v>115</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>40</v>
+      <c r="C77" t="s">
+        <v>28</v>
+      </c>
+      <c r="D77" t="s">
+        <v>29</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F77" s="2">
-        <v>2682</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F77" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G77" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
@@ -11748,20 +11730,20 @@
       <c r="B78" s="1">
         <v>115</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>40</v>
+      <c r="C78" t="s">
+        <v>132</v>
+      </c>
+      <c r="D78" t="s">
+        <v>23</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F78" s="2">
-        <v>51000</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F78" s="11">
+        <v>8700</v>
+      </c>
+      <c r="G78" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
@@ -11771,20 +11753,20 @@
       <c r="B79" s="1">
         <v>115</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>40</v>
+      <c r="C79" t="s">
+        <v>141</v>
+      </c>
+      <c r="D79" t="s">
+        <v>23</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F79" s="2">
-        <v>16788</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F79" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G79" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
@@ -11794,43 +11776,43 @@
       <c r="B80" s="1">
         <v>115</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>40</v>
+      <c r="C80" t="s">
+        <v>137</v>
+      </c>
+      <c r="D80" t="s">
+        <v>23</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F80" s="2">
-        <v>12800</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F80" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G80" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" s="1">
         <v>115</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F81" s="2">
-        <v>143300</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>82</v>
+      <c r="C81" t="s">
+        <v>125</v>
+      </c>
+      <c r="D81" t="s">
+        <v>20</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F81" s="11">
+        <v>9600</v>
+      </c>
+      <c r="G81" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.35">
@@ -11840,43 +11822,43 @@
       <c r="B82" s="1">
         <v>115</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>13</v>
+      <c r="C82" t="s">
+        <v>138</v>
+      </c>
+      <c r="D82" t="s">
+        <v>23</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F82" s="2">
-        <v>34568</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F82" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G82" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" s="1">
         <v>115</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D83" s="1" t="s">
+      <c r="C83" t="s">
+        <v>139</v>
+      </c>
+      <c r="D83" t="s">
         <v>23</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F83" s="2">
-        <v>300000</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>82</v>
+      <c r="E83" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F83" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G83" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.35">
@@ -11887,19 +11869,19 @@
         <v>115</v>
       </c>
       <c r="C84" t="s">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="D84" t="s">
-        <v>23</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F84" s="2">
-        <v>47500</v>
-      </c>
-      <c r="G84" s="9" t="s">
-        <v>88</v>
+        <v>177</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F84" s="11">
+        <v>400</v>
+      </c>
+      <c r="G84" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.35">
@@ -11909,43 +11891,43 @@
       <c r="B85" s="1">
         <v>115</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>16</v>
+      <c r="C85" t="s">
+        <v>161</v>
+      </c>
+      <c r="D85" t="s">
+        <v>177</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" s="2">
-        <v>52000</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F85" s="11">
+        <v>500</v>
+      </c>
+      <c r="G85" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" s="1">
         <v>115</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F86" s="2">
-        <v>210000</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>82</v>
+      <c r="C86" t="s">
+        <v>140</v>
+      </c>
+      <c r="D86" t="s">
+        <v>23</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F86" s="11">
+        <v>8700</v>
+      </c>
+      <c r="G86" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
@@ -11956,19 +11938,19 @@
         <v>115</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="F87" s="2">
-        <v>42500</v>
+        <v>11185</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.35">
@@ -11978,20 +11960,20 @@
       <c r="B88" s="1">
         <v>115</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D88" s="1" t="s">
+      <c r="C88" t="s">
+        <v>124</v>
+      </c>
+      <c r="D88" t="s">
         <v>20</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F88" s="2">
-        <v>70000</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F88" s="11">
+        <v>2500</v>
+      </c>
+      <c r="G88" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.35">
@@ -12002,13 +11984,13 @@
         <v>115</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F89" s="2">
         <v>59500</v>
@@ -12025,22 +12007,22 @@
         <v>115</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F90" s="2">
-        <v>59500</v>
+        <v>63000</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -12048,19 +12030,19 @@
         <v>115</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>81</v>
+        <v>30</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="F91" s="2">
-        <v>200000</v>
+        <v>40000</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.35">
@@ -12071,22 +12053,19 @@
         <v>115</v>
       </c>
       <c r="C92" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="D92" t="s">
         <v>23</v>
       </c>
-      <c r="E92" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F92" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H92" t="s">
-        <v>102</v>
+      <c r="E92" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F92" s="11">
+        <v>5000</v>
+      </c>
+      <c r="G92" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
@@ -12096,23 +12075,20 @@
       <c r="B93" s="1">
         <v>115</v>
       </c>
-      <c r="C93" t="s">
-        <v>95</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="C93" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E93" s="10" t="s">
-        <v>179</v>
+      <c r="E93" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F93" s="2">
-        <v>42393</v>
-      </c>
-      <c r="G93" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H93" t="s">
-        <v>102</v>
+        <v>70000</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.35">
@@ -12122,43 +12098,43 @@
       <c r="B94" s="1">
         <v>115</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>21</v>
+      <c r="C94" t="s">
+        <v>31</v>
+      </c>
+      <c r="D94" t="s">
+        <v>23</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="F94" s="2">
-        <v>44118</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>40000</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" s="1">
         <v>115</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F95" s="2">
-        <v>217500</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>82</v>
+      <c r="C95" t="s">
+        <v>31</v>
+      </c>
+      <c r="D95" t="s">
+        <v>23</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F95" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G95" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
@@ -12168,20 +12144,23 @@
       <c r="B96" s="1">
         <v>115</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>7</v>
+      <c r="C96" t="s">
+        <v>97</v>
+      </c>
+      <c r="D96" t="s">
+        <v>23</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="F96" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>8</v>
+        <v>50000</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H96" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.35">
@@ -12191,23 +12170,23 @@
       <c r="B97" s="1">
         <v>115</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>94</v>
+      <c r="C97" t="s">
+        <v>97</v>
+      </c>
+      <c r="D97" t="s">
+        <v>23</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="F97" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>91</v>
+        <v>38015</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="H97" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.35">
@@ -12217,20 +12196,20 @@
       <c r="B98" s="1">
         <v>115</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>13</v>
+      <c r="C98" t="s">
+        <v>97</v>
+      </c>
+      <c r="D98" t="s">
+        <v>172</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F98" s="2">
-        <v>52500</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F98" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G98" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.35">
@@ -12240,20 +12219,20 @@
       <c r="B99" s="1">
         <v>115</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>13</v>
+      <c r="C99" t="s">
+        <v>128</v>
+      </c>
+      <c r="D99" t="s">
+        <v>23</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F99" s="2">
-        <v>52776</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>84</v>
+        <v>170</v>
+      </c>
+      <c r="F99" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G99" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.35">
@@ -12264,16 +12243,16 @@
         <v>115</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F100" s="2">
-        <v>63000</v>
+        <v>56000</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>8</v>
@@ -12286,20 +12265,20 @@
       <c r="B101" s="1">
         <v>115</v>
       </c>
-      <c r="C101" t="s">
-        <v>49</v>
-      </c>
-      <c r="D101" t="s">
-        <v>23</v>
-      </c>
-      <c r="E101" s="8" t="s">
-        <v>87</v>
+      <c r="C101" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F101" s="2">
-        <v>41616</v>
-      </c>
-      <c r="G101" s="9" t="s">
-        <v>88</v>
+        <v>39355</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.35">
@@ -12310,22 +12289,19 @@
         <v>115</v>
       </c>
       <c r="C102" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D102" t="s">
-        <v>23</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F102" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G102" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H102" t="s">
-        <v>110</v>
+        <v>13</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F102" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G102" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
@@ -12335,23 +12311,20 @@
       <c r="B103" s="1">
         <v>115</v>
       </c>
-      <c r="C103" t="s">
-        <v>49</v>
-      </c>
-      <c r="D103" t="s">
-        <v>23</v>
-      </c>
-      <c r="E103" s="10" t="s">
-        <v>179</v>
+      <c r="C103" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F103" s="2">
-        <v>38569</v>
-      </c>
-      <c r="G103" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H103" t="s">
-        <v>110</v>
+        <v>59500</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
@@ -12362,22 +12335,22 @@
         <v>115</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F104" s="2">
-        <v>31500</v>
+        <v>63000</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -12385,68 +12358,74 @@
         <v>115</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F105" s="2">
-        <v>42500</v>
+        <v>106530</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
       <c r="B106" s="1">
         <v>115</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>81</v>
+      <c r="C106" t="s">
+        <v>33</v>
+      </c>
+      <c r="D106" t="s">
+        <v>10</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="F106" s="2">
-        <v>95912</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>19942</v>
+      </c>
+      <c r="G106" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H106" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
       <c r="B107" s="1">
         <v>115</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>81</v>
+      <c r="C107" t="s">
+        <v>33</v>
+      </c>
+      <c r="D107" t="s">
+        <v>10</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="F107" s="2">
-        <v>28500</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+        <v>16447</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H107" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -12454,19 +12433,19 @@
         <v>115</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>21</v>
+        <v>74</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F108" s="2">
-        <v>29250</v>
+        <v>117750</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.35">
@@ -12477,22 +12456,19 @@
         <v>115</v>
       </c>
       <c r="C109" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="D109" t="s">
-        <v>29</v>
-      </c>
-      <c r="E109" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F109" s="2">
-        <v>8900</v>
-      </c>
-      <c r="G109" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H109" t="s">
-        <v>105</v>
+        <v>171</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F109" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G109" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.35">
@@ -12502,23 +12478,20 @@
       <c r="B110" s="1">
         <v>115</v>
       </c>
-      <c r="C110" t="s">
-        <v>52</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="C110" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E110" s="10" t="s">
-        <v>178</v>
+      <c r="E110" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F110" s="2">
-        <v>0</v>
-      </c>
-      <c r="G110" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H110" t="s">
-        <v>112</v>
+        <v>59500</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
@@ -12529,22 +12502,19 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D111" t="s">
         <v>29</v>
       </c>
-      <c r="E111" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F111" s="2">
-        <v>19190</v>
-      </c>
-      <c r="G111" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H111" t="s">
-        <v>105</v>
+      <c r="E111" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F111" s="11">
+        <v>6000</v>
+      </c>
+      <c r="G111" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
@@ -12555,51 +12525,45 @@
         <v>115</v>
       </c>
       <c r="C112" t="s">
-        <v>52</v>
+        <v>147</v>
       </c>
       <c r="D112" t="s">
-        <v>29</v>
-      </c>
-      <c r="E112" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F112" s="2">
-        <v>17728</v>
-      </c>
-      <c r="G112" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H112" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F112" s="11">
+        <v>6400</v>
+      </c>
+      <c r="G112" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113" s="1">
         <v>115</v>
       </c>
-      <c r="C113" t="s">
-        <v>99</v>
-      </c>
-      <c r="D113" t="s">
+      <c r="C113" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E113" s="10" t="s">
-        <v>178</v>
+      <c r="E113" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F113" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G113" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H113" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+        <v>23014</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
@@ -12607,74 +12571,68 @@
         <v>115</v>
       </c>
       <c r="C114" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="D114" t="s">
         <v>23</v>
       </c>
-      <c r="E114" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F114" s="2">
-        <v>17600</v>
-      </c>
-      <c r="G114" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H114" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E114" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F114" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G114" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" s="1">
         <v>115</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D115" s="1" t="s">
+      <c r="C115" t="s">
+        <v>133</v>
+      </c>
+      <c r="D115" t="s">
         <v>23</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F115" s="2">
-        <v>41384</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F115" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G115" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116" s="1">
         <v>115</v>
       </c>
-      <c r="C116" t="s">
-        <v>53</v>
-      </c>
-      <c r="D116" t="s">
+      <c r="C116" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E116" s="10" t="s">
-        <v>178</v>
+      <c r="E116" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F116" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G116" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H116" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+        <v>300000</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
@@ -12682,25 +12640,22 @@
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D117" t="s">
-        <v>23</v>
-      </c>
-      <c r="E117" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F117" s="2">
-        <v>19200</v>
-      </c>
-      <c r="G117" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H117" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+        <v>173</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F117" s="11">
+        <v>3800</v>
+      </c>
+      <c r="G117" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
@@ -12708,22 +12663,22 @@
         <v>115</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F118" s="2">
-        <v>56000</v>
+        <v>59500</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -12731,22 +12686,22 @@
         <v>115</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>83</v>
+        <v>35</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F119" s="2">
-        <v>48284</v>
+        <v>255000</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
@@ -12754,45 +12709,45 @@
         <v>115</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="F120" s="2">
-        <v>42500</v>
+        <v>8285</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" s="1">
         <v>115</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>23</v>
+      <c r="C121" t="s">
+        <v>35</v>
+      </c>
+      <c r="D121" t="s">
+        <v>16</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F121" s="2">
-        <v>41770</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F121" s="11">
+        <v>9400</v>
+      </c>
+      <c r="G121" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -12800,68 +12755,68 @@
         <v>115</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F122" s="2">
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
       <c r="B123" s="1">
         <v>115</v>
       </c>
-      <c r="C123" t="s">
-        <v>57</v>
-      </c>
-      <c r="D123" t="s">
-        <v>86</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>87</v>
+      <c r="C123" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F123" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G123" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+        <v>250000</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
       <c r="B124" s="1">
         <v>115</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>23</v>
+      <c r="C124" t="s">
+        <v>36</v>
+      </c>
+      <c r="D124" t="s">
+        <v>176</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F124" s="2">
-        <v>39125</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F124" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G124" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
@@ -12869,239 +12824,245 @@
         <v>115</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F125" s="2">
-        <v>59500</v>
+        <v>20368</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
       <c r="B126" s="1">
         <v>115</v>
       </c>
-      <c r="C126" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F126" s="2">
-        <v>221000</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C126" t="s">
+        <v>37</v>
+      </c>
+      <c r="D126" t="s">
+        <v>23</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F126" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G126" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
       <c r="B127" s="1">
         <v>115</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>60</v>
+      <c r="C127" t="s">
+        <v>163</v>
+      </c>
+      <c r="D127" t="s">
+        <v>174</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F127" s="2">
-        <v>26283</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F127" s="11">
+        <v>7200</v>
+      </c>
+      <c r="G127" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
       <c r="B128" s="1">
         <v>115</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>60</v>
+      <c r="C128" t="s">
+        <v>150</v>
+      </c>
+      <c r="D128" t="s">
+        <v>23</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F128" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="129" spans="2:7" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F128" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G128" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="129" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B129" s="1">
         <v>115</v>
       </c>
       <c r="C129" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="D129" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F129" s="11">
-        <v>1100</v>
-      </c>
-      <c r="G129" s="12" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="130" spans="2:7" x14ac:dyDescent="0.35">
+        <v>5600</v>
+      </c>
+      <c r="G129" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="130" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B130" s="1">
         <v>115</v>
       </c>
       <c r="C130" t="s">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="D130" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F130" s="11">
-        <v>10000</v>
+        <v>5700</v>
       </c>
       <c r="G130" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="131" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B131" s="1">
         <v>115</v>
       </c>
       <c r="C131" t="s">
-        <v>59</v>
+        <v>167</v>
       </c>
       <c r="D131" t="s">
-        <v>60</v>
+        <v>174</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F131" s="11">
-        <v>2700</v>
+        <v>1400</v>
       </c>
       <c r="G131" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="132" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B132" s="1">
         <v>115</v>
       </c>
-      <c r="C132" t="s">
-        <v>68</v>
-      </c>
-      <c r="D132" t="s">
-        <v>16</v>
+      <c r="C132" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F132" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G132" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="133" spans="2:7" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="F132" s="2">
+        <v>45000</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B133" s="1">
         <v>115</v>
       </c>
       <c r="C133" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D133" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F133" s="11">
-        <v>10000</v>
+        <v>5600</v>
       </c>
       <c r="G133" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="134" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B134" s="1">
         <v>115</v>
       </c>
       <c r="C134" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="D134" t="s">
-        <v>16</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F134" s="11">
-        <v>9400</v>
-      </c>
-      <c r="G134" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="135" spans="2:7" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F134" s="2">
+        <v>3400</v>
+      </c>
+      <c r="G134" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H134" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="135" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B135" s="1">
         <v>115</v>
       </c>
       <c r="C135" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D135" t="s">
-        <v>16</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F135" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G135" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="136" spans="2:7" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F135" s="2">
+        <v>13120</v>
+      </c>
+      <c r="G135" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H135" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="136" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B136" s="1">
         <v>115</v>
       </c>
       <c r="C136" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="D136" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>170</v>
@@ -13113,512 +13074,518 @@
         <v>168</v>
       </c>
     </row>
-    <row r="137" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B137" s="1">
         <v>115</v>
       </c>
-      <c r="C137" t="s">
-        <v>118</v>
-      </c>
-      <c r="D137" t="s">
-        <v>29</v>
+      <c r="C137" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F137" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G137" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="138" spans="2:7" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="F137" s="2">
+        <v>2682</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B138" s="1">
         <v>115</v>
       </c>
-      <c r="C138" t="s">
-        <v>28</v>
-      </c>
-      <c r="D138" t="s">
-        <v>29</v>
+      <c r="C138" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F138" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G138" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="139" spans="2:7" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F138" s="2">
+        <v>51000</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B139" s="1">
         <v>115</v>
       </c>
       <c r="C139" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D139" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F139" s="11">
-        <v>6000</v>
+        <v>900</v>
       </c>
       <c r="G139" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="140" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B140" s="1">
         <v>115</v>
       </c>
       <c r="C140" t="s">
-        <v>52</v>
+        <v>157</v>
       </c>
       <c r="D140" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F140" s="11">
-        <v>2200</v>
+        <v>3500</v>
       </c>
       <c r="G140" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="141" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B141" s="1">
         <v>115</v>
       </c>
-      <c r="C141" t="s">
-        <v>119</v>
-      </c>
-      <c r="D141" t="s">
-        <v>29</v>
+      <c r="C141" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F141" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G141" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="142" spans="2:7" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="F141" s="2">
+        <v>16788</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B142" s="1">
         <v>115</v>
       </c>
-      <c r="C142" t="s">
-        <v>9</v>
-      </c>
-      <c r="D142" t="s">
-        <v>10</v>
+      <c r="C142" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F142" s="11">
-        <v>3700</v>
-      </c>
-      <c r="G142" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="143" spans="2:7" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="F142" s="2">
+        <v>12800</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="B143" s="1">
         <v>115</v>
       </c>
-      <c r="C143" t="s">
-        <v>120</v>
-      </c>
-      <c r="D143" t="s">
-        <v>10</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F143" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G143" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="144" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C143" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F143" s="2">
+        <v>143300</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="144" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B144" s="1">
         <v>115</v>
       </c>
-      <c r="C144" t="s">
-        <v>121</v>
-      </c>
-      <c r="D144" t="s">
-        <v>20</v>
+      <c r="C144" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F144" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G144" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="145" spans="2:7" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+      <c r="F144" s="2">
+        <v>34568</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="145" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B145" s="1">
         <v>115</v>
       </c>
       <c r="C145" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="D145" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F145" s="11">
-        <v>5100</v>
+        <v>10000</v>
       </c>
       <c r="G145" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="146" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="B146" s="1">
         <v>115</v>
       </c>
-      <c r="C146" t="s">
-        <v>123</v>
-      </c>
-      <c r="D146" t="s">
-        <v>20</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F146" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G146" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="147" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C146" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F146" s="2">
+        <v>300000</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="147" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B147" s="1">
         <v>115</v>
       </c>
       <c r="C147" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="D147" t="s">
-        <v>20</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F147" s="11">
-        <v>2500</v>
-      </c>
-      <c r="G147" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="148" spans="2:7" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F147" s="2">
+        <v>47500</v>
+      </c>
+      <c r="G147" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="148" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B148" s="1">
         <v>115</v>
       </c>
       <c r="C148" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D148" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F148" s="11">
-        <v>10000</v>
+        <v>3700</v>
       </c>
       <c r="G148" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="149" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B149" s="1">
         <v>115</v>
       </c>
       <c r="C149" t="s">
-        <v>38</v>
+        <v>155</v>
       </c>
       <c r="D149" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F149" s="11">
-        <v>5600</v>
+        <v>3500</v>
       </c>
       <c r="G149" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="150" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="150" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B150" s="1">
         <v>115</v>
       </c>
       <c r="C150" t="s">
-        <v>43</v>
+        <v>158</v>
       </c>
       <c r="D150" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F150" s="11">
-        <v>5600</v>
+        <v>3500</v>
       </c>
       <c r="G150" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="151" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B151" s="1">
         <v>115</v>
       </c>
       <c r="C151" t="s">
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="D151" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F151" s="11">
-        <v>5600</v>
+        <v>3500</v>
       </c>
       <c r="G151" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="152" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="152" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B152" s="1">
         <v>115</v>
       </c>
-      <c r="C152" t="s">
-        <v>26</v>
-      </c>
-      <c r="D152" t="s">
+      <c r="C152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F152" s="2">
+        <v>52000</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="B153" s="1">
+        <v>115</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F153" s="2">
+        <v>210000</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="154" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B154" s="1">
+        <v>115</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E152" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F152" s="11">
-        <v>8400</v>
-      </c>
-      <c r="G152" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="153" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B153" s="1">
-        <v>115</v>
-      </c>
-      <c r="C153" t="s">
-        <v>55</v>
-      </c>
-      <c r="D153" t="s">
+      <c r="E154" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F154" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B155" s="1">
+        <v>115</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E153" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F153" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G153" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="154" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B154" s="1">
-        <v>115</v>
-      </c>
-      <c r="C154" t="s">
-        <v>125</v>
-      </c>
-      <c r="D154" t="s">
+      <c r="E155" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F155" s="2">
+        <v>70000</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B156" s="1">
+        <v>115</v>
+      </c>
+      <c r="C156" t="s">
+        <v>43</v>
+      </c>
+      <c r="D156" t="s">
         <v>20</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F154" s="11">
-        <v>9600</v>
-      </c>
-      <c r="G154" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="155" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B155" s="1">
-        <v>115</v>
-      </c>
-      <c r="C155" t="s">
-        <v>126</v>
-      </c>
-      <c r="D155" t="s">
-        <v>23</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F155" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G155" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="156" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B156" s="1">
-        <v>115</v>
-      </c>
-      <c r="C156" t="s">
-        <v>127</v>
-      </c>
-      <c r="D156" t="s">
-        <v>23</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F156" s="11">
-        <v>3500</v>
+        <v>5600</v>
       </c>
       <c r="G156" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="157" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B157" s="1">
         <v>115</v>
       </c>
-      <c r="C157" t="s">
-        <v>128</v>
-      </c>
-      <c r="D157" t="s">
-        <v>23</v>
+      <c r="C157" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F157" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G157" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="158" spans="2:7" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="F157" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B158" s="1">
         <v>115</v>
       </c>
-      <c r="C158" t="s">
-        <v>97</v>
-      </c>
-      <c r="D158" t="s">
-        <v>172</v>
+      <c r="C158" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F158" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G158" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="159" spans="2:7" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F158" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="B159" s="1">
         <v>115</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C159" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F159" s="2">
+        <v>200000</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="160" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B160" s="1">
+        <v>115</v>
+      </c>
+      <c r="C160" t="s">
         <v>95</v>
-      </c>
-      <c r="D159" t="s">
-        <v>23</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F159" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G159" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="160" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B160" s="1">
-        <v>115</v>
-      </c>
-      <c r="C160" t="s">
-        <v>129</v>
       </c>
       <c r="D160" t="s">
         <v>23</v>
       </c>
-      <c r="E160" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F160" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G160" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="161" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E160" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F160" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G160" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H160" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="161" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B161" s="1">
         <v>115</v>
       </c>
       <c r="C161" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="D161" t="s">
         <v>23</v>
       </c>
-      <c r="E161" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F161" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G161" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="162" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E161" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F161" s="2">
+        <v>42393</v>
+      </c>
+      <c r="G161" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H161" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="162" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B162" s="1">
         <v>115</v>
       </c>
       <c r="C162" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="D162" t="s">
         <v>23</v>
@@ -13627,18 +13594,18 @@
         <v>170</v>
       </c>
       <c r="F162" s="11">
-        <v>3900</v>
+        <v>3500</v>
       </c>
       <c r="G162" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="163" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="163" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B163" s="1">
         <v>115</v>
       </c>
       <c r="C163" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="D163" t="s">
         <v>23</v>
@@ -13647,21 +13614,21 @@
         <v>170</v>
       </c>
       <c r="F163" s="11">
-        <v>8700</v>
+        <v>3500</v>
       </c>
       <c r="G163" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="164" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="164" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B164" s="1">
         <v>115</v>
       </c>
       <c r="C164" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="D164" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>170</v>
@@ -13673,312 +13640,321 @@
         <v>168</v>
       </c>
     </row>
-    <row r="165" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="165" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B165" s="1">
         <v>115</v>
       </c>
-      <c r="C165" t="s">
-        <v>72</v>
-      </c>
-      <c r="D165" t="s">
-        <v>23</v>
+      <c r="C165" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F165" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G165" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="166" spans="2:7" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="F165" s="2">
+        <v>44118</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="B166" s="1">
         <v>115</v>
       </c>
-      <c r="C166" t="s">
-        <v>71</v>
-      </c>
-      <c r="D166" t="s">
-        <v>173</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F166" s="11">
-        <v>3800</v>
-      </c>
-      <c r="G166" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="167" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C166" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F166" s="2">
+        <v>217500</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="167" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B167" s="1">
         <v>115</v>
       </c>
       <c r="C167" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D167" t="s">
-        <v>176</v>
+        <v>46</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F167" s="11">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="G167" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="168" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="168" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B168" s="1">
         <v>115</v>
       </c>
       <c r="C168" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="D168" t="s">
-        <v>23</v>
+        <v>175</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F168" s="11">
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="G168" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="169" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="169" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B169" s="1">
         <v>115</v>
       </c>
       <c r="C169" t="s">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="D169" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F169" s="11">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="G169" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="170" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B170" s="1">
         <v>115</v>
       </c>
-      <c r="C170" t="s">
-        <v>134</v>
-      </c>
-      <c r="D170" t="s">
-        <v>23</v>
+      <c r="C170" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F170" s="11">
-        <v>1500</v>
-      </c>
-      <c r="G170" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="171" spans="2:7" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F170" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B171" s="1">
         <v>115</v>
       </c>
-      <c r="C171" t="s">
-        <v>135</v>
-      </c>
-      <c r="D171" t="s">
-        <v>23</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F171" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G171" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="172" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C171" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F171" s="2">
+        <v>60000</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H171" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="172" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B172" s="1">
         <v>115</v>
       </c>
       <c r="C172" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="D172" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F172" s="11">
-        <v>3500</v>
+        <v>1400</v>
       </c>
       <c r="G172" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="173" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="173" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B173" s="1">
         <v>115</v>
       </c>
-      <c r="C173" t="s">
-        <v>27</v>
-      </c>
-      <c r="D173" t="s">
-        <v>23</v>
+      <c r="C173" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F173" s="11">
-        <v>3700</v>
-      </c>
-      <c r="G173" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="174" spans="2:7" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F173" s="2">
+        <v>52500</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="174" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B174" s="1">
         <v>115</v>
       </c>
-      <c r="C174" t="s">
-        <v>85</v>
-      </c>
-      <c r="D174" t="s">
-        <v>23</v>
+      <c r="C174" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F174" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G174" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="175" spans="2:7" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+      <c r="F174" s="2">
+        <v>52776</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="175" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B175" s="1">
         <v>115</v>
       </c>
       <c r="C175" t="s">
-        <v>136</v>
+        <v>48</v>
       </c>
       <c r="D175" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F175" s="11">
-        <v>3500</v>
+        <v>900</v>
       </c>
       <c r="G175" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="176" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="176" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B176" s="1">
         <v>115</v>
       </c>
-      <c r="C176" t="s">
-        <v>137</v>
-      </c>
-      <c r="D176" t="s">
+      <c r="C176" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F176" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G176" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="177" spans="2:7" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F176" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="177" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B177" s="1">
         <v>115</v>
       </c>
       <c r="C177" t="s">
-        <v>138</v>
+        <v>49</v>
       </c>
       <c r="D177" t="s">
         <v>23</v>
       </c>
-      <c r="E177" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F177" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G177" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="178" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E177" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F177" s="2">
+        <v>41616</v>
+      </c>
+      <c r="G177" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="178" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B178" s="1">
         <v>115</v>
       </c>
       <c r="C178" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="D178" t="s">
         <v>23</v>
       </c>
-      <c r="E178" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F178" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G178" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="179" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E178" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F178" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G178" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H178" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="179" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B179" s="1">
         <v>115</v>
       </c>
       <c r="C179" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="D179" t="s">
         <v>23</v>
       </c>
-      <c r="E179" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F179" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G179" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="180" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E179" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F179" s="2">
+        <v>38569</v>
+      </c>
+      <c r="G179" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H179" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="180" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B180" s="1">
         <v>115</v>
       </c>
       <c r="C180" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="D180" t="s">
         <v>23</v>
@@ -13987,18 +13963,18 @@
         <v>170</v>
       </c>
       <c r="F180" s="11">
-        <v>8700</v>
+        <v>5000</v>
       </c>
       <c r="G180" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="181" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="181" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B181" s="1">
         <v>115</v>
       </c>
       <c r="C181" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="D181" t="s">
         <v>23</v>
@@ -14007,41 +13983,41 @@
         <v>170</v>
       </c>
       <c r="F181" s="11">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="G181" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="182" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="182" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B182" s="1">
         <v>115</v>
       </c>
-      <c r="C182" t="s">
-        <v>49</v>
-      </c>
-      <c r="D182" t="s">
+      <c r="C182" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F182" s="11">
-        <v>5000</v>
-      </c>
-      <c r="G182" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="183" spans="2:7" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="F182" s="2">
+        <v>31500</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="183" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B183" s="1">
         <v>115</v>
       </c>
       <c r="C183" t="s">
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="D183" t="s">
-        <v>23</v>
+        <v>172</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>170</v>
@@ -14053,72 +14029,72 @@
         <v>168</v>
       </c>
     </row>
-    <row r="184" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="184" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B184" s="1">
         <v>115</v>
       </c>
-      <c r="C184" t="s">
-        <v>142</v>
-      </c>
-      <c r="D184" t="s">
-        <v>23</v>
+      <c r="C184" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F184" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G184" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="185" spans="2:7" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="F184" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B185" s="1">
         <v>115</v>
       </c>
       <c r="C185" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="D185" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F185" s="11">
-        <v>3500</v>
+        <v>5600</v>
       </c>
       <c r="G185" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="186" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="186" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="B186" s="1">
         <v>115</v>
       </c>
-      <c r="C186" t="s">
-        <v>14</v>
-      </c>
-      <c r="D186" t="s">
+      <c r="C186" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E186" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F186" s="11">
-        <v>7600</v>
-      </c>
-      <c r="G186" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="187" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E186" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F186" s="2">
+        <v>95912</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="187" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B187" s="1">
         <v>115</v>
       </c>
       <c r="C187" t="s">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="D187" t="s">
         <v>23</v>
@@ -14133,12 +14109,12 @@
         <v>168</v>
       </c>
     </row>
-    <row r="188" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="188" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B188" s="1">
         <v>115</v>
       </c>
       <c r="C188" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="D188" t="s">
         <v>23</v>
@@ -14147,38 +14123,38 @@
         <v>170</v>
       </c>
       <c r="F188" s="11">
-        <v>3900</v>
+        <v>3500</v>
       </c>
       <c r="G188" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="189" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="189" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="B189" s="1">
         <v>115</v>
       </c>
-      <c r="C189" t="s">
-        <v>6</v>
-      </c>
-      <c r="D189" t="s">
-        <v>23</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F189" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G189" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="190" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C189" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F189" s="2">
+        <v>28500</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="190" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B190" s="1">
         <v>115</v>
       </c>
       <c r="C190" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="D190" t="s">
         <v>23</v>
@@ -14187,18 +14163,18 @@
         <v>170</v>
       </c>
       <c r="F190" s="11">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="G190" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="191" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B191" s="1">
         <v>115</v>
       </c>
       <c r="C191" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D191" t="s">
         <v>23</v>
@@ -14213,12 +14189,12 @@
         <v>168</v>
       </c>
     </row>
-    <row r="192" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="192" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B192" s="1">
         <v>115</v>
       </c>
       <c r="C192" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D192" t="s">
         <v>23</v>
@@ -14233,12 +14209,12 @@
         <v>168</v>
       </c>
     </row>
-    <row r="193" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="193" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B193" s="1">
         <v>115</v>
       </c>
       <c r="C193" t="s">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="D193" t="s">
         <v>23</v>
@@ -14247,141 +14223,153 @@
         <v>170</v>
       </c>
       <c r="F193" s="11">
-        <v>7500</v>
+        <v>3500</v>
       </c>
       <c r="G193" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="194" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="194" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B194" s="1">
         <v>115</v>
       </c>
-      <c r="C194" t="s">
-        <v>147</v>
-      </c>
-      <c r="D194" t="s">
-        <v>23</v>
+      <c r="C194" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F194" s="11">
-        <v>6400</v>
-      </c>
-      <c r="G194" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="195" spans="2:7" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="F194" s="2">
+        <v>29250</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="195" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B195" s="1">
         <v>115</v>
       </c>
       <c r="C195" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="D195" t="s">
-        <v>23</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F195" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G195" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="196" spans="2:7" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="E195" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F195" s="2">
+        <v>8900</v>
+      </c>
+      <c r="G195" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H195" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="196" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B196" s="1">
         <v>115</v>
       </c>
       <c r="C196" t="s">
-        <v>149</v>
+        <v>52</v>
       </c>
       <c r="D196" t="s">
-        <v>23</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F196" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G196" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="197" spans="2:7" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="E196" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F196" s="2">
+        <v>0</v>
+      </c>
+      <c r="G196" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H196" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="197" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B197" s="1">
         <v>115</v>
       </c>
       <c r="C197" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D197" t="s">
-        <v>172</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F197" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G197" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="198" spans="2:7" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="E197" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F197" s="2">
+        <v>19190</v>
+      </c>
+      <c r="G197" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H197" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="198" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B198" s="1">
         <v>115</v>
       </c>
       <c r="C198" t="s">
-        <v>150</v>
+        <v>52</v>
       </c>
       <c r="D198" t="s">
-        <v>23</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F198" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G198" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="199" spans="2:7" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="E198" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F198" s="2">
+        <v>17728</v>
+      </c>
+      <c r="G198" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H198" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="199" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B199" s="1">
         <v>115</v>
       </c>
       <c r="C199" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="D199" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F199" s="11">
-        <v>3500</v>
+        <v>2200</v>
       </c>
       <c r="G199" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="200" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="200" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B200" s="1">
         <v>115</v>
       </c>
       <c r="C200" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D200" t="s">
-        <v>23</v>
+        <v>172</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>170</v>
@@ -14393,52 +14381,58 @@
         <v>168</v>
       </c>
     </row>
-    <row r="201" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="201" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B201" s="1">
         <v>115</v>
       </c>
       <c r="C201" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="D201" t="s">
         <v>23</v>
       </c>
-      <c r="E201" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F201" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G201" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="202" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E201" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F201" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G201" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H201" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="202" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B202" s="1">
         <v>115</v>
       </c>
       <c r="C202" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="D202" t="s">
         <v>23</v>
       </c>
-      <c r="E202" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F202" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G202" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="203" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E202" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F202" s="2">
+        <v>17600</v>
+      </c>
+      <c r="G202" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H202" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="203" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B203" s="1">
         <v>115</v>
       </c>
       <c r="C203" t="s">
-        <v>153</v>
+        <v>99</v>
       </c>
       <c r="D203" t="s">
         <v>23</v>
@@ -14447,18 +14441,18 @@
         <v>170</v>
       </c>
       <c r="F203" s="11">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="G203" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="204" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="204" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B204" s="1">
         <v>115</v>
       </c>
       <c r="C204" t="s">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="D204" t="s">
         <v>23</v>
@@ -14467,78 +14461,84 @@
         <v>170</v>
       </c>
       <c r="F204" s="11">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="G204" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="205" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="205" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B205" s="1">
         <v>115</v>
       </c>
-      <c r="C205" t="s">
-        <v>154</v>
-      </c>
-      <c r="D205" t="s">
+      <c r="C205" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F205" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G205" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="206" spans="2:7" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="F205" s="2">
+        <v>41384</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B206" s="1">
         <v>115</v>
       </c>
       <c r="C206" t="s">
-        <v>155</v>
+        <v>53</v>
       </c>
       <c r="D206" t="s">
         <v>23</v>
       </c>
-      <c r="E206" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F206" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G206" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="207" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E206" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F206" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G206" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H206" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="207" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B207" s="1">
         <v>115</v>
       </c>
       <c r="C207" t="s">
-        <v>156</v>
+        <v>53</v>
       </c>
       <c r="D207" t="s">
         <v>23</v>
       </c>
-      <c r="E207" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F207" s="11">
-        <v>5700</v>
-      </c>
-      <c r="G207" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="208" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E207" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F207" s="2">
+        <v>19200</v>
+      </c>
+      <c r="G207" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H207" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="208" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B208" s="1">
         <v>115</v>
       </c>
       <c r="C208" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="D208" t="s">
         <v>23</v>
@@ -14557,40 +14557,40 @@
       <c r="B209" s="1">
         <v>115</v>
       </c>
-      <c r="C209" t="s">
-        <v>158</v>
-      </c>
-      <c r="D209" t="s">
-        <v>23</v>
+      <c r="C209" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F209" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G209" t="s">
-        <v>168</v>
+        <v>7</v>
+      </c>
+      <c r="F209" s="2">
+        <v>56000</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="210" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B210" s="1">
         <v>115</v>
       </c>
-      <c r="C210" t="s">
-        <v>56</v>
-      </c>
-      <c r="D210" t="s">
-        <v>23</v>
+      <c r="C210" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F210" s="11">
-        <v>4100</v>
-      </c>
-      <c r="G210" t="s">
-        <v>168</v>
+        <v>83</v>
+      </c>
+      <c r="F210" s="2">
+        <v>48284</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="211" spans="2:7" x14ac:dyDescent="0.35">
@@ -14598,16 +14598,16 @@
         <v>115</v>
       </c>
       <c r="C211" t="s">
-        <v>159</v>
+        <v>54</v>
       </c>
       <c r="D211" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F211" s="11">
-        <v>3500</v>
+        <v>6300</v>
       </c>
       <c r="G211" t="s">
         <v>168</v>
@@ -14617,20 +14617,20 @@
       <c r="B212" s="1">
         <v>115</v>
       </c>
-      <c r="C212" t="s">
-        <v>160</v>
-      </c>
-      <c r="D212" t="s">
-        <v>172</v>
+      <c r="C212" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F212" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G212" t="s">
-        <v>168</v>
+        <v>21</v>
+      </c>
+      <c r="F212" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="213" spans="2:7" x14ac:dyDescent="0.35">
@@ -14638,16 +14638,16 @@
         <v>115</v>
       </c>
       <c r="C213" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="D213" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F213" s="11">
-        <v>10000</v>
+        <v>5600</v>
       </c>
       <c r="G213" t="s">
         <v>168</v>
@@ -14657,20 +14657,20 @@
       <c r="B214" s="1">
         <v>115</v>
       </c>
-      <c r="C214" t="s">
-        <v>17</v>
-      </c>
-      <c r="D214" t="s">
-        <v>13</v>
+      <c r="C214" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F214" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G214" t="s">
-        <v>168</v>
+        <v>21</v>
+      </c>
+      <c r="F214" s="2">
+        <v>41770</v>
+      </c>
+      <c r="G214" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="215" spans="2:7" x14ac:dyDescent="0.35">
@@ -14678,16 +14678,16 @@
         <v>115</v>
       </c>
       <c r="C215" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="D215" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F215" s="11">
-        <v>7200</v>
+        <v>4100</v>
       </c>
       <c r="G215" t="s">
         <v>168</v>
@@ -14697,20 +14697,20 @@
       <c r="B216" s="1">
         <v>115</v>
       </c>
-      <c r="C216" t="s">
-        <v>74</v>
-      </c>
-      <c r="D216" t="s">
-        <v>171</v>
+      <c r="C216" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F216" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G216" t="s">
-        <v>168</v>
+        <v>7</v>
+      </c>
+      <c r="F216" s="2">
+        <v>45000</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="217" spans="2:7" x14ac:dyDescent="0.35">
@@ -14718,19 +14718,19 @@
         <v>115</v>
       </c>
       <c r="C217" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D217" t="s">
-        <v>13</v>
-      </c>
-      <c r="E217" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F217" s="11">
-        <v>900</v>
-      </c>
-      <c r="G217" t="s">
-        <v>168</v>
+        <v>86</v>
+      </c>
+      <c r="E217" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F217" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G217" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="218" spans="2:7" x14ac:dyDescent="0.35">
@@ -14738,16 +14738,16 @@
         <v>115</v>
       </c>
       <c r="C218" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="D218" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F218" s="11">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="G218" t="s">
         <v>168</v>
@@ -14758,16 +14758,16 @@
         <v>115</v>
       </c>
       <c r="C219" t="s">
-        <v>54</v>
+        <v>152</v>
       </c>
       <c r="D219" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F219" s="11">
-        <v>6300</v>
+        <v>3500</v>
       </c>
       <c r="G219" t="s">
         <v>168</v>
@@ -14778,16 +14778,16 @@
         <v>115</v>
       </c>
       <c r="C220" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="D220" t="s">
-        <v>177</v>
+        <v>23</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F220" s="11">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G220" t="s">
         <v>168</v>
@@ -14797,20 +14797,20 @@
       <c r="B221" s="1">
         <v>115</v>
       </c>
-      <c r="C221" t="s">
-        <v>161</v>
-      </c>
-      <c r="D221" t="s">
-        <v>177</v>
+      <c r="C221" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F221" s="11">
-        <v>500</v>
-      </c>
-      <c r="G221" t="s">
-        <v>168</v>
+        <v>83</v>
+      </c>
+      <c r="F221" s="2">
+        <v>39125</v>
+      </c>
+      <c r="G221" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="222" spans="2:7" x14ac:dyDescent="0.35">
@@ -14818,16 +14818,16 @@
         <v>115</v>
       </c>
       <c r="C222" t="s">
-        <v>162</v>
+        <v>65</v>
       </c>
       <c r="D222" t="s">
-        <v>177</v>
+        <v>23</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F222" s="11">
-        <v>400</v>
+        <v>7500</v>
       </c>
       <c r="G222" t="s">
         <v>168</v>
@@ -14838,16 +14838,16 @@
         <v>115</v>
       </c>
       <c r="C223" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D223" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F223" s="11">
-        <v>7200</v>
+        <v>5200</v>
       </c>
       <c r="G223" t="s">
         <v>168</v>
@@ -14858,7 +14858,7 @@
         <v>115</v>
       </c>
       <c r="C224" t="s">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="D224" t="s">
         <v>40</v>
@@ -14867,7 +14867,7 @@
         <v>170</v>
       </c>
       <c r="F224" s="11">
-        <v>900</v>
+        <v>5200</v>
       </c>
       <c r="G224" t="s">
         <v>168</v>
@@ -14877,60 +14877,60 @@
       <c r="B225" s="1">
         <v>115</v>
       </c>
-      <c r="C225" t="s">
-        <v>164</v>
-      </c>
-      <c r="D225" t="s">
-        <v>173</v>
+      <c r="C225" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F225" s="11">
-        <v>5200</v>
-      </c>
-      <c r="G225" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="226" spans="2:7" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F225" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G225" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="226" spans="2:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="B226" s="1">
         <v>115</v>
       </c>
-      <c r="C226" t="s">
-        <v>165</v>
-      </c>
-      <c r="D226" t="s">
-        <v>40</v>
-      </c>
-      <c r="E226" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F226" s="11">
-        <v>5200</v>
-      </c>
-      <c r="G226" t="s">
-        <v>168</v>
+      <c r="C226" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F226" s="2">
+        <v>221000</v>
+      </c>
+      <c r="G226" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="227" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B227" s="1">
         <v>115</v>
       </c>
-      <c r="C227" t="s">
-        <v>47</v>
-      </c>
-      <c r="D227" t="s">
-        <v>46</v>
+      <c r="C227" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F227" s="11">
-        <v>1400</v>
-      </c>
-      <c r="G227" t="s">
-        <v>168</v>
+        <v>83</v>
+      </c>
+      <c r="F227" s="2">
+        <v>26283</v>
+      </c>
+      <c r="G227" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="228" spans="2:7" x14ac:dyDescent="0.35">
@@ -14938,39 +14938,39 @@
         <v>115</v>
       </c>
       <c r="C228" t="s">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="D228" t="s">
-        <v>175</v>
+        <v>60</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F228" s="11">
-        <v>6000</v>
-      </c>
-      <c r="G228" t="s">
-        <v>168</v>
+        <v>1100</v>
+      </c>
+      <c r="G228" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="229" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B229" s="1">
         <v>115</v>
       </c>
-      <c r="C229" t="s">
-        <v>45</v>
-      </c>
-      <c r="D229" t="s">
-        <v>46</v>
+      <c r="C229" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F229" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G229" t="s">
-        <v>168</v>
+        <v>11</v>
+      </c>
+      <c r="F229" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G229" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="230" spans="2:7" x14ac:dyDescent="0.35">
@@ -14978,25 +14978,24 @@
         <v>115</v>
       </c>
       <c r="C230" t="s">
-        <v>167</v>
+        <v>59</v>
       </c>
       <c r="D230" t="s">
-        <v>174</v>
+        <v>60</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F230" s="11">
-        <v>1400</v>
+        <v>2700</v>
       </c>
       <c r="G230" t="s">
         <v>168</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H128" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:H128">
-    <sortCondition ref="C2:C128"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:H230">
+    <sortCondition ref="C2:C230"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F5D769-1152-44A6-ADEE-3E43A3AA58BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB39575-CDA4-4C76-AB69-5C67B62D07BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$H$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$H$133</definedName>
     <definedName name="Barcode">OFFSET(#REF!,MATCH(#REF!,#REF!,0)-1,0)</definedName>
     <definedName name="重大活動行事曆">[1]重要活動行事曆!$C$2:$I$467</definedName>
     <definedName name="資料">#REF!</definedName>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="187">
   <si>
     <t>序號</t>
   </si>
@@ -671,6 +671,362 @@
   <si>
     <t>參加國際研討會並發表_研習報名(註冊)費</t>
   </si>
+  <si>
+    <t>獎勵教師輔導學生獲取國家或國際證照</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>獎勵教師指導學 生參與校外競賽獲獎</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>指導學生參加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2026IFA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>國際時尚美學創意競賽，榮獲國際創意飾品設計（平面）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>金牌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>指導學生參加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>屆美國</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>MNS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>國際菁英盃競賽，榮獲創意塗鴉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>冠軍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>指導學生參加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>悅色技藝美學大賞，榮獲乙級華麗新娘妝紙圖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>冠軍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>指導學生參加第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>屆（線上靜態組）全國暨國際形象美學創意設計競賽，榮獲文創商品設計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>第一名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>指導學生參加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2025TICCPA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>國際菁英盃競賽，榮獲乙級華麗新娘紙圖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>冠軍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -680,7 +1036,7 @@
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
     <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -918,6 +1274,19 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="33">
@@ -9893,7 +10262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BAC909-8D45-4443-AECB-1592B366F0B1}">
-  <dimension ref="A1:H230"/>
+  <dimension ref="A1:H235"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="4.75" bestFit="1" customWidth="1"/>
@@ -10661,7 +11030,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -10684,7 +11053,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -10707,7 +11076,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -10730,7 +11099,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -10753,7 +11122,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -10776,7 +11145,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -10799,7 +11168,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -10822,7 +11191,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -10836,7 +11205,7 @@
         <v>16</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F40" s="11">
         <v>10000</v>
@@ -10845,879 +11214,873 @@
         <v>168</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>40</v>
-      </c>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B41" s="1">
         <v>115</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F41" s="2">
-        <v>31500</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>41</v>
-      </c>
+      <c r="C41" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" t="s">
+        <v>181</v>
+      </c>
+      <c r="F41" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H41" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B42" s="1">
         <v>115</v>
       </c>
       <c r="C42" t="s">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="D42" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>170</v>
+        <v>16</v>
+      </c>
+      <c r="E42" t="s">
+        <v>181</v>
       </c>
       <c r="F42" s="11">
         <v>10000</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G42" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H42" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B43" s="1">
+        <v>115</v>
+      </c>
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" t="s">
+        <v>181</v>
+      </c>
+      <c r="F43" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H43" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B44" s="1">
+        <v>115</v>
+      </c>
+      <c r="C44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" t="s">
+        <v>181</v>
+      </c>
+      <c r="F44" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H44" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B45" s="1">
+        <v>115</v>
+      </c>
+      <c r="C45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" t="s">
+        <v>181</v>
+      </c>
+      <c r="F45" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H45" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>40</v>
+      </c>
+      <c r="B46" s="1">
+        <v>115</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F46" s="2">
+        <v>31500</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>41</v>
+      </c>
+      <c r="B47" s="1">
+        <v>115</v>
+      </c>
+      <c r="C47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D47" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F47" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G47" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48">
         <v>42</v>
       </c>
-      <c r="B43" s="1">
-        <v>115</v>
-      </c>
-      <c r="C43" s="1" t="s">
+      <c r="B48" s="1">
+        <v>115</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F48" s="2">
         <v>59500</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49">
         <v>43</v>
       </c>
-      <c r="B44" s="1">
-        <v>115</v>
-      </c>
-      <c r="C44" s="1" t="s">
+      <c r="B49" s="1">
+        <v>115</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F49" s="2">
         <v>20564</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G49" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50">
         <v>44</v>
       </c>
-      <c r="B45" s="1">
-        <v>115</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B50" s="1">
+        <v>115</v>
+      </c>
+      <c r="C50" t="s">
         <v>22</v>
-      </c>
-      <c r="D45" t="s">
-        <v>23</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F45" s="2">
-        <v>45000</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" s="1">
-        <v>115</v>
-      </c>
-      <c r="C46" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" t="s">
-        <v>23</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F46" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G46" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" s="1">
-        <v>115</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" s="2">
-        <v>51750</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" s="1">
-        <v>115</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F48" s="2">
-        <v>47687</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" s="1">
-        <v>115</v>
-      </c>
-      <c r="C49" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F49" s="11">
-        <v>7200</v>
-      </c>
-      <c r="G49" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" s="1">
-        <v>115</v>
-      </c>
-      <c r="C50" t="s">
-        <v>134</v>
       </c>
       <c r="D50" t="s">
         <v>23</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F50" s="2">
+        <v>45000</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>45</v>
+      </c>
+      <c r="B51" s="1">
+        <v>115</v>
+      </c>
+      <c r="C51" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F50" s="11">
-        <v>1500</v>
-      </c>
-      <c r="G50" t="s">
+      <c r="F51" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G51" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" s="1">
-        <v>115</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F51" s="2">
-        <v>42500</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B52" s="1">
         <v>115</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F52" s="2">
-        <v>63000</v>
+        <v>51750</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B53" s="1">
         <v>115</v>
       </c>
-      <c r="C53" t="s">
-        <v>25</v>
-      </c>
-      <c r="D53" t="s">
-        <v>16</v>
+      <c r="C53" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F53" s="11">
-        <v>5600</v>
-      </c>
-      <c r="G53" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+      <c r="F53" s="2">
+        <v>47687</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B54" s="1">
         <v>115</v>
       </c>
       <c r="C54" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="D54" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F54" s="11">
-        <v>3500</v>
+        <v>7200</v>
       </c>
       <c r="G54" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B55" s="1">
         <v>115</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>20</v>
+      <c r="C55" t="s">
+        <v>134</v>
+      </c>
+      <c r="D55" t="s">
+        <v>23</v>
       </c>
       <c r="E55" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F55" s="11">
+        <v>1500</v>
+      </c>
+      <c r="G55" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>50</v>
+      </c>
+      <c r="B56" s="1">
+        <v>115</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F55" s="2">
-        <v>17000</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" s="1">
-        <v>115</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F56" s="2">
-        <v>60000</v>
+        <v>42500</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B57" s="1">
         <v>115</v>
       </c>
-      <c r="C57" t="s">
-        <v>26</v>
-      </c>
-      <c r="D57" t="s">
-        <v>86</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>87</v>
+      <c r="C57" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F57" s="2">
-        <v>47500</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+        <v>63000</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B58" s="1">
         <v>115</v>
       </c>
       <c r="C58" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F58" s="11">
-        <v>8400</v>
+        <v>5600</v>
       </c>
       <c r="G58" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59">
+        <v>53</v>
+      </c>
+      <c r="B59" s="1">
+        <v>115</v>
+      </c>
+      <c r="C59" t="s">
+        <v>135</v>
+      </c>
+      <c r="D59" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F59" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G59" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>54</v>
+      </c>
+      <c r="B60" s="1">
+        <v>115</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F60" s="2">
+        <v>17000</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>55</v>
+      </c>
+      <c r="B61" s="1">
+        <v>115</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="2">
+        <v>60000</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>56</v>
+      </c>
+      <c r="B62" s="1">
+        <v>115</v>
+      </c>
+      <c r="C62" t="s">
+        <v>26</v>
+      </c>
+      <c r="D62" t="s">
+        <v>86</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F62" s="2">
+        <v>47500</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>57</v>
+      </c>
+      <c r="B63" s="1">
+        <v>115</v>
+      </c>
+      <c r="C63" t="s">
+        <v>26</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F63" s="11">
+        <v>8400</v>
+      </c>
+      <c r="G63" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64">
         <v>58</v>
       </c>
-      <c r="B59" s="1">
-        <v>115</v>
-      </c>
-      <c r="C59" s="1" t="s">
+      <c r="B64" s="1">
+        <v>115</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="E64" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F64" s="2">
         <v>50000</v>
       </c>
-      <c r="G59" s="9" t="s">
+      <c r="G64" s="9" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A65">
         <v>59</v>
       </c>
-      <c r="B60" s="1">
-        <v>115</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="B65" s="1">
+        <v>115</v>
+      </c>
+      <c r="C65" t="s">
         <v>85</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D65" t="s">
         <v>23</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E65" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F65" s="2">
         <v>30850</v>
       </c>
-      <c r="G60" s="10" t="s">
+      <c r="G65" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H65" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" s="1">
-        <v>115</v>
-      </c>
-      <c r="C61" t="s">
-        <v>85</v>
-      </c>
-      <c r="D61" t="s">
-        <v>23</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F61" s="2">
-        <v>9696</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H61" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" s="1">
-        <v>115</v>
-      </c>
-      <c r="C62" t="s">
-        <v>85</v>
-      </c>
-      <c r="D62" t="s">
-        <v>23</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F62" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G62" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" s="1">
-        <v>115</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" s="1">
-        <v>115</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F64" s="2">
-        <v>32320</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H64" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" s="1">
-        <v>115</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F65" s="2">
-        <v>140000</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B66" s="1">
         <v>115</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D66" s="1" t="s">
+      <c r="C66" t="s">
+        <v>85</v>
+      </c>
+      <c r="D66" t="s">
         <v>23</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>83</v>
+      <c r="E66" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="F66" s="2">
-        <v>28884</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>84</v>
+        <v>9696</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H66" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B67" s="1">
         <v>115</v>
       </c>
       <c r="C67" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="D67" t="s">
         <v>23</v>
       </c>
-      <c r="E67" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F67" s="2">
-        <v>30850</v>
-      </c>
-      <c r="G67" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H67" t="s">
-        <v>101</v>
+      <c r="E67" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F67" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G67" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B68" s="1">
         <v>115</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E68" s="10" t="s">
-        <v>178</v>
+      <c r="E68" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F68" s="2">
-        <v>19150</v>
-      </c>
-      <c r="G68" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H68" t="s">
-        <v>106</v>
+        <v>59500</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B69" s="1">
         <v>115</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F69" s="2">
+        <v>32320</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H69" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>64</v>
+      </c>
+      <c r="B70" s="1">
+        <v>115</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D70" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E69" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F69" s="2">
-        <v>12936</v>
-      </c>
-      <c r="G69" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H69" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" s="1">
-        <v>115</v>
-      </c>
-      <c r="C70" t="s">
-        <v>27</v>
-      </c>
-      <c r="D70" t="s">
-        <v>23</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>179</v>
+      <c r="E70" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F70" s="2">
-        <v>31462</v>
-      </c>
-      <c r="G70" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H70" t="s">
-        <v>106</v>
+        <v>140000</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B71" s="1">
         <v>115</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F71" s="11">
-        <v>3700</v>
-      </c>
-      <c r="G71" t="s">
-        <v>168</v>
+        <v>83</v>
+      </c>
+      <c r="F71" s="2">
+        <v>28884</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B72" s="1">
         <v>115</v>
       </c>
       <c r="C72" t="s">
-        <v>136</v>
+        <v>27</v>
       </c>
       <c r="D72" t="s">
         <v>23</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F72" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G72" t="s">
-        <v>168</v>
+      <c r="E72" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F72" s="2">
+        <v>30850</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H72" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B73" s="1">
         <v>115</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>7</v>
+      <c r="C73" t="s">
+        <v>27</v>
+      </c>
+      <c r="D73" t="s">
+        <v>23</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="F73" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>19150</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H73" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B74" s="1">
         <v>115</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>81</v>
+      <c r="C74" t="s">
+        <v>27</v>
+      </c>
+      <c r="D74" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="F74" s="2">
-        <v>150000</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>82</v>
+        <v>12936</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H74" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B75" s="1">
         <v>115</v>
       </c>
       <c r="C75" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D75" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F75" s="2">
-        <v>17789</v>
+        <v>31462</v>
       </c>
       <c r="G75" s="10" t="s">
         <v>117</v>
       </c>
       <c r="H75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B76" s="1">
         <v>115</v>
       </c>
       <c r="C76" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D76" t="s">
-        <v>29</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F76" s="2">
-        <v>8085</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H76" t="s">
-        <v>107</v>
+        <v>23</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F76" s="11">
+        <v>3700</v>
+      </c>
+      <c r="G76" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B77" s="1">
         <v>115</v>
       </c>
       <c r="C77" t="s">
-        <v>28</v>
+        <v>136</v>
       </c>
       <c r="D77" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F77" s="11">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="G77" t="s">
         <v>168</v>
@@ -11725,114 +12088,120 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B78" s="1">
         <v>115</v>
       </c>
-      <c r="C78" t="s">
-        <v>132</v>
-      </c>
-      <c r="D78" t="s">
-        <v>23</v>
+      <c r="C78" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F78" s="11">
-        <v>8700</v>
-      </c>
-      <c r="G78" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F78" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B79" s="1">
         <v>115</v>
       </c>
-      <c r="C79" t="s">
-        <v>141</v>
-      </c>
-      <c r="D79" t="s">
-        <v>23</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F79" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G79" t="s">
-        <v>168</v>
+      <c r="C79" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F79" s="2">
+        <v>150000</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B80" s="1">
         <v>115</v>
       </c>
       <c r="C80" t="s">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="D80" t="s">
-        <v>23</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F80" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G80" t="s">
-        <v>168</v>
+        <v>29</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F80" s="2">
+        <v>17789</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H80" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B81" s="1">
         <v>115</v>
       </c>
       <c r="C81" t="s">
-        <v>125</v>
+        <v>28</v>
       </c>
       <c r="D81" t="s">
-        <v>20</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F81" s="11">
-        <v>9600</v>
-      </c>
-      <c r="G81" t="s">
-        <v>168</v>
+        <v>29</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F81" s="2">
+        <v>8085</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H81" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B82" s="1">
         <v>115</v>
       </c>
       <c r="C82" t="s">
-        <v>138</v>
+        <v>28</v>
       </c>
       <c r="D82" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F82" s="11">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="G82" t="s">
         <v>168</v>
@@ -11840,13 +12209,13 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B83" s="1">
         <v>115</v>
       </c>
       <c r="C83" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D83" t="s">
         <v>23</v>
@@ -11855,7 +12224,7 @@
         <v>170</v>
       </c>
       <c r="F83" s="11">
-        <v>10000</v>
+        <v>8700</v>
       </c>
       <c r="G83" t="s">
         <v>168</v>
@@ -11863,22 +12232,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B84" s="1">
         <v>115</v>
       </c>
       <c r="C84" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="D84" t="s">
-        <v>177</v>
+        <v>23</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F84" s="11">
-        <v>400</v>
+        <v>3500</v>
       </c>
       <c r="G84" t="s">
         <v>168</v>
@@ -11886,22 +12255,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B85" s="1">
         <v>115</v>
       </c>
       <c r="C85" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="D85" t="s">
-        <v>177</v>
+        <v>23</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F85" s="11">
-        <v>500</v>
+        <v>3500</v>
       </c>
       <c r="G85" t="s">
         <v>168</v>
@@ -11909,22 +12278,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B86" s="1">
         <v>115</v>
       </c>
       <c r="C86" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D86" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F86" s="11">
-        <v>8700</v>
+        <v>9600</v>
       </c>
       <c r="G86" t="s">
         <v>168</v>
@@ -11932,45 +12301,45 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B87" s="1">
         <v>115</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>60</v>
+      <c r="C87" t="s">
+        <v>138</v>
+      </c>
+      <c r="D87" t="s">
+        <v>23</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F87" s="2">
-        <v>11185</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>84</v>
+        <v>170</v>
+      </c>
+      <c r="F87" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G87" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B88" s="1">
         <v>115</v>
       </c>
       <c r="C88" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D88" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F88" s="11">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="G88" t="s">
         <v>168</v>
@@ -11978,603 +12347,603 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B89" s="1">
         <v>115</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>23</v>
+      <c r="C89" t="s">
+        <v>162</v>
+      </c>
+      <c r="D89" t="s">
+        <v>177</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F89" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F89" s="11">
+        <v>400</v>
+      </c>
+      <c r="G89" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B90" s="1">
         <v>115</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>23</v>
+      <c r="C90" t="s">
+        <v>161</v>
+      </c>
+      <c r="D90" t="s">
+        <v>177</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F90" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F90" s="11">
+        <v>500</v>
+      </c>
+      <c r="G90" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B91" s="1">
         <v>115</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D91" s="1" t="s">
+      <c r="C91" t="s">
+        <v>140</v>
+      </c>
+      <c r="D91" t="s">
         <v>23</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F91" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F91" s="11">
+        <v>8700</v>
+      </c>
+      <c r="G91" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B92" s="1">
         <v>115</v>
       </c>
-      <c r="C92" t="s">
-        <v>30</v>
-      </c>
-      <c r="D92" t="s">
-        <v>23</v>
+      <c r="C92" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F92" s="11">
-        <v>5000</v>
-      </c>
-      <c r="G92" t="s">
-        <v>168</v>
+        <v>83</v>
+      </c>
+      <c r="F92" s="2">
+        <v>11185</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B93" s="1">
         <v>115</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>23</v>
+      <c r="C93" t="s">
+        <v>124</v>
+      </c>
+      <c r="D93" t="s">
+        <v>20</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F93" s="2">
-        <v>70000</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F93" s="11">
+        <v>2500</v>
+      </c>
+      <c r="G93" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B94" s="1">
         <v>115</v>
       </c>
-      <c r="C94" t="s">
-        <v>31</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="C94" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E94" s="8" t="s">
-        <v>87</v>
+      <c r="E94" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F94" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G94" s="9" t="s">
-        <v>88</v>
+        <v>59500</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B95" s="1">
         <v>115</v>
       </c>
-      <c r="C95" t="s">
-        <v>31</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="C95" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F95" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G95" t="s">
-        <v>168</v>
+        <v>11</v>
+      </c>
+      <c r="F95" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B96" s="1">
         <v>115</v>
       </c>
-      <c r="C96" t="s">
-        <v>97</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="C96" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E96" s="10" t="s">
-        <v>178</v>
+      <c r="E96" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="F96" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G96" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H96" t="s">
-        <v>111</v>
+        <v>40000</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B97" s="1">
         <v>115</v>
       </c>
       <c r="C97" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="D97" t="s">
         <v>23</v>
       </c>
-      <c r="E97" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F97" s="2">
-        <v>38015</v>
-      </c>
-      <c r="G97" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H97" t="s">
-        <v>111</v>
+      <c r="E97" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F97" s="11">
+        <v>5000</v>
+      </c>
+      <c r="G97" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B98" s="1">
         <v>115</v>
       </c>
-      <c r="C98" t="s">
-        <v>97</v>
-      </c>
-      <c r="D98" t="s">
-        <v>172</v>
+      <c r="C98" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F98" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G98" t="s">
-        <v>168</v>
+        <v>7</v>
+      </c>
+      <c r="F98" s="2">
+        <v>70000</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B99" s="1">
         <v>115</v>
       </c>
       <c r="C99" t="s">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="D99" t="s">
         <v>23</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F99" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G99" t="s">
-        <v>168</v>
+      <c r="E99" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F99" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B100" s="1">
         <v>115</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>13</v>
+      <c r="C100" t="s">
+        <v>31</v>
+      </c>
+      <c r="D100" t="s">
+        <v>23</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F100" s="2">
-        <v>56000</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F100" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G100" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B101" s="1">
         <v>115</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>83</v>
+      <c r="C101" t="s">
+        <v>97</v>
+      </c>
+      <c r="D101" t="s">
+        <v>23</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="F101" s="2">
-        <v>39355</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>84</v>
+        <v>50000</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H101" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B102" s="1">
         <v>115</v>
       </c>
       <c r="C102" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="D102" t="s">
-        <v>13</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F102" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G102" t="s">
-        <v>168</v>
+        <v>23</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F102" s="2">
+        <v>38015</v>
+      </c>
+      <c r="G102" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H102" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B103" s="1">
         <v>115</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>10</v>
+      <c r="C103" t="s">
+        <v>97</v>
+      </c>
+      <c r="D103" t="s">
+        <v>172</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F103" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G103" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B104" s="1">
         <v>115</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>10</v>
+      <c r="C104" t="s">
+        <v>128</v>
+      </c>
+      <c r="D104" t="s">
+        <v>23</v>
       </c>
       <c r="E104" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F104" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G104" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>99</v>
+      </c>
+      <c r="B105" s="1">
+        <v>115</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F104" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G104" s="1" t="s">
+      <c r="F105" s="2">
+        <v>56000</v>
+      </c>
+      <c r="G105" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="A105">
-        <v>104</v>
-      </c>
-      <c r="B105" s="1">
-        <v>115</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F105" s="2">
-        <v>106530</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B106" s="1">
         <v>115</v>
       </c>
-      <c r="C106" t="s">
-        <v>33</v>
-      </c>
-      <c r="D106" t="s">
-        <v>10</v>
-      </c>
-      <c r="E106" s="10" t="s">
-        <v>178</v>
+      <c r="C106" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F106" s="2">
-        <v>19942</v>
-      </c>
-      <c r="G106" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H106" t="s">
-        <v>109</v>
+        <v>39355</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B107" s="1">
         <v>115</v>
       </c>
       <c r="C107" t="s">
+        <v>32</v>
+      </c>
+      <c r="D107" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F107" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G107" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>102</v>
+      </c>
+      <c r="B108" s="1">
+        <v>115</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D108" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E107" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F107" s="2">
-        <v>16447</v>
-      </c>
-      <c r="G107" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H107" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="A108">
-        <v>107</v>
-      </c>
-      <c r="B108" s="1">
-        <v>115</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D108" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>81</v>
+      <c r="E108" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F108" s="2">
-        <v>117750</v>
+        <v>59500</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B109" s="1">
         <v>115</v>
       </c>
-      <c r="C109" t="s">
-        <v>74</v>
-      </c>
-      <c r="D109" t="s">
-        <v>171</v>
+      <c r="C109" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F109" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G109" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F109" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A110">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B110" s="1">
         <v>115</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F110" s="2">
-        <v>59500</v>
+        <v>106530</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B111" s="1">
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D111" t="s">
-        <v>29</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F111" s="11">
-        <v>6000</v>
-      </c>
-      <c r="G111" t="s">
-        <v>168</v>
+        <v>10</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F111" s="2">
+        <v>19942</v>
+      </c>
+      <c r="G111" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H111" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B112" s="1">
         <v>115</v>
       </c>
       <c r="C112" t="s">
-        <v>147</v>
+        <v>33</v>
       </c>
       <c r="D112" t="s">
-        <v>23</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F112" s="11">
-        <v>6400</v>
-      </c>
-      <c r="G112" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F112" s="2">
+        <v>16447</v>
+      </c>
+      <c r="G112" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H112" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A113">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B113" s="1">
         <v>115</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F113" s="2">
-        <v>23014</v>
+        <v>117750</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B114" s="1">
         <v>115</v>
       </c>
       <c r="C114" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D114" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>170</v>
@@ -12588,68 +12957,68 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B115" s="1">
         <v>115</v>
       </c>
-      <c r="C115" t="s">
-        <v>133</v>
-      </c>
-      <c r="D115" t="s">
-        <v>23</v>
+      <c r="C115" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="E115" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F115" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>110</v>
+      </c>
+      <c r="B116" s="1">
+        <v>115</v>
+      </c>
+      <c r="C116" t="s">
+        <v>34</v>
+      </c>
+      <c r="D116" t="s">
+        <v>29</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F115" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G115" t="s">
+      <c r="F116" s="11">
+        <v>6000</v>
+      </c>
+      <c r="G116" t="s">
         <v>168</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="A116">
-        <v>115</v>
-      </c>
-      <c r="B116" s="1">
-        <v>115</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F116" s="2">
-        <v>300000</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B117" s="1">
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>71</v>
+        <v>147</v>
       </c>
       <c r="D117" t="s">
-        <v>173</v>
+        <v>23</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F117" s="11">
-        <v>3800</v>
+        <v>6400</v>
       </c>
       <c r="G117" t="s">
         <v>168</v>
@@ -12657,206 +13026,206 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B118" s="1">
         <v>115</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="F118" s="2">
-        <v>59500</v>
+        <v>23014</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B119" s="1">
         <v>115</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D119" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F119" s="2">
-        <v>255000</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>82</v>
+      <c r="C119" t="s">
+        <v>69</v>
+      </c>
+      <c r="D119" t="s">
+        <v>23</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F119" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G119" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B120" s="1">
         <v>115</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>16</v>
+      <c r="C120" t="s">
+        <v>133</v>
+      </c>
+      <c r="D120" t="s">
+        <v>23</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F120" s="2">
-        <v>8285</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F120" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G120" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A121">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B121" s="1">
         <v>115</v>
       </c>
-      <c r="C121" t="s">
-        <v>35</v>
-      </c>
-      <c r="D121" t="s">
-        <v>16</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F121" s="11">
-        <v>9400</v>
-      </c>
-      <c r="G121" t="s">
-        <v>168</v>
+      <c r="C121" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F121" s="2">
+        <v>300000</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B122" s="1">
         <v>115</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>23</v>
+      <c r="C122" t="s">
+        <v>71</v>
+      </c>
+      <c r="D122" t="s">
+        <v>173</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F122" s="2">
-        <v>51000</v>
-      </c>
-      <c r="G122" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F122" s="11">
+        <v>3800</v>
+      </c>
+      <c r="G122" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>117</v>
+      </c>
+      <c r="B123" s="1">
+        <v>115</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G123" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="A123">
-        <v>122</v>
-      </c>
-      <c r="B123" s="1">
-        <v>115</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E123" s="3" t="s">
+    <row r="124" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>118</v>
+      </c>
+      <c r="B124" s="1">
+        <v>115</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E124" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F123" s="2">
-        <v>250000</v>
-      </c>
-      <c r="G123" s="1" t="s">
+      <c r="F124" s="2">
+        <v>255000</v>
+      </c>
+      <c r="G124" s="1" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A124">
-        <v>123</v>
-      </c>
-      <c r="B124" s="1">
-        <v>115</v>
-      </c>
-      <c r="C124" t="s">
-        <v>36</v>
-      </c>
-      <c r="D124" t="s">
-        <v>176</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F124" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G124" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B125" s="1">
         <v>115</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="F125" s="2">
-        <v>20368</v>
+        <v>8285</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B126" s="1">
         <v>115</v>
       </c>
       <c r="C126" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D126" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F126" s="11">
-        <v>3500</v>
+        <v>9400</v>
       </c>
       <c r="G126" t="s">
         <v>168</v>
@@ -12864,622 +13233,637 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B127" s="1">
         <v>115</v>
       </c>
-      <c r="C127" t="s">
-        <v>163</v>
-      </c>
-      <c r="D127" t="s">
-        <v>174</v>
+      <c r="C127" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F127" s="11">
-        <v>7200</v>
-      </c>
-      <c r="G127" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F127" s="2">
+        <v>51000</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A128">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B128" s="1">
         <v>115</v>
       </c>
-      <c r="C128" t="s">
-        <v>150</v>
-      </c>
-      <c r="D128" t="s">
+      <c r="C128" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E128" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F128" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G128" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="129" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E128" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F128" s="2">
+        <v>250000</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>123</v>
+      </c>
       <c r="B129" s="1">
         <v>115</v>
       </c>
       <c r="C129" t="s">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="D129" t="s">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F129" s="11">
-        <v>5600</v>
+        <v>3500</v>
       </c>
       <c r="G129" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>124</v>
+      </c>
       <c r="B130" s="1">
         <v>115</v>
       </c>
-      <c r="C130" t="s">
-        <v>156</v>
-      </c>
-      <c r="D130" t="s">
+      <c r="C130" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F130" s="11">
-        <v>5700</v>
-      </c>
-      <c r="G130" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="F130" s="2">
+        <v>20368</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>125</v>
+      </c>
       <c r="B131" s="1">
         <v>115</v>
       </c>
       <c r="C131" t="s">
-        <v>167</v>
+        <v>37</v>
       </c>
       <c r="D131" t="s">
-        <v>174</v>
+        <v>23</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F131" s="11">
-        <v>1400</v>
+        <v>3500</v>
       </c>
       <c r="G131" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="132" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>126</v>
+      </c>
       <c r="B132" s="1">
         <v>115</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>20</v>
+      <c r="C132" t="s">
+        <v>163</v>
+      </c>
+      <c r="D132" t="s">
+        <v>174</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F132" s="2">
-        <v>45000</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="133" spans="2:8" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F132" s="11">
+        <v>7200</v>
+      </c>
+      <c r="G132" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>127</v>
+      </c>
       <c r="B133" s="1">
         <v>115</v>
       </c>
       <c r="C133" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="D133" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F133" s="11">
-        <v>5600</v>
+        <v>3500</v>
       </c>
       <c r="G133" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="134" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B134" s="1">
         <v>115</v>
       </c>
       <c r="C134" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="D134" t="s">
-        <v>60</v>
-      </c>
-      <c r="E134" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F134" s="2">
-        <v>3400</v>
-      </c>
-      <c r="G134" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H134" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="135" spans="2:8" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F134" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G134" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B135" s="1">
         <v>115</v>
       </c>
       <c r="C135" t="s">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="D135" t="s">
-        <v>60</v>
-      </c>
-      <c r="E135" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F135" s="2">
-        <v>13120</v>
-      </c>
-      <c r="G135" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H135" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F135" s="11">
+        <v>5700</v>
+      </c>
+      <c r="G135" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B136" s="1">
         <v>115</v>
       </c>
       <c r="C136" t="s">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="D136" t="s">
-        <v>60</v>
+        <v>174</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F136" s="11">
-        <v>10000</v>
+        <v>1400</v>
       </c>
       <c r="G136" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="137" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B137" s="1">
         <v>115</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F137" s="2">
-        <v>2682</v>
+        <v>45000</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B138" s="1">
         <v>115</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="C138" t="s">
+        <v>38</v>
+      </c>
+      <c r="D138" t="s">
+        <v>20</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F138" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G138" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B139" s="1">
+        <v>115</v>
+      </c>
+      <c r="C139" t="s">
+        <v>100</v>
+      </c>
+      <c r="D139" t="s">
+        <v>60</v>
+      </c>
+      <c r="E139" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F139" s="2">
+        <v>3400</v>
+      </c>
+      <c r="G139" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H139" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B140" s="1">
+        <v>115</v>
+      </c>
+      <c r="C140" t="s">
+        <v>100</v>
+      </c>
+      <c r="D140" t="s">
+        <v>60</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F140" s="2">
+        <v>13120</v>
+      </c>
+      <c r="G140" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H140" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B141" s="1">
+        <v>115</v>
+      </c>
+      <c r="C141" t="s">
+        <v>100</v>
+      </c>
+      <c r="D141" t="s">
+        <v>60</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F141" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G141" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B142" s="1">
+        <v>115</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F138" s="2">
-        <v>51000</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B139" s="1">
-        <v>115</v>
-      </c>
-      <c r="C139" t="s">
-        <v>39</v>
-      </c>
-      <c r="D139" t="s">
-        <v>40</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F139" s="11">
-        <v>900</v>
-      </c>
-      <c r="G139" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B140" s="1">
-        <v>115</v>
-      </c>
-      <c r="C140" t="s">
-        <v>157</v>
-      </c>
-      <c r="D140" t="s">
-        <v>23</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F140" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G140" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B141" s="1">
-        <v>115</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F141" s="2">
-        <v>16788</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B142" s="1">
-        <v>115</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>40</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F142" s="2">
-        <v>12800</v>
+        <v>2682</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="143" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B143" s="1">
         <v>115</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D143" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E143" s="3" t="s">
-        <v>81</v>
+        <v>39</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F143" s="2">
-        <v>143300</v>
+        <v>51000</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B144" s="1">
         <v>115</v>
       </c>
-      <c r="C144" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>13</v>
+      <c r="C144" t="s">
+        <v>39</v>
+      </c>
+      <c r="D144" t="s">
+        <v>40</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F144" s="2">
-        <v>34568</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="145" spans="2:8" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F144" s="11">
+        <v>900</v>
+      </c>
+      <c r="G144" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="145" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B145" s="1">
         <v>115</v>
       </c>
       <c r="C145" t="s">
-        <v>66</v>
+        <v>157</v>
       </c>
       <c r="D145" t="s">
-        <v>177</v>
+        <v>23</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F145" s="11">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="G145" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="146" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B146" s="1">
         <v>115</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E146" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F146" s="2">
+        <v>16788</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B147" s="1">
+        <v>115</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" s="2">
+        <v>12800</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="2:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="B148" s="1">
+        <v>115</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E148" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F146" s="2">
-        <v>300000</v>
-      </c>
-      <c r="G146" s="1" t="s">
+      <c r="F148" s="2">
+        <v>143300</v>
+      </c>
+      <c r="G148" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="147" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B147" s="1">
-        <v>115</v>
-      </c>
-      <c r="C147" t="s">
-        <v>73</v>
-      </c>
-      <c r="D147" t="s">
-        <v>23</v>
-      </c>
-      <c r="E147" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F147" s="2">
-        <v>47500</v>
-      </c>
-      <c r="G147" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="148" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B148" s="1">
-        <v>115</v>
-      </c>
-      <c r="C148" t="s">
-        <v>73</v>
-      </c>
-      <c r="D148" t="s">
-        <v>23</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F148" s="11">
-        <v>3700</v>
-      </c>
-      <c r="G148" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="149" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B149" s="1">
         <v>115</v>
       </c>
-      <c r="C149" t="s">
-        <v>155</v>
-      </c>
-      <c r="D149" t="s">
-        <v>23</v>
+      <c r="C149" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F149" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G149" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="150" spans="2:8" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+      <c r="F149" s="2">
+        <v>34568</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="150" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B150" s="1">
         <v>115</v>
       </c>
       <c r="C150" t="s">
-        <v>158</v>
+        <v>66</v>
       </c>
       <c r="D150" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F150" s="11">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="G150" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="151" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="151" spans="2:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="B151" s="1">
         <v>115</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F151" s="2">
+        <v>300000</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="152" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B152" s="1">
+        <v>115</v>
+      </c>
+      <c r="C152" t="s">
+        <v>73</v>
+      </c>
+      <c r="D152" t="s">
+        <v>23</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F152" s="2">
+        <v>47500</v>
+      </c>
+      <c r="G152" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="153" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B153" s="1">
+        <v>115</v>
+      </c>
+      <c r="C153" t="s">
+        <v>73</v>
+      </c>
+      <c r="D153" t="s">
+        <v>23</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F153" s="11">
+        <v>3700</v>
+      </c>
+      <c r="G153" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="154" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B154" s="1">
+        <v>115</v>
+      </c>
+      <c r="C154" t="s">
+        <v>155</v>
+      </c>
+      <c r="D154" t="s">
+        <v>23</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F154" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G154" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="155" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B155" s="1">
+        <v>115</v>
+      </c>
+      <c r="C155" t="s">
+        <v>158</v>
+      </c>
+      <c r="D155" t="s">
+        <v>23</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F155" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G155" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="156" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B156" s="1">
+        <v>115</v>
+      </c>
+      <c r="C156" t="s">
         <v>154</v>
       </c>
-      <c r="D151" t="s">
+      <c r="D156" t="s">
         <v>23</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F151" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G151" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="152" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B152" s="1">
-        <v>115</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F152" s="2">
-        <v>52000</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="153" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="B153" s="1">
-        <v>115</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D153" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E153" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F153" s="2">
-        <v>210000</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="154" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B154" s="1">
-        <v>115</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F154" s="2">
-        <v>42500</v>
-      </c>
-      <c r="G154" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="155" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B155" s="1">
-        <v>115</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F155" s="2">
-        <v>70000</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="156" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B156" s="1">
-        <v>115</v>
-      </c>
-      <c r="C156" t="s">
-        <v>43</v>
-      </c>
-      <c r="D156" t="s">
-        <v>20</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F156" s="11">
-        <v>5600</v>
+        <v>3500</v>
       </c>
       <c r="G156" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="157" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B157" s="1">
         <v>115</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>16</v>
@@ -13488,73 +13872,70 @@
         <v>11</v>
       </c>
       <c r="F157" s="2">
-        <v>59500</v>
+        <v>52000</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="158" spans="2:7" ht="17.25" x14ac:dyDescent="0.35">
       <c r="B158" s="1">
         <v>115</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E158" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F158" s="2">
+        <v>210000</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="159" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B159" s="1">
+        <v>115</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F159" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B160" s="1">
+        <v>115</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F158" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G158" s="1" t="s">
+      <c r="F160" s="2">
+        <v>70000</v>
+      </c>
+      <c r="G160" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="159" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
-      <c r="B159" s="1">
-        <v>115</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D159" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E159" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F159" s="2">
-        <v>200000</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="160" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B160" s="1">
-        <v>115</v>
-      </c>
-      <c r="C160" t="s">
-        <v>95</v>
-      </c>
-      <c r="D160" t="s">
-        <v>23</v>
-      </c>
-      <c r="E160" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F160" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G160" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H160" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="161" spans="2:8" x14ac:dyDescent="0.35">
@@ -13562,122 +13943,125 @@
         <v>115</v>
       </c>
       <c r="C161" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="D161" t="s">
-        <v>23</v>
-      </c>
-      <c r="E161" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F161" s="2">
-        <v>42393</v>
-      </c>
-      <c r="G161" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H161" t="s">
-        <v>102</v>
+        <v>20</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F161" s="11">
+        <v>5600</v>
+      </c>
+      <c r="G161" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="162" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B162" s="1">
         <v>115</v>
       </c>
-      <c r="C162" t="s">
-        <v>95</v>
-      </c>
-      <c r="D162" t="s">
-        <v>23</v>
+      <c r="C162" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F162" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G162" t="s">
-        <v>168</v>
+        <v>11</v>
+      </c>
+      <c r="F162" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B163" s="1">
         <v>115</v>
       </c>
-      <c r="C163" t="s">
-        <v>159</v>
-      </c>
-      <c r="D163" t="s">
-        <v>23</v>
+      <c r="C163" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F163" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G163" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="164" spans="2:8" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F163" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="B164" s="1">
         <v>115</v>
       </c>
-      <c r="C164" t="s">
-        <v>119</v>
-      </c>
-      <c r="D164" t="s">
-        <v>29</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F164" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G164" t="s">
-        <v>168</v>
+      <c r="C164" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F164" s="2">
+        <v>200000</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="165" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B165" s="1">
         <v>115</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>21</v>
+      <c r="C165" t="s">
+        <v>95</v>
+      </c>
+      <c r="D165" t="s">
+        <v>23</v>
+      </c>
+      <c r="E165" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="F165" s="2">
-        <v>44118</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="166" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
+        <v>50000</v>
+      </c>
+      <c r="G165" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H165" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="166" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B166" s="1">
         <v>115</v>
       </c>
-      <c r="C166" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D166" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E166" s="3" t="s">
-        <v>81</v>
+      <c r="C166" t="s">
+        <v>95</v>
+      </c>
+      <c r="D166" t="s">
+        <v>23</v>
+      </c>
+      <c r="E166" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="F166" s="2">
-        <v>217500</v>
-      </c>
-      <c r="G166" s="1" t="s">
-        <v>82</v>
+        <v>42393</v>
+      </c>
+      <c r="G166" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H166" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="167" spans="2:8" x14ac:dyDescent="0.35">
@@ -13685,16 +14069,16 @@
         <v>115</v>
       </c>
       <c r="C167" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="D167" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F167" s="11">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="G167" t="s">
         <v>168</v>
@@ -13705,16 +14089,16 @@
         <v>115</v>
       </c>
       <c r="C168" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D168" t="s">
-        <v>175</v>
+        <v>23</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F168" s="11">
-        <v>6000</v>
+        <v>3500</v>
       </c>
       <c r="G168" t="s">
         <v>168</v>
@@ -13725,10 +14109,10 @@
         <v>115</v>
       </c>
       <c r="C169" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D169" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>170</v>
@@ -13745,42 +14129,39 @@
         <v>115</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F170" s="2">
-        <v>59500</v>
+        <v>44118</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="171" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="171" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="B171" s="1">
         <v>115</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D171" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D171" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E171" s="6" t="s">
-        <v>94</v>
+      <c r="E171" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F171" s="2">
-        <v>60000</v>
+        <v>217500</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H171" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="172" spans="2:8" x14ac:dyDescent="0.35">
@@ -13788,7 +14169,7 @@
         <v>115</v>
       </c>
       <c r="C172" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D172" t="s">
         <v>46</v>
@@ -13797,7 +14178,7 @@
         <v>170</v>
       </c>
       <c r="F172" s="11">
-        <v>1400</v>
+        <v>10000</v>
       </c>
       <c r="G172" t="s">
         <v>168</v>
@@ -13807,60 +14188,60 @@
       <c r="B173" s="1">
         <v>115</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>13</v>
+      <c r="C173" t="s">
+        <v>166</v>
+      </c>
+      <c r="D173" t="s">
+        <v>175</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F173" s="2">
-        <v>52500</v>
-      </c>
-      <c r="G173" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F173" s="11">
+        <v>6000</v>
+      </c>
+      <c r="G173" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="174" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B174" s="1">
         <v>115</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>13</v>
+      <c r="C174" t="s">
+        <v>120</v>
+      </c>
+      <c r="D174" t="s">
+        <v>10</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F174" s="2">
-        <v>52776</v>
-      </c>
-      <c r="G174" s="1" t="s">
-        <v>84</v>
+        <v>170</v>
+      </c>
+      <c r="F174" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G174" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="175" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B175" s="1">
         <v>115</v>
       </c>
-      <c r="C175" t="s">
-        <v>48</v>
-      </c>
-      <c r="D175" t="s">
-        <v>13</v>
+      <c r="C175" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F175" s="11">
-        <v>900</v>
-      </c>
-      <c r="G175" t="s">
-        <v>168</v>
+        <v>7</v>
+      </c>
+      <c r="F175" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="176" spans="2:8" x14ac:dyDescent="0.35">
@@ -13868,19 +14249,22 @@
         <v>115</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>7</v>
+        <v>63</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="F176" s="2">
-        <v>63000</v>
+        <v>60000</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>8</v>
+        <v>91</v>
+      </c>
+      <c r="H176" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="177" spans="2:8" x14ac:dyDescent="0.35">
@@ -13888,65 +14272,59 @@
         <v>115</v>
       </c>
       <c r="C177" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D177" t="s">
-        <v>23</v>
-      </c>
-      <c r="E177" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F177" s="2">
-        <v>41616</v>
-      </c>
-      <c r="G177" s="9" t="s">
-        <v>88</v>
+        <v>46</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F177" s="11">
+        <v>1400</v>
+      </c>
+      <c r="G177" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="178" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B178" s="1">
         <v>115</v>
       </c>
-      <c r="C178" t="s">
-        <v>49</v>
-      </c>
-      <c r="D178" t="s">
-        <v>23</v>
-      </c>
-      <c r="E178" s="10" t="s">
-        <v>178</v>
+      <c r="C178" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="F178" s="2">
-        <v>50000</v>
-      </c>
-      <c r="G178" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H178" t="s">
-        <v>110</v>
+        <v>52500</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B179" s="1">
         <v>115</v>
       </c>
-      <c r="C179" t="s">
-        <v>49</v>
-      </c>
-      <c r="D179" t="s">
-        <v>23</v>
-      </c>
-      <c r="E179" s="10" t="s">
-        <v>179</v>
+      <c r="C179" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F179" s="2">
-        <v>38569</v>
-      </c>
-      <c r="G179" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H179" t="s">
-        <v>110</v>
+        <v>52776</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="180" spans="2:8" x14ac:dyDescent="0.35">
@@ -13954,16 +14332,16 @@
         <v>115</v>
       </c>
       <c r="C180" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D180" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F180" s="11">
-        <v>5000</v>
+        <v>900</v>
       </c>
       <c r="G180" t="s">
         <v>168</v>
@@ -13973,40 +14351,40 @@
       <c r="B181" s="1">
         <v>115</v>
       </c>
-      <c r="C181" t="s">
-        <v>142</v>
-      </c>
-      <c r="D181" t="s">
+      <c r="C181" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F181" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G181" t="s">
-        <v>168</v>
+        <v>7</v>
+      </c>
+      <c r="F181" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="182" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B182" s="1">
         <v>115</v>
       </c>
-      <c r="C182" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D182" s="1" t="s">
+      <c r="C182" t="s">
+        <v>49</v>
+      </c>
+      <c r="D182" t="s">
         <v>23</v>
       </c>
-      <c r="E182" s="1" t="s">
-        <v>21</v>
+      <c r="E182" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="F182" s="2">
-        <v>31500</v>
-      </c>
-      <c r="G182" s="1" t="s">
-        <v>8</v>
+        <v>41616</v>
+      </c>
+      <c r="G182" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="183" spans="2:8" x14ac:dyDescent="0.35">
@@ -14014,39 +14392,45 @@
         <v>115</v>
       </c>
       <c r="C183" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D183" t="s">
-        <v>172</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F183" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G183" t="s">
-        <v>168</v>
+        <v>23</v>
+      </c>
+      <c r="E183" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F183" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G183" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H183" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="184" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B184" s="1">
         <v>115</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>21</v>
+      <c r="C184" t="s">
+        <v>49</v>
+      </c>
+      <c r="D184" t="s">
+        <v>23</v>
+      </c>
+      <c r="E184" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="F184" s="2">
-        <v>42500</v>
-      </c>
-      <c r="G184" s="1" t="s">
-        <v>8</v>
+        <v>38569</v>
+      </c>
+      <c r="G184" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H184" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="185" spans="2:8" x14ac:dyDescent="0.35">
@@ -14054,59 +14438,59 @@
         <v>115</v>
       </c>
       <c r="C185" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D185" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F185" s="11">
-        <v>5600</v>
+        <v>5000</v>
       </c>
       <c r="G185" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="186" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="186" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B186" s="1">
         <v>115</v>
       </c>
-      <c r="C186" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D186" s="1" t="s">
+      <c r="C186" t="s">
+        <v>142</v>
+      </c>
+      <c r="D186" t="s">
         <v>23</v>
       </c>
-      <c r="E186" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F186" s="2">
-        <v>95912</v>
-      </c>
-      <c r="G186" s="1" t="s">
-        <v>82</v>
+      <c r="E186" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F186" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G186" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="187" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B187" s="1">
         <v>115</v>
       </c>
-      <c r="C187" t="s">
-        <v>72</v>
-      </c>
-      <c r="D187" t="s">
+      <c r="C187" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F187" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G187" t="s">
-        <v>168</v>
+        <v>21</v>
+      </c>
+      <c r="F187" s="2">
+        <v>31500</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="188" spans="2:8" x14ac:dyDescent="0.35">
@@ -14114,10 +14498,10 @@
         <v>115</v>
       </c>
       <c r="C188" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="D188" t="s">
-        <v>23</v>
+        <v>172</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>170</v>
@@ -14129,24 +14513,24 @@
         <v>168</v>
       </c>
     </row>
-    <row r="189" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="189" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B189" s="1">
         <v>115</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E189" s="3" t="s">
-        <v>81</v>
+        <v>20</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="F189" s="2">
-        <v>28500</v>
+        <v>42500</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="2:8" x14ac:dyDescent="0.35">
@@ -14154,39 +14538,39 @@
         <v>115</v>
       </c>
       <c r="C190" t="s">
-        <v>129</v>
+        <v>51</v>
       </c>
       <c r="D190" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F190" s="11">
-        <v>3500</v>
+        <v>5600</v>
       </c>
       <c r="G190" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="191" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="B191" s="1">
         <v>115</v>
       </c>
-      <c r="C191" t="s">
-        <v>143</v>
-      </c>
-      <c r="D191" t="s">
+      <c r="C191" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E191" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F191" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G191" t="s">
-        <v>168</v>
+      <c r="E191" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F191" s="2">
+        <v>95912</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="192" spans="2:8" x14ac:dyDescent="0.35">
@@ -14194,7 +14578,7 @@
         <v>115</v>
       </c>
       <c r="C192" t="s">
-        <v>148</v>
+        <v>72</v>
       </c>
       <c r="D192" t="s">
         <v>23</v>
@@ -14214,7 +14598,7 @@
         <v>115</v>
       </c>
       <c r="C193" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="D193" t="s">
         <v>23</v>
@@ -14229,24 +14613,24 @@
         <v>168</v>
       </c>
     </row>
-    <row r="194" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="194" spans="2:8" ht="17.25" x14ac:dyDescent="0.35">
       <c r="B194" s="1">
         <v>115</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="F194" s="2">
-        <v>29250</v>
+        <v>28500</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="195" spans="2:8" x14ac:dyDescent="0.35">
@@ -14254,22 +14638,19 @@
         <v>115</v>
       </c>
       <c r="C195" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="D195" t="s">
-        <v>29</v>
-      </c>
-      <c r="E195" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F195" s="2">
-        <v>8900</v>
-      </c>
-      <c r="G195" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H195" t="s">
-        <v>105</v>
+        <v>23</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F195" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G195" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="196" spans="2:8" x14ac:dyDescent="0.35">
@@ -14277,22 +14658,19 @@
         <v>115</v>
       </c>
       <c r="C196" t="s">
-        <v>52</v>
+        <v>143</v>
       </c>
       <c r="D196" t="s">
-        <v>29</v>
-      </c>
-      <c r="E196" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F196" s="2">
-        <v>0</v>
-      </c>
-      <c r="G196" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H196" t="s">
-        <v>112</v>
+        <v>23</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F196" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G196" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="197" spans="2:8" x14ac:dyDescent="0.35">
@@ -14300,22 +14678,19 @@
         <v>115</v>
       </c>
       <c r="C197" t="s">
-        <v>52</v>
+        <v>148</v>
       </c>
       <c r="D197" t="s">
-        <v>29</v>
-      </c>
-      <c r="E197" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F197" s="2">
-        <v>19190</v>
-      </c>
-      <c r="G197" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H197" t="s">
-        <v>105</v>
+        <v>23</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F197" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G197" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="198" spans="2:8" x14ac:dyDescent="0.35">
@@ -14323,42 +14698,39 @@
         <v>115</v>
       </c>
       <c r="C198" t="s">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="D198" t="s">
-        <v>29</v>
-      </c>
-      <c r="E198" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F198" s="2">
-        <v>17728</v>
-      </c>
-      <c r="G198" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H198" t="s">
-        <v>112</v>
+        <v>23</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F198" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G198" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="199" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B199" s="1">
         <v>115</v>
       </c>
-      <c r="C199" t="s">
+      <c r="C199" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D199" t="s">
+      <c r="D199" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F199" s="11">
-        <v>2200</v>
-      </c>
-      <c r="G199" t="s">
-        <v>168</v>
+        <v>21</v>
+      </c>
+      <c r="F199" s="2">
+        <v>29250</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="200" spans="2:8" x14ac:dyDescent="0.35">
@@ -14366,19 +14738,22 @@
         <v>115</v>
       </c>
       <c r="C200" t="s">
-        <v>160</v>
+        <v>52</v>
       </c>
       <c r="D200" t="s">
-        <v>172</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F200" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G200" t="s">
-        <v>168</v>
+        <v>29</v>
+      </c>
+      <c r="E200" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F200" s="2">
+        <v>8900</v>
+      </c>
+      <c r="G200" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H200" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="201" spans="2:8" x14ac:dyDescent="0.35">
@@ -14386,22 +14761,22 @@
         <v>115</v>
       </c>
       <c r="C201" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="D201" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>178</v>
       </c>
       <c r="F201" s="2">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="G201" s="10" t="s">
         <v>117</v>
       </c>
       <c r="H201" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="202" spans="2:8" x14ac:dyDescent="0.35">
@@ -14409,22 +14784,22 @@
         <v>115</v>
       </c>
       <c r="C202" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="D202" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E202" s="10" t="s">
         <v>179</v>
       </c>
       <c r="F202" s="2">
-        <v>17600</v>
+        <v>19190</v>
       </c>
       <c r="G202" s="10" t="s">
         <v>117</v>
       </c>
       <c r="H202" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="203" spans="2:8" x14ac:dyDescent="0.35">
@@ -14432,19 +14807,22 @@
         <v>115</v>
       </c>
       <c r="C203" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="D203" t="s">
-        <v>23</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F203" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G203" t="s">
-        <v>168</v>
+        <v>29</v>
+      </c>
+      <c r="E203" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F203" s="2">
+        <v>17728</v>
+      </c>
+      <c r="G203" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H203" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="204" spans="2:8" x14ac:dyDescent="0.35">
@@ -14452,16 +14830,16 @@
         <v>115</v>
       </c>
       <c r="C204" t="s">
-        <v>151</v>
+        <v>52</v>
       </c>
       <c r="D204" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F204" s="11">
-        <v>3500</v>
+        <v>2200</v>
       </c>
       <c r="G204" t="s">
         <v>168</v>
@@ -14471,20 +14849,20 @@
       <c r="B205" s="1">
         <v>115</v>
       </c>
-      <c r="C205" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>23</v>
+      <c r="C205" t="s">
+        <v>160</v>
+      </c>
+      <c r="D205" t="s">
+        <v>172</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F205" s="2">
-        <v>41384</v>
-      </c>
-      <c r="G205" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F205" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G205" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="206" spans="2:8" x14ac:dyDescent="0.35">
@@ -14492,7 +14870,7 @@
         <v>115</v>
       </c>
       <c r="C206" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="D206" t="s">
         <v>23</v>
@@ -14507,7 +14885,7 @@
         <v>117</v>
       </c>
       <c r="H206" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="207" spans="2:8" x14ac:dyDescent="0.35">
@@ -14515,7 +14893,7 @@
         <v>115</v>
       </c>
       <c r="C207" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="D207" t="s">
         <v>23</v>
@@ -14524,13 +14902,13 @@
         <v>179</v>
       </c>
       <c r="F207" s="2">
-        <v>19200</v>
+        <v>17600</v>
       </c>
       <c r="G207" s="10" t="s">
         <v>117</v>
       </c>
       <c r="H207" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="208" spans="2:8" x14ac:dyDescent="0.35">
@@ -14538,7 +14916,7 @@
         <v>115</v>
       </c>
       <c r="C208" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="D208" t="s">
         <v>23</v>
@@ -14553,192 +14931,198 @@
         <v>168</v>
       </c>
     </row>
-    <row r="209" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="209" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B209" s="1">
         <v>115</v>
       </c>
-      <c r="C209" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>13</v>
+      <c r="C209" t="s">
+        <v>151</v>
+      </c>
+      <c r="D209" t="s">
+        <v>23</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F209" s="2">
-        <v>56000</v>
-      </c>
-      <c r="G209" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F209" s="11">
+        <v>3500</v>
+      </c>
+      <c r="G209" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="210" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B210" s="1">
+        <v>115</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F210" s="2">
+        <v>41384</v>
+      </c>
+      <c r="G210" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="210" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B210" s="1">
-        <v>115</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F210" s="2">
-        <v>48284</v>
-      </c>
-      <c r="G210" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="211" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="211" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B211" s="1">
         <v>115</v>
       </c>
       <c r="C211" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D211" t="s">
-        <v>13</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F211" s="11">
-        <v>6300</v>
-      </c>
-      <c r="G211" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="212" spans="2:7" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="E211" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F211" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G211" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H211" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="212" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B212" s="1">
         <v>115</v>
       </c>
-      <c r="C212" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>21</v>
+      <c r="C212" t="s">
+        <v>53</v>
+      </c>
+      <c r="D212" t="s">
+        <v>23</v>
+      </c>
+      <c r="E212" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="F212" s="2">
-        <v>42500</v>
-      </c>
-      <c r="G212" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="213" spans="2:7" x14ac:dyDescent="0.35">
+        <v>19200</v>
+      </c>
+      <c r="G212" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H212" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="213" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B213" s="1">
         <v>115</v>
       </c>
       <c r="C213" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D213" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F213" s="11">
-        <v>5600</v>
+        <v>3500</v>
       </c>
       <c r="G213" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="214" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="214" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B214" s="1">
         <v>115</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F214" s="2">
-        <v>41770</v>
+        <v>56000</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="215" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B215" s="1">
         <v>115</v>
       </c>
-      <c r="C215" t="s">
-        <v>56</v>
-      </c>
-      <c r="D215" t="s">
-        <v>23</v>
+      <c r="C215" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E215" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F215" s="2">
+        <v>48284</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="216" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B216" s="1">
+        <v>115</v>
+      </c>
+      <c r="C216" t="s">
+        <v>54</v>
+      </c>
+      <c r="D216" t="s">
+        <v>13</v>
+      </c>
+      <c r="E216" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F215" s="11">
-        <v>4100</v>
-      </c>
-      <c r="G215" t="s">
+      <c r="F216" s="11">
+        <v>6300</v>
+      </c>
+      <c r="G216" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="216" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B216" s="1">
-        <v>115</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D216" s="1" t="s">
+    <row r="217" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B217" s="1">
+        <v>115</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D217" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E216" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F216" s="2">
-        <v>45000</v>
-      </c>
-      <c r="G216" s="1" t="s">
+      <c r="E217" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F217" s="2">
+        <v>42500</v>
+      </c>
+      <c r="G217" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="217" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B217" s="1">
-        <v>115</v>
-      </c>
-      <c r="C217" t="s">
-        <v>57</v>
-      </c>
-      <c r="D217" t="s">
-        <v>86</v>
-      </c>
-      <c r="E217" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F217" s="2">
-        <v>40000</v>
-      </c>
-      <c r="G217" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="218" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="218" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B218" s="1">
         <v>115</v>
       </c>
       <c r="C218" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D218" t="s">
         <v>20</v>
@@ -14747,38 +15131,38 @@
         <v>170</v>
       </c>
       <c r="F218" s="11">
-        <v>10000</v>
+        <v>5600</v>
       </c>
       <c r="G218" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="219" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="219" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B219" s="1">
         <v>115</v>
       </c>
-      <c r="C219" t="s">
-        <v>152</v>
-      </c>
-      <c r="D219" t="s">
+      <c r="C219" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F219" s="11">
-        <v>3500</v>
-      </c>
-      <c r="G219" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="220" spans="2:7" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="F219" s="2">
+        <v>41770</v>
+      </c>
+      <c r="G219" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B220" s="1">
         <v>115</v>
       </c>
       <c r="C220" t="s">
-        <v>153</v>
+        <v>56</v>
       </c>
       <c r="D220" t="s">
         <v>23</v>
@@ -14787,87 +15171,87 @@
         <v>170</v>
       </c>
       <c r="F220" s="11">
-        <v>5000</v>
+        <v>4100</v>
       </c>
       <c r="G220" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="221" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="221" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B221" s="1">
         <v>115</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F221" s="2">
-        <v>39125</v>
+        <v>45000</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="222" spans="2:7" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="222" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B222" s="1">
         <v>115</v>
       </c>
       <c r="C222" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D222" t="s">
-        <v>23</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F222" s="11">
-        <v>7500</v>
-      </c>
-      <c r="G222" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="223" spans="2:7" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+      <c r="E222" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F222" s="2">
+        <v>40000</v>
+      </c>
+      <c r="G222" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="223" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B223" s="1">
         <v>115</v>
       </c>
       <c r="C223" t="s">
-        <v>164</v>
+        <v>57</v>
       </c>
       <c r="D223" t="s">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F223" s="11">
-        <v>5200</v>
+        <v>10000</v>
       </c>
       <c r="G223" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="224" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="224" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B224" s="1">
         <v>115</v>
       </c>
       <c r="C224" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="D224" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F224" s="11">
-        <v>5200</v>
+        <v>3500</v>
       </c>
       <c r="G224" t="s">
         <v>168</v>
@@ -14877,60 +15261,60 @@
       <c r="B225" s="1">
         <v>115</v>
       </c>
-      <c r="C225" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D225" s="1" t="s">
-        <v>60</v>
+      <c r="C225" t="s">
+        <v>153</v>
+      </c>
+      <c r="D225" t="s">
+        <v>23</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F225" s="2">
-        <v>59500</v>
-      </c>
-      <c r="G225" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="226" spans="2:7" ht="17.25" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="F225" s="11">
+        <v>5000</v>
+      </c>
+      <c r="G225" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="226" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B226" s="1">
         <v>115</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D226" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E226" s="3" t="s">
-        <v>81</v>
+        <v>65</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F226" s="2">
-        <v>221000</v>
+        <v>39125</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="227" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B227" s="1">
         <v>115</v>
       </c>
-      <c r="C227" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D227" s="1" t="s">
-        <v>60</v>
+      <c r="C227" t="s">
+        <v>65</v>
+      </c>
+      <c r="D227" t="s">
+        <v>23</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F227" s="2">
-        <v>26283</v>
-      </c>
-      <c r="G227" s="1" t="s">
-        <v>84</v>
+        <v>170</v>
+      </c>
+      <c r="F227" s="11">
+        <v>7500</v>
+      </c>
+      <c r="G227" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="228" spans="2:7" x14ac:dyDescent="0.35">
@@ -14938,64 +15322,164 @@
         <v>115</v>
       </c>
       <c r="C228" t="s">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="D228" t="s">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F228" s="11">
-        <v>1100</v>
-      </c>
-      <c r="G228" s="12" t="s">
-        <v>169</v>
+        <v>5200</v>
+      </c>
+      <c r="G228" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="229" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B229" s="1">
         <v>115</v>
       </c>
-      <c r="C229" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>60</v>
+      <c r="C229" t="s">
+        <v>165</v>
+      </c>
+      <c r="D229" t="s">
+        <v>40</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F229" s="2">
-        <v>63000</v>
-      </c>
-      <c r="G229" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
+      </c>
+      <c r="F229" s="11">
+        <v>5200</v>
+      </c>
+      <c r="G229" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="230" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B230" s="1">
         <v>115</v>
       </c>
-      <c r="C230" t="s">
+      <c r="C230" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F230" s="2">
+        <v>59500</v>
+      </c>
+      <c r="G230" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="231" spans="2:7" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="B231" s="1">
+        <v>115</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D231" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F231" s="2">
+        <v>221000</v>
+      </c>
+      <c r="G231" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="232" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B232" s="1">
+        <v>115</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F232" s="2">
+        <v>26283</v>
+      </c>
+      <c r="G232" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="233" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B233" s="1">
+        <v>115</v>
+      </c>
+      <c r="C233" t="s">
+        <v>58</v>
+      </c>
+      <c r="D233" t="s">
+        <v>60</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F233" s="11">
+        <v>1100</v>
+      </c>
+      <c r="G233" s="12" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="234" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B234" s="1">
+        <v>115</v>
+      </c>
+      <c r="C234" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D230" t="s">
+      <c r="D234" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E230" s="1" t="s">
+      <c r="E234" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F234" s="2">
+        <v>63000</v>
+      </c>
+      <c r="G234" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="235" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B235" s="1">
+        <v>115</v>
+      </c>
+      <c r="C235" t="s">
+        <v>59</v>
+      </c>
+      <c r="D235" t="s">
+        <v>60</v>
+      </c>
+      <c r="E235" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F230" s="11">
+      <c r="F235" s="11">
         <v>2700</v>
       </c>
-      <c r="G230" t="s">
+      <c r="G235" t="s">
         <v>168</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:H230">
-    <sortCondition ref="C2:C230"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:H235">
+    <sortCondition ref="C2:C235"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5.2. 獎補助執行清冊、自評表\★.教師獎補助查詢系統_v10.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB39575-CDA4-4C76-AB69-5C67B62D07BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A009742C-F46A-458A-9CA2-1E6692EC7991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$H$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資料表!$A$1:$H$235</definedName>
     <definedName name="Barcode">OFFSET(#REF!,MATCH(#REF!,#REF!,0)-1,0)</definedName>
     <definedName name="重大活動行事曆">[1]重要活動行事曆!$C$2:$I$467</definedName>
     <definedName name="資料">#REF!</definedName>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="181">
   <si>
     <t>序號</t>
   </si>
@@ -645,27 +645,6 @@
     <t>獎勵教師輔導學生獲取國家或國際證照</t>
   </si>
   <si>
-    <t>秘書室</t>
-  </si>
-  <si>
-    <t>教務處</t>
-  </si>
-  <si>
-    <t>學生事務處</t>
-  </si>
-  <si>
-    <t>圖書資訊處</t>
-  </si>
-  <si>
-    <t>會計室</t>
-  </si>
-  <si>
-    <t>校長室</t>
-  </si>
-  <si>
-    <t>技術合作處</t>
-  </si>
-  <si>
     <t>參加國際研討會並發表_研習差旅費</t>
   </si>
   <si>
@@ -673,10 +652,6 @@
   </si>
   <si>
     <t>獎勵教師輔導學生獲取國家或國際證照</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>獎勵教師指導學 生參與校外競賽獲獎</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -1026,6 +1001,13 @@
       </rPr>
       <t>。</t>
     </r>
+  </si>
+  <si>
+    <t>獎勵教師指導學生參與校外競賽獲獎</t>
+  </si>
+  <si>
+    <t>跨領域教育中心</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -10355,8 +10337,8 @@
       <c r="C4" t="s">
         <v>122</v>
       </c>
-      <c r="D4" t="s">
-        <v>173</v>
+      <c r="D4" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>170</v>
@@ -10405,7 +10387,7 @@
         <v>23</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F6" s="2">
         <v>29000</v>
@@ -10431,7 +10413,7 @@
         <v>23</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F7" s="2">
         <v>2000</v>
@@ -10664,7 +10646,7 @@
         <v>23</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F17" s="2">
         <v>29636</v>
@@ -10690,7 +10672,7 @@
         <v>23</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F18" s="2">
         <v>11068</v>
@@ -10785,7 +10767,7 @@
         <v>23</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F22" s="2">
         <v>30850</v>
@@ -10811,7 +10793,7 @@
         <v>23</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F23" s="2">
         <v>12726</v>
@@ -11205,7 +11187,7 @@
         <v>16</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F40" s="11">
         <v>10000</v>
@@ -11225,7 +11207,7 @@
         <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F41" s="11">
         <v>10000</v>
@@ -11234,7 +11216,7 @@
         <v>117</v>
       </c>
       <c r="H41" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -11248,7 +11230,7 @@
         <v>16</v>
       </c>
       <c r="E42" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F42" s="11">
         <v>10000</v>
@@ -11257,7 +11239,7 @@
         <v>117</v>
       </c>
       <c r="H42" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -11271,7 +11253,7 @@
         <v>16</v>
       </c>
       <c r="E43" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F43" s="11">
         <v>10000</v>
@@ -11280,7 +11262,7 @@
         <v>117</v>
       </c>
       <c r="H43" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -11294,7 +11276,7 @@
         <v>16</v>
       </c>
       <c r="E44" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F44" s="11">
         <v>10000</v>
@@ -11303,7 +11285,7 @@
         <v>117</v>
       </c>
       <c r="H44" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -11317,7 +11299,7 @@
         <v>16</v>
       </c>
       <c r="E45" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F45" s="11">
         <v>10000</v>
@@ -11326,7 +11308,7 @@
         <v>117</v>
       </c>
       <c r="H45" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
@@ -11780,7 +11762,7 @@
         <v>23</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F65" s="2">
         <v>30850</v>
@@ -11806,7 +11788,7 @@
         <v>23</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F66" s="2">
         <v>9696</v>
@@ -11950,7 +11932,7 @@
         <v>23</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F72" s="2">
         <v>30850</v>
@@ -11976,7 +11958,7 @@
         <v>23</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F73" s="2">
         <v>19150</v>
@@ -12002,7 +11984,7 @@
         <v>23</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F74" s="2">
         <v>12936</v>
@@ -12028,7 +12010,7 @@
         <v>23</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F75" s="2">
         <v>31462</v>
@@ -12146,7 +12128,7 @@
         <v>29</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F80" s="2">
         <v>17789</v>
@@ -12172,7 +12154,7 @@
         <v>29</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F81" s="2">
         <v>8085</v>
@@ -12355,8 +12337,8 @@
       <c r="C89" t="s">
         <v>162</v>
       </c>
-      <c r="D89" t="s">
-        <v>177</v>
+      <c r="D89" s="10" t="s">
+        <v>180</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>170</v>
@@ -12378,8 +12360,8 @@
       <c r="C90" t="s">
         <v>161</v>
       </c>
-      <c r="D90" t="s">
-        <v>177</v>
+      <c r="D90" s="10" t="s">
+        <v>180</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>170</v>
@@ -12635,7 +12617,7 @@
         <v>23</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F101" s="2">
         <v>50000</v>
@@ -12661,7 +12643,7 @@
         <v>23</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F102" s="2">
         <v>38015</v>
@@ -12683,8 +12665,8 @@
       <c r="C103" t="s">
         <v>97</v>
       </c>
-      <c r="D103" t="s">
-        <v>172</v>
+      <c r="D103" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>170</v>
@@ -12871,7 +12853,7 @@
         <v>10</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F111" s="2">
         <v>19942</v>
@@ -12897,7 +12879,7 @@
         <v>10</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F112" s="2">
         <v>16447</v>
@@ -12942,8 +12924,8 @@
       <c r="C114" t="s">
         <v>74</v>
       </c>
-      <c r="D114" t="s">
-        <v>171</v>
+      <c r="D114" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>170</v>
@@ -13126,8 +13108,8 @@
       <c r="C122" t="s">
         <v>71</v>
       </c>
-      <c r="D122" t="s">
-        <v>173</v>
+      <c r="D122" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>170</v>
@@ -13287,8 +13269,8 @@
       <c r="C129" t="s">
         <v>36</v>
       </c>
-      <c r="D129" t="s">
-        <v>176</v>
+      <c r="D129" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>170</v>
@@ -13356,8 +13338,8 @@
       <c r="C132" t="s">
         <v>163</v>
       </c>
-      <c r="D132" t="s">
-        <v>174</v>
+      <c r="D132" s="10" t="s">
+        <v>180</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>170</v>
@@ -13439,8 +13421,8 @@
       <c r="C136" t="s">
         <v>167</v>
       </c>
-      <c r="D136" t="s">
-        <v>174</v>
+      <c r="D136" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>170</v>
@@ -13503,7 +13485,7 @@
         <v>60</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F139" s="2">
         <v>3400</v>
@@ -13526,7 +13508,7 @@
         <v>60</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F140" s="2">
         <v>13120</v>
@@ -13725,8 +13707,8 @@
       <c r="C150" t="s">
         <v>66</v>
       </c>
-      <c r="D150" t="s">
-        <v>177</v>
+      <c r="D150" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>170</v>
@@ -14029,7 +14011,7 @@
         <v>23</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F165" s="2">
         <v>50000</v>
@@ -14052,7 +14034,7 @@
         <v>23</v>
       </c>
       <c r="E166" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F166" s="2">
         <v>42393</v>
@@ -14191,8 +14173,8 @@
       <c r="C173" t="s">
         <v>166</v>
       </c>
-      <c r="D173" t="s">
-        <v>175</v>
+      <c r="D173" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>170</v>
@@ -14398,7 +14380,7 @@
         <v>23</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F183" s="2">
         <v>50000</v>
@@ -14421,7 +14403,7 @@
         <v>23</v>
       </c>
       <c r="E184" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F184" s="2">
         <v>38569</v>
@@ -14500,8 +14482,8 @@
       <c r="C188" t="s">
         <v>50</v>
       </c>
-      <c r="D188" t="s">
-        <v>172</v>
+      <c r="D188" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>170</v>
@@ -14744,7 +14726,7 @@
         <v>29</v>
       </c>
       <c r="E200" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F200" s="2">
         <v>8900</v>
@@ -14767,7 +14749,7 @@
         <v>29</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F201" s="2">
         <v>0</v>
@@ -14790,7 +14772,7 @@
         <v>29</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F202" s="2">
         <v>19190</v>
@@ -14813,7 +14795,7 @@
         <v>29</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F203" s="2">
         <v>17728</v>
@@ -14852,8 +14834,8 @@
       <c r="C205" t="s">
         <v>160</v>
       </c>
-      <c r="D205" t="s">
-        <v>172</v>
+      <c r="D205" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>170</v>
@@ -14876,7 +14858,7 @@
         <v>23</v>
       </c>
       <c r="E206" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F206" s="2">
         <v>40000</v>
@@ -14899,7 +14881,7 @@
         <v>23</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F207" s="2">
         <v>17600</v>
@@ -14982,7 +14964,7 @@
         <v>23</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F211" s="2">
         <v>40000</v>
@@ -15005,7 +14987,7 @@
         <v>23</v>
       </c>
       <c r="E212" s="10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F212" s="2">
         <v>19200</v>
@@ -15324,8 +15306,8 @@
       <c r="C228" t="s">
         <v>164</v>
       </c>
-      <c r="D228" t="s">
-        <v>173</v>
+      <c r="D228" s="10" t="s">
+        <v>180</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>170</v>
